--- a/support/specifications/ccda/CCDA to FHIR Conversion Spec - Epic.xlsx
+++ b/support/specifications/ccda/CCDA to FHIR Conversion Spec - Epic.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12180" tabRatio="709" activeTab="7"/>
+    <workbookView windowWidth="19200" windowHeight="8000" tabRatio="709" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Epic" sheetId="11" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="692" uniqueCount="443">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="696" uniqueCount="446">
   <si>
     <t>Epic CCDA</t>
   </si>
@@ -103,7 +103,12 @@
   <si>
     <t>"meta" : {
     "lastUpdated" : "2024-02-23T00:00:00Z",
-    "profile" : ["http://shinny.org/us/ny/hrsn/StructureDefinition/SHINNYBundleProfile"]
+    "profile" : ["http://shinny.org/us/ny/hrsn/StructureDefinition/SHINNYBundleProfile"],
+    "security": [ {
+                  "code": "ETH",
+                  "system": "http://terminology.hl7.org/CodeSystem/v3-ActCode",
+                  "display": "Substance abuse information sensitivity"
+              } ]
   },</t>
   </si>
   <si>
@@ -113,6 +118,56 @@
     <t>"http://shinny.org/us/ny/hrsn/StructureDefinition/SHINNYBundleProfile"</t>
   </si>
   <si>
+    <t>meta -&gt; security</t>
+  </si>
+  <si>
+    <r>
+      <t>If the header variable `</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>X-TechBD-Part2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>` has the value '</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>True</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>', then only the meta -&gt; security will be added.</t>
+    </r>
+  </si>
+  <si>
     <t>type</t>
   </si>
   <si>
@@ -128,7 +183,7 @@
     <t>entry</t>
   </si>
   <si>
-    <t>Resources - Patient, Encounter, Organization, Consent, Sexual orientation, Observations, Grouper Observation</t>
+    <t>Resources - Patient, Encounter, Organization, Consent, Sexual orientation, Observations, Grouper Observation, Location</t>
   </si>
   <si>
     <t>FHIR Resources</t>
@@ -339,6 +394,13 @@
   </si>
   <si>
     <t>Observation (Observation Grouper)</t>
+  </si>
+  <si>
+    <t>Location</t>
+  </si>
+  <si>
+    <t>The Location details are taken from Document.componentOf.encompassingEncounter.location.healthCareFacility.location.
+If it is not present in the CCDA file, the location details will be taken from the first occurance of the ClinicalDocument.component.structuredBody.component.section[code[@code='46240-8']].entry[1].encounter.participant.participantRole.</t>
   </si>
   <si>
     <t>Remarks</t>
@@ -3840,6 +3902,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>Combine the Facility ID obtained from the header variable '</t>
     </r>
     <r>
@@ -5071,9 +5140,6 @@
     <t>Included references to all the Observation resources.</t>
   </si>
   <si>
-    <t>Location</t>
-  </si>
-  <si>
     <r>
       <rPr>
         <sz val="11"/>
@@ -5209,7 +5275,7 @@
     <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="179" formatCode="_ &quot;₹&quot;* #,##0_ ;_ &quot;₹&quot;* \-#,##0_ ;_ &quot;₹&quot;* &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="39">
+  <fonts count="40">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -5291,6 +5357,12 @@
       <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
     </font>
     <font>
       <u/>
@@ -5454,6 +5526,14 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color rgb="FFC00000"/>
       <name val="Calibri"/>
       <charset val="134"/>
@@ -5489,14 +5569,6 @@
       <i/>
       <sz val="11"/>
       <color rgb="FF00B050"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -5834,16 +5906,13 @@
     <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -5852,119 +5921,122 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -6025,9 +6097,6 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -6044,6 +6113,21 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -6592,20 +6676,20 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultColWidth="8.88571428571429" defaultRowHeight="15" outlineLevelRow="6" outlineLevelCol="2"/>
+  <sheetFormatPr defaultColWidth="8.88181818181818" defaultRowHeight="14.5" outlineLevelRow="6" outlineLevelCol="2"/>
   <cols>
-    <col min="1" max="1" width="8.88571428571429" style="27"/>
-    <col min="2" max="2" width="35.2190476190476" customWidth="1"/>
-    <col min="3" max="3" width="92.6666666666667" customWidth="1"/>
+    <col min="1" max="1" width="8.88181818181818" style="31"/>
+    <col min="2" max="2" width="35.2181818181818" customWidth="1"/>
+    <col min="3" max="3" width="92.6636363636364" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:2">
-      <c r="B1" s="28" t="s">
+      <c r="B1" s="32" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:3">
-      <c r="A3" s="27">
+      <c r="A3" s="31">
         <v>1</v>
       </c>
       <c r="B3" s="5" t="s">
@@ -6616,7 +6700,7 @@
       </c>
     </row>
     <row r="4" spans="1:3">
-      <c r="A4" s="27">
+      <c r="A4" s="31">
         <v>2</v>
       </c>
       <c r="B4" s="9" t="s">
@@ -6627,7 +6711,7 @@
       </c>
     </row>
     <row r="5" spans="1:3">
-      <c r="A5" s="27">
+      <c r="A5" s="31">
         <v>3</v>
       </c>
       <c r="B5" s="15" t="s">
@@ -6638,10 +6722,10 @@
       </c>
     </row>
     <row r="6" spans="1:3">
-      <c r="A6" s="27">
+      <c r="A6" s="31">
         <v>4</v>
       </c>
-      <c r="B6" s="26" t="s">
+      <c r="B6" s="25" t="s">
         <v>3</v>
       </c>
       <c r="C6" t="s">
@@ -6649,10 +6733,10 @@
       </c>
     </row>
     <row r="7" spans="1:3">
-      <c r="A7" s="27">
+      <c r="A7" s="31">
         <v>5</v>
       </c>
-      <c r="B7" s="29" t="s">
+      <c r="B7" s="33" t="s">
         <v>3</v>
       </c>
       <c r="C7" t="s">
@@ -6669,14 +6753,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F21"/>
-  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9.14545454545454" defaultRowHeight="14.5" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="14.7142857142857" customWidth="1"/>
-    <col min="2" max="2" width="33.5714285714286" customWidth="1"/>
-    <col min="3" max="3" width="49.6666666666667" customWidth="1"/>
-    <col min="4" max="4" width="56.552380952381" customWidth="1"/>
-    <col min="5" max="5" width="53.2857142857143" customWidth="1"/>
-    <col min="6" max="6" width="47.5714285714286" customWidth="1"/>
+    <col min="1" max="1" width="14.7181818181818" customWidth="1"/>
+    <col min="2" max="2" width="33.5727272727273" customWidth="1"/>
+    <col min="3" max="3" width="49.6636363636364" customWidth="1"/>
+    <col min="4" max="4" width="56.5545454545455" customWidth="1"/>
+    <col min="5" max="5" width="53.2818181818182" customWidth="1"/>
+    <col min="6" max="6" width="47.5727272727273" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" spans="1:6">
@@ -6693,18 +6777,18 @@
         <v>11</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
     </row>
     <row r="2" ht="33" customHeight="1" spans="1:6">
       <c r="A2" s="1" t="s">
-        <v>422</v>
+        <v>47</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="3"/>
@@ -6716,10 +6800,10 @@
         <v>14</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="4" ht="60" spans="2:6">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="4" ht="43.5" spans="2:6">
       <c r="B4" s="5" t="s">
         <v>16</v>
       </c>
@@ -6727,7 +6811,7 @@
         <v>17</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="F4" s="7"/>
     </row>
@@ -6736,142 +6820,142 @@
         <v>19</v>
       </c>
       <c r="C5" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="D5"/>
       <c r="E5" s="8"/>
     </row>
-    <row r="6" customFormat="1" ht="30" spans="2:6">
+    <row r="6" customFormat="1" ht="29" spans="2:6">
       <c r="B6" s="5" t="s">
         <v>22</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="D6"/>
       <c r="E6" s="4" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="F6" s="9" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
     </row>
     <row r="7" spans="2:6">
       <c r="B7" s="5" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="D7" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="E7" s="11"/>
       <c r="F7" s="4"/>
     </row>
-    <row r="8" ht="120" spans="2:5">
+    <row r="8" ht="116" spans="2:5">
       <c r="B8" s="4" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="E8" s="13" t="s">
-        <v>432</v>
-      </c>
-    </row>
-    <row r="9" ht="60" spans="2:5">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="9" ht="58" spans="2:5">
       <c r="B9" s="4" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="D9" s="12"/>
       <c r="E9" s="4"/>
     </row>
     <row r="10" spans="2:5">
       <c r="B10" s="4" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="D10" s="12"/>
       <c r="E10" s="4"/>
     </row>
     <row r="11" spans="2:5">
       <c r="B11" s="4" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="D11" s="12"/>
       <c r="E11" s="4"/>
     </row>
     <row r="12" spans="2:5">
       <c r="B12" s="4" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="D12" s="12"/>
       <c r="E12" s="4"/>
     </row>
     <row r="13" spans="2:5">
       <c r="B13" s="4" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="D13" s="12"/>
       <c r="E13" s="4"/>
     </row>
     <row r="14" spans="2:5">
       <c r="B14" s="4" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="D14" s="12"/>
       <c r="E14" s="4"/>
     </row>
     <row r="15" spans="2:5">
       <c r="B15" s="4" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="D15" s="12"/>
       <c r="E15" s="4"/>
     </row>
     <row r="16" spans="2:6">
       <c r="B16" s="4" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="D16" s="14" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="E16" s="8"/>
       <c r="F16" s="4"/>
     </row>
     <row r="17" ht="84" customHeight="1" spans="2:6">
       <c r="B17" s="4" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="D17" s="14"/>
       <c r="E17" s="8"/>
@@ -6908,15 +6992,15 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F21"/>
-  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelCol="5"/>
+  <dimension ref="A1:G23"/>
+  <sheetFormatPr defaultColWidth="9.14545454545454" defaultRowHeight="14.5" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="14.7142857142857" customWidth="1"/>
-    <col min="2" max="2" width="28.3333333333333" customWidth="1"/>
-    <col min="3" max="3" width="66.2857142857143" customWidth="1"/>
-    <col min="4" max="4" width="46.2190476190476" customWidth="1"/>
-    <col min="5" max="5" width="61.2857142857143" customWidth="1"/>
-    <col min="6" max="6" width="46.2857142857143" customWidth="1"/>
+    <col min="1" max="1" width="14.7181818181818" customWidth="1"/>
+    <col min="2" max="2" width="28.3363636363636" customWidth="1"/>
+    <col min="3" max="3" width="65.4545454545455" customWidth="1"/>
+    <col min="4" max="4" width="46.2181818181818" customWidth="1"/>
+    <col min="5" max="5" width="61.2818181818182" customWidth="1"/>
+    <col min="6" max="6" width="46.2818181818182" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" spans="1:6">
@@ -6965,102 +7049,105 @@
         <v>18</v>
       </c>
     </row>
-    <row r="5" ht="90" spans="2:4">
-      <c r="B5" t="s">
+    <row r="5" s="26" customFormat="1" ht="61" customHeight="1" spans="1:4">
+      <c r="A5" s="27"/>
+      <c r="B5" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="28" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="6" spans="2:4">
-      <c r="B6" t="s">
+    <row r="6" s="26" customFormat="1" ht="49" customHeight="1" spans="1:4">
+      <c r="A6" s="27"/>
+      <c r="B6" s="27" t="s">
         <v>22</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C6" s="27" t="s">
         <v>23</v>
       </c>
-      <c r="D6" s="4"/>
-    </row>
-    <row r="7" spans="2:4">
-      <c r="B7" t="s">
+      <c r="D6" s="28"/>
+    </row>
+    <row r="7" s="26" customFormat="1" ht="86" customHeight="1" spans="1:4">
+      <c r="A7" s="27"/>
+      <c r="B7" s="27" t="s">
         <v>24</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C7" s="29" t="s">
         <v>25</v>
       </c>
-      <c r="D7" s="4"/>
-    </row>
-    <row r="8" spans="2:3">
+      <c r="D7" s="28"/>
+    </row>
+    <row r="8" spans="2:4">
       <c r="B8" t="s">
         <v>26</v>
       </c>
       <c r="C8" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="9" ht="30" spans="2:3">
+      <c r="D8" s="4"/>
+    </row>
+    <row r="9" spans="2:3">
       <c r="B9" t="s">
         <v>28</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="C9" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="14" spans="1:1">
-      <c r="A14" s="2" t="s">
+    <row r="10" ht="29" spans="2:3">
+      <c r="B10" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="15" spans="2:3">
-      <c r="B15" t="s">
+      <c r="C10" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="C15" t="s">
+    </row>
+    <row r="15" spans="1:1">
+      <c r="A15" s="2" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="16" ht="75" spans="2:3">
+    <row r="16" spans="2:3">
       <c r="B16" t="s">
         <v>33</v>
       </c>
-      <c r="C16" s="10" t="s">
+      <c r="C16" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="17" spans="2:3">
+    <row r="17" ht="72.5" spans="2:3">
       <c r="B17" t="s">
         <v>35</v>
       </c>
-      <c r="C17" t="s">
+      <c r="C17" s="10" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="18" ht="75" spans="2:5">
+    <row r="18" spans="2:3">
       <c r="B18" t="s">
         <v>37</v>
       </c>
       <c r="C18" t="s">
         <v>38</v>
       </c>
-      <c r="E18" s="18" t="s">
+    </row>
+    <row r="19" ht="72.5" spans="2:5">
+      <c r="B19" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="19" ht="45" spans="2:5">
-      <c r="B19" s="4" t="s">
+      <c r="C19" t="s">
         <v>40</v>
       </c>
-      <c r="C19" s="10" t="s">
+      <c r="E19" s="18" t="s">
         <v>41</v>
       </c>
-      <c r="E19" s="10"/>
-    </row>
-    <row r="20" ht="60" spans="2:5">
-      <c r="B20" t="s">
+    </row>
+    <row r="20" ht="29" spans="2:5">
+      <c r="B20" s="4" t="s">
         <v>42</v>
       </c>
       <c r="C20" s="10" t="s">
@@ -7068,13 +7155,37 @@
       </c>
       <c r="E20" s="10"/>
     </row>
-    <row r="21" ht="30" spans="2:5">
-      <c r="B21" s="4" t="s">
+    <row r="21" ht="58" spans="2:5">
+      <c r="B21" t="s">
         <v>44</v>
       </c>
-      <c r="E21" s="8"/>
+      <c r="C21" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="E21" s="10"/>
+    </row>
+    <row r="22" ht="29" spans="2:5">
+      <c r="B22" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="E22" s="8"/>
+    </row>
+    <row r="23" ht="101.5" spans="2:7">
+      <c r="B23" s="30" t="s">
+        <v>47</v>
+      </c>
+      <c r="C23" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="D23" s="7"/>
+      <c r="E23" s="7"/>
+      <c r="F23" s="7"/>
+      <c r="G23" s="7"/>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="D5:D7"/>
+  </mergeCells>
   <hyperlinks>
     <hyperlink ref="C6" r:id="rId1" display="&quot;http://shinny.org/us/ny/hrsn/StructureDefinition/SHINNYBundleProfile&quot;"/>
   </hyperlinks>
@@ -7087,13 +7198,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F68"/>
-  <sheetFormatPr defaultColWidth="8.88571428571429" defaultRowHeight="15" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="8.88181818181818" defaultRowHeight="14.5" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="14.7142857142857" customWidth="1"/>
-    <col min="2" max="2" width="41.7809523809524" style="4" customWidth="1"/>
-    <col min="3" max="3" width="63.8857142857143" style="4" customWidth="1"/>
-    <col min="4" max="4" width="81.2857142857143" style="4" customWidth="1"/>
-    <col min="5" max="5" width="48.4285714285714" style="4" customWidth="1"/>
+    <col min="1" max="1" width="14.7181818181818" customWidth="1"/>
+    <col min="2" max="2" width="41.7818181818182" style="4" customWidth="1"/>
+    <col min="3" max="3" width="63.8818181818182" style="4" customWidth="1"/>
+    <col min="4" max="4" width="81.2818181818182" style="4" customWidth="1"/>
+    <col min="5" max="5" width="48.4272727272727" style="4" customWidth="1"/>
     <col min="6" max="6" width="45" customWidth="1"/>
   </cols>
   <sheetData>
@@ -7101,25 +7212,25 @@
       <c r="A1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="24" t="s">
+      <c r="B1" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="C1" s="24" t="s">
+      <c r="C1" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="D1" s="24" t="s">
+      <c r="D1" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="E1" s="24" t="s">
-        <v>45</v>
-      </c>
-      <c r="F1" s="24" t="s">
-        <v>46</v>
+      <c r="E1" s="23" t="s">
+        <v>49</v>
+      </c>
+      <c r="F1" s="23" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -7128,7 +7239,7 @@
         <v>14</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
     </row>
     <row r="4" spans="2:4">
@@ -7139,7 +7250,7 @@
         <v>17</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -7148,7 +7259,7 @@
         <v>19</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
     </row>
     <row r="6" spans="2:3">
@@ -7156,658 +7267,658 @@
         <v>22</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="7" ht="30" spans="2:4">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="7" ht="29" spans="2:4">
       <c r="B7" s="4" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="8" ht="60" spans="2:5">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="8" ht="58" spans="2:5">
       <c r="B8" s="4" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="D8" s="10" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
     </row>
     <row r="9" spans="2:4">
       <c r="B9" s="10" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="D9" s="10"/>
     </row>
     <row r="10" spans="2:4">
       <c r="B10" s="4" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
     </row>
     <row r="11" spans="2:4">
       <c r="B11" s="17" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="D11" s="10" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
     </row>
     <row r="12" spans="2:4">
       <c r="B12" s="17" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="D12" s="10" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="13" ht="60" spans="2:4">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="13" ht="58" spans="2:4">
       <c r="B13" s="4" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="D13" s="10" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="14" ht="30" spans="2:4">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="14" ht="29" spans="2:4">
       <c r="B14" s="4" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="15" ht="30" spans="2:4">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="15" ht="29" spans="2:4">
       <c r="B15" s="4" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
     </row>
     <row r="16" spans="2:4">
       <c r="B16" s="17" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="D16" s="10" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="17" ht="120" spans="2:5">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="17" ht="116" spans="2:5">
       <c r="B17" s="4" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="D17" s="12" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="E17" s="13" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="18" ht="60" spans="2:4">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="18" ht="58" spans="2:4">
       <c r="B18" s="4" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="D18" s="12"/>
     </row>
     <row r="19" spans="2:4">
       <c r="B19" s="4" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="D19" s="12"/>
     </row>
     <row r="20" spans="2:4">
       <c r="B20" s="4" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="D20" s="12"/>
     </row>
     <row r="21" spans="2:4">
       <c r="B21" s="4" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="D21" s="12"/>
     </row>
     <row r="22" spans="2:4">
       <c r="B22" s="4" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="D22" s="12"/>
     </row>
     <row r="23" spans="2:4">
       <c r="B23" s="4" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="D23" s="12"/>
     </row>
     <row r="24" ht="48" customHeight="1" spans="2:5">
       <c r="B24" s="4" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
     </row>
     <row r="25" spans="2:3">
       <c r="B25" s="4" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
     </row>
     <row r="26" ht="198" customHeight="1" spans="2:5">
       <c r="B26" s="4" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="E26" s="13" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="27" ht="45" spans="2:5">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="27" ht="43.5" spans="2:5">
       <c r="B27" s="4" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="D27" s="12" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="E27" s="8" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="28" ht="30" spans="2:5">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="28" spans="2:5">
       <c r="B28" s="4" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="D28" s="14"/>
       <c r="E28" s="8"/>
     </row>
     <row r="29" spans="2:5">
       <c r="B29" s="4" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="D29" s="14"/>
       <c r="E29" s="8"/>
     </row>
-    <row r="30" ht="30" spans="2:5">
+    <row r="30" spans="2:5">
       <c r="B30" s="4" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="D30" s="14"/>
       <c r="E30" s="8"/>
     </row>
     <row r="31" spans="2:5">
       <c r="B31" s="4" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="D31" s="14"/>
       <c r="E31" s="8"/>
     </row>
-    <row r="32" ht="45" spans="2:5">
+    <row r="32" ht="43.5" spans="2:5">
       <c r="B32" s="4" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="D32" s="14" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="E32" s="8" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="33" ht="30" spans="2:4">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="33" spans="2:4">
       <c r="B33" s="4" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="D33" s="14"/>
     </row>
     <row r="34" spans="2:4">
       <c r="B34" s="4" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="D34" s="14"/>
     </row>
-    <row r="35" ht="30" spans="2:4">
+    <row r="35" spans="2:4">
       <c r="B35" s="4" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="D35" s="14"/>
     </row>
     <row r="36" spans="2:4">
       <c r="B36" s="4" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="D36" s="14"/>
     </row>
     <row r="37" spans="2:4">
       <c r="B37" s="4" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="D37" s="14" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="38" ht="45" spans="2:5">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="38" ht="43.5" spans="2:5">
       <c r="B38" s="4" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="D38" s="14"/>
-      <c r="E38" s="30" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="39" ht="120" spans="2:6">
+      <c r="E38" s="34" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="39" ht="116" spans="2:6">
       <c r="B39" s="4" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="D39" s="10" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="F39" s="4" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="40" ht="120" spans="2:6">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="40" ht="116" spans="2:6">
       <c r="B40" s="4" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="D40" s="10" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="F40" s="4" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
     </row>
     <row r="41" spans="2:4">
       <c r="B41" s="17" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="D41" s="10"/>
     </row>
     <row r="42" spans="2:4">
       <c r="B42" s="17" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="D42" s="10"/>
     </row>
     <row r="43" spans="2:4">
       <c r="B43" s="17" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="D43" s="10"/>
     </row>
     <row r="44" spans="2:4">
       <c r="B44" s="4" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="D44" s="10"/>
     </row>
-    <row r="45" ht="195" spans="2:5">
+    <row r="45" ht="188.5" spans="2:5">
       <c r="B45" s="17" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="C45" s="10" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="D45" s="10" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="E45" s="18" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="46" ht="195" spans="2:5">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="46" ht="188.5" spans="2:5">
       <c r="B46" s="17" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="C46" s="18" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="D46" s="10" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="E46" s="8" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="47" ht="195" spans="2:5">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="47" ht="188.5" spans="2:5">
       <c r="B47" s="17" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="D47" s="10" t="s">
-        <v>149</v>
-      </c>
-      <c r="E47" s="25"/>
+        <v>153</v>
+      </c>
+      <c r="E47" s="24"/>
     </row>
     <row r="48" customFormat="1" spans="2:5">
       <c r="B48" s="4" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="D48" s="10"/>
       <c r="E48" s="4"/>
     </row>
     <row r="49" customFormat="1" spans="2:5">
       <c r="B49" s="4" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="D49" s="10"/>
       <c r="E49" s="4"/>
     </row>
     <row r="50" customFormat="1" spans="2:5">
       <c r="B50" s="4" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="D50" s="10"/>
       <c r="E50" s="4"/>
     </row>
     <row r="51" customFormat="1" spans="2:5">
       <c r="B51" s="4" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="D51" s="10"/>
       <c r="E51" s="4"/>
     </row>
-    <row r="52" ht="150" spans="2:5">
+    <row r="52" ht="145" spans="2:5">
       <c r="B52" s="10" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="C52" s="18" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="D52" s="10" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="E52" s="8" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
     </row>
     <row r="53" spans="2:5">
       <c r="B53" s="4" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="C53" s="10" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="D53" s="10"/>
       <c r="E53" s="8"/>
     </row>
     <row r="54" customFormat="1" spans="2:5">
       <c r="B54" s="4" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="C54" s="4" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="D54" s="10"/>
       <c r="E54" s="8"/>
     </row>
     <row r="55" customFormat="1" spans="2:5">
       <c r="B55" s="4" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="D55" s="10"/>
       <c r="E55" s="8"/>
     </row>
     <row r="56" customFormat="1" spans="2:5">
       <c r="B56" s="4" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="C56" s="4" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="D56" s="10"/>
       <c r="E56" s="8"/>
     </row>
     <row r="57" customFormat="1" spans="2:5">
       <c r="B57" s="4" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="D57" s="10"/>
       <c r="E57" s="8"/>
     </row>
     <row r="58" spans="2:5">
       <c r="B58" s="4" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="C58" s="10" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="D58" s="10"/>
       <c r="E58" s="8"/>
     </row>
-    <row r="59" ht="180" spans="2:5">
+    <row r="59" ht="174" spans="2:5">
       <c r="B59" s="10" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="C59" s="10" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="D59" s="10" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="E59" s="18" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="60" ht="255" spans="2:6">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="60" ht="246.5" spans="2:6">
       <c r="B60" s="4" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="D60" s="10" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="F60" s="4" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
     </row>
     <row r="61" spans="2:6">
       <c r="B61" s="4" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="D61" s="10"/>
       <c r="F61" s="4"/>
     </row>
     <row r="62" spans="2:6">
       <c r="B62" s="4" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="C62" s="4" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="D62" s="10"/>
       <c r="F62" s="4"/>
     </row>
-    <row r="63" ht="210" spans="2:6">
+    <row r="63" ht="203" spans="2:6">
       <c r="B63" s="4" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="D63" s="10"/>
       <c r="E63" s="13" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="F63" s="4"/>
     </row>
     <row r="64" ht="56" customHeight="1" spans="2:6">
       <c r="B64" s="4" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="D64" s="12" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="F64" s="4" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
     </row>
     <row r="65" ht="43" customHeight="1" spans="2:4">
       <c r="B65" s="4" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="C65" s="4" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="D65" s="12"/>
     </row>
     <row r="66" ht="40" customHeight="1" spans="2:4">
       <c r="B66" s="4" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="C66" s="4" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="D66" s="12"/>
     </row>
     <row r="67" spans="2:4">
       <c r="B67" s="4" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="C67" s="4" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="D67" s="14" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
     </row>
     <row r="68" ht="43" customHeight="1" spans="2:4">
       <c r="B68" s="4" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="C68" s="4" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="D68" s="14"/>
     </row>
@@ -7830,14 +7941,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:G22"/>
-  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelCol="6"/>
+  <sheetFormatPr defaultColWidth="9.14545454545454" defaultRowHeight="14.5" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="14.7142857142857" customWidth="1"/>
-    <col min="2" max="2" width="30.8571428571429" customWidth="1"/>
-    <col min="3" max="3" width="63.4285714285714" customWidth="1"/>
-    <col min="4" max="4" width="70.7142857142857" customWidth="1"/>
-    <col min="5" max="5" width="52.4285714285714" customWidth="1"/>
-    <col min="6" max="6" width="57.5714285714286" customWidth="1"/>
+    <col min="1" max="1" width="14.7181818181818" customWidth="1"/>
+    <col min="2" max="2" width="30.8545454545455" customWidth="1"/>
+    <col min="3" max="3" width="63.4272727272727" customWidth="1"/>
+    <col min="4" max="4" width="70.7181818181818" customWidth="1"/>
+    <col min="5" max="5" width="52.4272727272727" customWidth="1"/>
+    <col min="6" max="6" width="57.5727272727273" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" spans="1:6">
@@ -7854,18 +7965,18 @@
         <v>11</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
     </row>
     <row r="2" ht="33" customHeight="1" spans="1:5">
       <c r="A2" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="3"/>
@@ -7876,10 +7987,10 @@
         <v>14</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="4" ht="60" spans="2:7">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="4" ht="58" spans="2:7">
       <c r="B4" s="5" t="s">
         <v>16</v>
       </c>
@@ -7887,7 +7998,7 @@
         <v>17</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="F4" s="7"/>
       <c r="G4" s="7"/>
@@ -7897,7 +8008,7 @@
         <v>19</v>
       </c>
       <c r="C5" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="E5" s="8"/>
     </row>
@@ -7906,210 +8017,210 @@
         <v>22</v>
       </c>
       <c r="C6" t="s">
-        <v>197</v>
-      </c>
-      <c r="E6" s="26"/>
-    </row>
-    <row r="7" ht="120" spans="2:6">
+        <v>201</v>
+      </c>
+      <c r="E6" s="25"/>
+    </row>
+    <row r="7" ht="116" spans="2:6">
       <c r="B7" s="5" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="D7" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="E7" s="11" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="F7" s="4"/>
     </row>
     <row r="8" ht="94" customHeight="1" spans="2:5">
       <c r="B8" s="5" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="C8" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="D8" s="10" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
     </row>
     <row r="9" customFormat="1" spans="2:5">
       <c r="B9" s="5" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="C9" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="D9" s="10"/>
       <c r="E9" s="8" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
     </row>
     <row r="10" spans="2:5">
       <c r="B10" s="5" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="C10" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="D10" s="10"/>
       <c r="E10" s="8" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="11" ht="225" spans="2:5">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="11" ht="203" spans="2:5">
       <c r="B11" s="5" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="C11" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="D11" s="10" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
     </row>
     <row r="12" spans="2:5">
       <c r="B12" s="5" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="C12" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="E12" s="8" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
     </row>
     <row r="13" spans="2:5">
       <c r="B13" s="5" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="C13" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="14" ht="30" spans="2:5">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="14" ht="29" spans="2:5">
       <c r="B14" s="5" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="C14" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="D14" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="E14" s="8" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="15" ht="45" spans="2:5">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="15" ht="43.5" spans="2:5">
       <c r="B15" s="5" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="C15" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="E15" s="8" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="16" ht="45" spans="2:5">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="16" ht="43.5" spans="2:5">
       <c r="B16" s="5" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="C16" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="E16" s="8"/>
     </row>
-    <row r="17" ht="45" spans="2:5">
+    <row r="17" ht="43.5" spans="2:5">
       <c r="B17" s="5" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="C17" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="E17" s="8"/>
     </row>
-    <row r="18" ht="45" spans="2:5">
+    <row r="18" ht="43.5" spans="2:5">
       <c r="B18" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="C18" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="D18" s="10" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="E18" s="8" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="19" ht="60" spans="2:5">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="19" ht="58" spans="2:5">
       <c r="B19" s="5" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="C19" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="E19" s="8" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
     </row>
     <row r="20" customFormat="1" spans="2:5">
       <c r="B20" s="5" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="C20" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="D20" s="4"/>
       <c r="E20" s="8" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
     </row>
     <row r="21" customFormat="1" spans="2:6">
       <c r="B21" s="4" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="D21" s="14" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="E21" s="8"/>
       <c r="F21" s="4"/>
     </row>
     <row r="22" customFormat="1" ht="60" customHeight="1" spans="2:6">
       <c r="B22" s="4" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="D22" s="14"/>
       <c r="E22" s="8"/>
@@ -8130,14 +8241,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F26"/>
-  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9.14545454545454" defaultRowHeight="14.5" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="14.7142857142857" customWidth="1"/>
-    <col min="2" max="2" width="35.1428571428571" customWidth="1"/>
-    <col min="3" max="3" width="42.2857142857143" style="4" customWidth="1"/>
-    <col min="4" max="4" width="73.5714285714286" customWidth="1"/>
+    <col min="1" max="1" width="14.7181818181818" customWidth="1"/>
+    <col min="2" max="2" width="35.1454545454545" customWidth="1"/>
+    <col min="3" max="3" width="42.2818181818182" style="4" customWidth="1"/>
+    <col min="4" max="4" width="73.5727272727273" customWidth="1"/>
     <col min="5" max="5" width="53" customWidth="1"/>
-    <col min="6" max="6" width="51.7142857142857" customWidth="1"/>
+    <col min="6" max="6" width="51.7181818181818" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" spans="1:6">
@@ -8147,7 +8258,7 @@
       <c r="B1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C1" s="24" t="s">
+      <c r="C1" s="23" t="s">
         <v>10</v>
       </c>
       <c r="D1" s="2" t="s">
@@ -8162,10 +8273,10 @@
     </row>
     <row r="2" ht="35" customHeight="1" spans="1:5">
       <c r="A2" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="3"/>
@@ -8176,10 +8287,10 @@
         <v>14</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="4" ht="75" spans="1:5">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="4" ht="72.5" spans="1:5">
       <c r="A4" s="1"/>
       <c r="B4" s="5" t="s">
         <v>16</v>
@@ -8188,10 +8299,10 @@
         <v>17</v>
       </c>
       <c r="D4" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
     </row>
     <row r="5" customFormat="1" spans="1:6">
@@ -8200,226 +8311,226 @@
         <v>19</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="D5" s="4"/>
       <c r="E5" s="4"/>
       <c r="F5" s="4"/>
     </row>
-    <row r="6" customFormat="1" ht="30" spans="2:6">
+    <row r="6" customFormat="1" ht="29" spans="2:6">
       <c r="B6" s="17" t="s">
         <v>22</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="D6" s="4"/>
       <c r="E6" s="4"/>
       <c r="F6" s="4"/>
     </row>
-    <row r="7" ht="165" spans="2:5">
+    <row r="7" ht="159.5" spans="2:5">
       <c r="B7" s="5" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="C7" s="18" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="D7" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="E7" s="11" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
     </row>
     <row r="8" ht="71" customHeight="1" spans="2:5">
       <c r="B8" s="5" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="D8" s="10" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="E8" s="9"/>
     </row>
-    <row r="9" ht="30" spans="2:5">
+    <row r="9" ht="29" spans="2:5">
       <c r="B9" s="5" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="D9" s="10"/>
-      <c r="E9" s="25"/>
+      <c r="E9" s="24"/>
     </row>
     <row r="10" spans="2:5">
       <c r="B10" s="5" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="D10" s="10"/>
       <c r="E10" s="9"/>
     </row>
-    <row r="11" ht="30" spans="2:4">
+    <row r="11" ht="29" spans="2:4">
       <c r="B11" s="5" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="C11" s="18" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="D11" s="12" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="12" ht="60" spans="2:5">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="12" ht="58" spans="2:5">
       <c r="B12" s="5" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D12" s="12"/>
       <c r="E12" s="13" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
     </row>
     <row r="13" ht="33" customHeight="1" spans="2:4">
       <c r="B13" s="5" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="D13" s="12"/>
     </row>
     <row r="14" customFormat="1" spans="2:3">
       <c r="B14" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="15" customFormat="1" ht="60" spans="2:4">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="15" customFormat="1" ht="58" spans="2:4">
       <c r="B15" s="5" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="C15" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="16" customFormat="1" ht="30" spans="2:3">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="16" customFormat="1" ht="29" spans="2:3">
       <c r="B16" s="5" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="17" ht="60" spans="2:4">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="17" ht="58" spans="2:4">
       <c r="B17" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="D17" s="10" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
     </row>
     <row r="18" spans="2:3">
       <c r="B18" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="19" ht="45" spans="2:5">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="19" ht="43.5" spans="2:5">
       <c r="B19" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="D19" s="10" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
     </row>
     <row r="20" spans="2:5">
       <c r="B20" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="E20" s="15"/>
     </row>
     <row r="21" ht="409.5" spans="2:5">
       <c r="B21" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="E21" s="13" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="22" ht="60" spans="2:5">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="22" ht="58" spans="2:5">
       <c r="B22" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>284</v>
-      </c>
-      <c r="E22" s="23"/>
+        <v>288</v>
+      </c>
+      <c r="E22" s="22"/>
     </row>
     <row r="23" ht="66" customHeight="1" spans="2:5">
       <c r="B23" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="C23" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="D23" s="10" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="E23" s="4"/>
     </row>
     <row r="24" customFormat="1" spans="2:5">
       <c r="B24" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="D24" s="10"/>
       <c r="E24" s="4"/>
     </row>
     <row r="25" customFormat="1" spans="2:4">
       <c r="B25" s="4" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="D25" s="14" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
     </row>
     <row r="26" customFormat="1" ht="46" customHeight="1" spans="2:4">
       <c r="B26" s="4" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="D26" s="14"/>
     </row>
@@ -8441,14 +8552,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F32"/>
-  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9.14545454545454" defaultRowHeight="14.5" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="14.7142857142857" customWidth="1"/>
-    <col min="2" max="2" width="27.3333333333333" customWidth="1"/>
-    <col min="3" max="3" width="50.8857142857143" customWidth="1"/>
-    <col min="4" max="4" width="72.8571428571429" customWidth="1"/>
-    <col min="5" max="5" width="46.4285714285714" customWidth="1"/>
-    <col min="6" max="6" width="45.7142857142857" customWidth="1"/>
+    <col min="1" max="1" width="14.7181818181818" customWidth="1"/>
+    <col min="2" max="2" width="27.3363636363636" customWidth="1"/>
+    <col min="3" max="3" width="50.8818181818182" customWidth="1"/>
+    <col min="4" max="4" width="72.8545454545455" customWidth="1"/>
+    <col min="5" max="5" width="46.4272727272727" customWidth="1"/>
+    <col min="6" max="6" width="45.7181818181818" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" spans="1:6">
@@ -8465,15 +8576,15 @@
         <v>11</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="3" customFormat="1" spans="2:3">
@@ -8481,7 +8592,7 @@
         <v>14</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
     </row>
     <row r="4" spans="2:3">
@@ -8498,20 +8609,20 @@
         <v>19</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="D5" s="4"/>
       <c r="E5" s="4" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="F5" s="4"/>
     </row>
-    <row r="6" customFormat="1" ht="30" spans="2:6">
+    <row r="6" customFormat="1" ht="29" spans="2:6">
       <c r="B6" s="4" t="s">
         <v>22</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="D6" s="4"/>
       <c r="E6" s="4"/>
@@ -8519,270 +8630,270 @@
     </row>
     <row r="7" spans="2:6">
       <c r="B7" s="5" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="D7" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="F7" s="9" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
     </row>
     <row r="8" ht="63" customHeight="1" spans="2:6">
       <c r="B8" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="C8" s="18" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="D8" s="10" t="s">
-        <v>301</v>
-      </c>
-      <c r="F8" s="20" t="s">
-        <v>302</v>
+        <v>305</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>306</v>
       </c>
     </row>
     <row r="9" spans="2:5">
       <c r="B9" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="D9" s="10"/>
       <c r="E9" s="8"/>
     </row>
-    <row r="10" ht="30" spans="2:5">
+    <row r="10" ht="29" spans="2:5">
       <c r="B10" s="4" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="D10" s="10"/>
       <c r="E10" s="8"/>
     </row>
-    <row r="11" ht="30" spans="2:5">
+    <row r="11" ht="29" spans="2:5">
       <c r="B11" s="4" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="D11" s="10"/>
       <c r="E11" s="8"/>
     </row>
-    <row r="12" ht="30" spans="2:5">
+    <row r="12" ht="29" spans="2:5">
       <c r="B12" s="4" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="D12" s="10"/>
       <c r="E12" s="8"/>
     </row>
     <row r="13" customFormat="1" ht="66" customHeight="1" spans="2:6">
       <c r="B13" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="C13" s="18" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="D13" s="10" t="s">
-        <v>312</v>
-      </c>
-      <c r="F13" s="20" t="s">
-        <v>302</v>
+        <v>316</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>306</v>
       </c>
     </row>
     <row r="14" customFormat="1" spans="2:5">
       <c r="B14" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="D14" s="10"/>
-      <c r="E14" s="23"/>
-    </row>
-    <row r="15" customFormat="1" ht="30" spans="2:5">
+      <c r="E14" s="22"/>
+    </row>
+    <row r="15" customFormat="1" ht="29" spans="2:5">
       <c r="B15" s="4" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="D15" s="10"/>
-      <c r="E15" s="23"/>
-    </row>
-    <row r="16" customFormat="1" ht="30" spans="2:5">
+      <c r="E15" s="22"/>
+    </row>
+    <row r="16" customFormat="1" ht="29" spans="2:5">
       <c r="B16" s="4" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="D16" s="10"/>
       <c r="E16" s="4"/>
     </row>
-    <row r="17" customFormat="1" ht="30" spans="2:4">
+    <row r="17" customFormat="1" ht="29" spans="2:4">
       <c r="B17" s="4" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="D17" s="10"/>
     </row>
-    <row r="18" ht="60" spans="2:5">
+    <row r="18" ht="58" spans="2:5">
       <c r="B18" s="5" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="C18" s="18" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="D18" s="10" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
     </row>
     <row r="19" ht="93" customHeight="1" spans="2:6">
       <c r="B19" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="D19" s="10" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="F19" s="8" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
     </row>
     <row r="20" customFormat="1" spans="2:6">
       <c r="B20" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="C20" s="4"/>
       <c r="D20" s="10"/>
       <c r="F20" s="8" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
     </row>
     <row r="21" customFormat="1" ht="50" customHeight="1" spans="2:6">
       <c r="B21" s="4" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="C21" s="4"/>
       <c r="D21" s="10" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="F21" s="4"/>
     </row>
-    <row r="22" customFormat="1" ht="30" spans="2:6">
+    <row r="22" customFormat="1" ht="29" spans="2:6">
       <c r="B22" s="4" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="D22" s="10"/>
       <c r="F22" s="4"/>
     </row>
-    <row r="23" customFormat="1" ht="195" spans="2:6">
+    <row r="23" customFormat="1" ht="188.5" spans="2:6">
       <c r="B23" s="4" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="D23" s="10"/>
       <c r="E23" s="13" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="F23" s="4"/>
     </row>
-    <row r="24" customFormat="1" ht="120" spans="2:6">
+    <row r="24" customFormat="1" ht="116" spans="2:6">
       <c r="B24" s="4" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="D24" s="10" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="E24" s="4"/>
       <c r="F24" s="4"/>
     </row>
-    <row r="25" customFormat="1" ht="30" spans="2:6">
+    <row r="25" customFormat="1" ht="29" spans="2:6">
       <c r="B25" s="4" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="D25" s="10"/>
       <c r="E25" s="4"/>
       <c r="F25" s="4"/>
     </row>
-    <row r="26" customFormat="1" ht="30" spans="2:6">
+    <row r="26" customFormat="1" ht="29" spans="2:6">
       <c r="B26" s="4" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="D26" s="10"/>
       <c r="E26" s="4"/>
       <c r="F26" s="4"/>
     </row>
-    <row r="27" customFormat="1" ht="30" spans="2:6">
+    <row r="27" customFormat="1" ht="29" spans="2:6">
       <c r="B27" s="4" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="D27" s="10"/>
       <c r="E27" s="4"/>
       <c r="F27" s="4"/>
     </row>
-    <row r="28" customFormat="1" ht="30" spans="2:6">
+    <row r="28" customFormat="1" ht="29" spans="2:6">
       <c r="B28" s="4" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="D28" s="10"/>
       <c r="E28" s="4"/>
       <c r="F28" s="4"/>
     </row>
-    <row r="29" customFormat="1" ht="30" spans="2:6">
+    <row r="29" customFormat="1" ht="29" spans="2:6">
       <c r="B29" s="4" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="D29" s="10"/>
       <c r="E29" s="4"/>
       <c r="F29" s="4"/>
     </row>
-    <row r="30" customFormat="1" ht="30" spans="2:6">
+    <row r="30" customFormat="1" ht="29" spans="2:6">
       <c r="B30" s="4" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="D30" s="10"/>
       <c r="E30" s="4"/>
@@ -8790,21 +8901,21 @@
     </row>
     <row r="31" customFormat="1" spans="2:4">
       <c r="B31" s="4" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="D31" s="14" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
     </row>
     <row r="32" customFormat="1" ht="46" customHeight="1" spans="2:4">
       <c r="B32" s="4" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="D32" s="14"/>
     </row>
@@ -8826,13 +8937,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F21"/>
-  <sheetFormatPr defaultColWidth="8.88571428571429" defaultRowHeight="15" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="8.88181818181818" defaultRowHeight="14.5" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="14.7142857142857" customWidth="1"/>
-    <col min="2" max="2" width="33.8857142857143" customWidth="1"/>
-    <col min="3" max="3" width="46.8571428571429" customWidth="1"/>
-    <col min="4" max="4" width="57.1142857142857" customWidth="1"/>
-    <col min="5" max="5" width="54.7142857142857" customWidth="1"/>
+    <col min="1" max="1" width="14.7181818181818" customWidth="1"/>
+    <col min="2" max="2" width="33.8818181818182" customWidth="1"/>
+    <col min="3" max="3" width="46.8545454545455" customWidth="1"/>
+    <col min="4" max="4" width="57.1181818181818" customWidth="1"/>
+    <col min="5" max="5" width="54.7181818181818" customWidth="1"/>
     <col min="6" max="6" width="38" customWidth="1"/>
   </cols>
   <sheetData>
@@ -8850,15 +8961,15 @@
         <v>11</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="2" ht="45" spans="1:1">
-      <c r="A2" s="22" t="s">
-        <v>342</v>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="2" ht="43.5" spans="1:1">
+      <c r="A2" s="21" t="s">
+        <v>346</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -8867,7 +8978,7 @@
         <v>14</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -8879,7 +8990,7 @@
         <v>17</v>
       </c>
       <c r="D4" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -8888,18 +8999,18 @@
         <v>19</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="D5" s="4"/>
       <c r="E5" s="4"/>
       <c r="F5" s="4"/>
     </row>
-    <row r="6" ht="30" spans="2:6">
+    <row r="6" ht="29" spans="2:6">
       <c r="B6" s="17" t="s">
         <v>22</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="D6" s="4"/>
       <c r="E6" s="4"/>
@@ -8907,161 +9018,161 @@
     </row>
     <row r="7" spans="2:6">
       <c r="B7" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="D7" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="8" ht="150" spans="2:5">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="8" ht="145" spans="2:5">
       <c r="B8" s="5" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="D8" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="E8" s="11" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
     </row>
     <row r="9" ht="70" customHeight="1" spans="2:4">
       <c r="B9" s="5" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="D9" s="10" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="10" ht="30" spans="2:4">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="10" ht="29" spans="2:4">
       <c r="B10" s="5" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="D10" s="10"/>
     </row>
     <row r="11" spans="2:5">
       <c r="B11" s="5" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="D11" s="10"/>
       <c r="E11" s="8"/>
     </row>
-    <row r="12" ht="30" spans="2:4">
+    <row r="12" ht="29" spans="2:4">
       <c r="B12" s="5" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="D12" s="10"/>
     </row>
     <row r="13" ht="38" customHeight="1" spans="2:4">
       <c r="B13" s="4" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="D13" s="10" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="14" ht="30" spans="2:4">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="14" ht="29" spans="2:4">
       <c r="B14" s="4" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="D14" s="10"/>
     </row>
     <row r="15" ht="153" customHeight="1" spans="2:5">
       <c r="B15" s="4" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="D15" s="10"/>
       <c r="E15" s="8" t="s">
-        <v>364</v>
-      </c>
-    </row>
-    <row r="16" ht="75" spans="2:4">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="16" ht="58" spans="2:4">
       <c r="B16" s="5" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="C16" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="D16" s="10" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="17" ht="30" spans="2:3">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="17" ht="29" spans="2:3">
       <c r="B17" s="5" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="18" ht="90" spans="2:5">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="18" ht="87" spans="2:5">
       <c r="B18" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="D18" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
     </row>
     <row r="19" spans="2:6">
       <c r="B19" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="D19" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="F19" s="15" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
     </row>
     <row r="20" spans="2:4">
       <c r="B20" s="4" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="D20" s="14" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
     </row>
     <row r="21" ht="45" customHeight="1" spans="2:4">
       <c r="B21" s="4" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="D21" s="14"/>
     </row>
@@ -9080,14 +9191,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F31"/>
-  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9.14545454545454" defaultRowHeight="14.5" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="14.7142857142857" customWidth="1"/>
-    <col min="2" max="2" width="34.5714285714286" customWidth="1"/>
-    <col min="3" max="3" width="49.6666666666667" customWidth="1"/>
-    <col min="4" max="4" width="58.7142857142857" customWidth="1"/>
-    <col min="5" max="5" width="53.2857142857143" customWidth="1"/>
-    <col min="6" max="6" width="50.2857142857143" customWidth="1"/>
+    <col min="1" max="1" width="14.7181818181818" customWidth="1"/>
+    <col min="2" max="2" width="34.5727272727273" customWidth="1"/>
+    <col min="3" max="3" width="49.6636363636364" customWidth="1"/>
+    <col min="4" max="4" width="58.7181818181818" customWidth="1"/>
+    <col min="5" max="5" width="53.2818181818182" customWidth="1"/>
+    <col min="6" max="6" width="50.2818181818182" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" spans="1:6">
@@ -9104,18 +9215,18 @@
         <v>11</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
     </row>
     <row r="2" ht="17" customHeight="1" spans="1:6">
       <c r="A2" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="3"/>
@@ -9128,19 +9239,19 @@
         <v>14</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="4" ht="78" spans="1:4">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="4" ht="82.5" spans="1:4">
       <c r="A4" s="1"/>
       <c r="B4" s="5" t="s">
         <v>16</v>
       </c>
       <c r="C4" s="18" t="s">
-        <v>375</v>
-      </c>
-      <c r="D4" s="20" t="s">
-        <v>376</v>
+        <v>379</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>380</v>
       </c>
     </row>
     <row r="5" customFormat="1" spans="1:6">
@@ -9149,18 +9260,18 @@
         <v>19</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="D5" s="4"/>
       <c r="E5" s="4"/>
       <c r="F5" s="4"/>
     </row>
-    <row r="6" customFormat="1" ht="30" spans="2:6">
+    <row r="6" customFormat="1" ht="29" spans="2:6">
       <c r="B6" s="17" t="s">
         <v>22</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="D6" s="4"/>
       <c r="E6" s="4"/>
@@ -9168,268 +9279,268 @@
     </row>
     <row r="7" spans="2:6">
       <c r="B7" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="D7" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="8" ht="150" spans="2:5">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="8" ht="145" spans="2:5">
       <c r="B8" s="5" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="D8" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="E8" s="11" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
     </row>
     <row r="9" ht="139" customHeight="1" spans="2:5">
       <c r="B9" s="5" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="E9" s="18" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="10" ht="45" spans="2:5">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="10" ht="43.5" spans="2:5">
       <c r="B10" s="5" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="D10" s="6"/>
       <c r="E10" s="8" t="s">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="11" ht="210" spans="2:5">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="11" ht="203" spans="2:5">
       <c r="B11" s="5" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="D11" s="6"/>
       <c r="E11" s="11" t="s">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="12" ht="210" spans="2:5">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="12" ht="203" spans="2:5">
       <c r="B12" s="5" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="D12" s="6"/>
       <c r="E12" s="11" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
     </row>
     <row r="13" spans="2:5">
       <c r="B13" s="5" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="D13" s="6"/>
       <c r="E13" s="8" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
     </row>
     <row r="14" ht="84" customHeight="1" spans="2:5">
       <c r="B14" s="5" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="D14" s="10" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="E14" s="9"/>
     </row>
     <row r="15" spans="2:5">
       <c r="B15" s="5" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="D15" s="10"/>
       <c r="E15" s="9"/>
     </row>
     <row r="16" spans="2:5">
       <c r="B16" s="5" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="D16" s="10"/>
       <c r="E16" s="9"/>
     </row>
-    <row r="17" ht="30" spans="2:5">
+    <row r="17" ht="29" spans="2:5">
       <c r="B17" s="5" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="D17" s="10"/>
       <c r="E17" s="8" t="s">
-        <v>390</v>
-      </c>
-    </row>
-    <row r="18" ht="105" spans="2:5">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="18" ht="101.5" spans="2:5">
       <c r="B18" s="4" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="D18" s="10" t="s">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="E18" s="18" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="19" ht="30" spans="2:3">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="19" ht="29" spans="2:3">
       <c r="B19" s="4" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>394</v>
-      </c>
-    </row>
-    <row r="20" ht="30" spans="2:3">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="20" ht="29" spans="2:3">
       <c r="B20" s="4" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="C20" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
     </row>
     <row r="21" ht="37" customHeight="1" spans="2:5">
       <c r="B21" s="5" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="D21" s="12" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="E21" s="8"/>
     </row>
-    <row r="22" ht="75" spans="2:5">
+    <row r="22" ht="72.5" spans="2:5">
       <c r="B22" s="5" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="C22" t="s">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="D22" s="12"/>
-      <c r="E22" s="21" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="23" ht="45" spans="2:5">
+      <c r="E22" s="20" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="23" ht="43.5" spans="2:5">
       <c r="B23" s="5" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="D23" s="12"/>
       <c r="E23" s="11" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="24" ht="75" spans="2:4">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="24" ht="58" spans="2:4">
       <c r="B24" s="5" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="C24" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="D24" s="10" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="25" ht="30" spans="2:3">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="25" ht="29" spans="2:3">
       <c r="B25" s="5" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="26" ht="45" spans="2:4">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="26" ht="43.5" spans="2:4">
       <c r="B26" s="5" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="C26" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="27" ht="225" spans="2:5">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="27" ht="203" spans="2:5">
       <c r="B27" s="5" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="C27" s="4"/>
       <c r="D27" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="E27" s="18" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="28" ht="45" spans="2:4">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="28" ht="43.5" spans="2:4">
       <c r="B28" s="5" t="s">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
     </row>
     <row r="29" spans="2:6">
       <c r="B29" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="D29" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="E29" s="8"/>
       <c r="F29" s="8" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
     </row>
     <row r="30" spans="2:4">
       <c r="B30" s="4" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="D30" s="14" t="s">
-        <v>409</v>
+        <v>413</v>
       </c>
     </row>
     <row r="31" ht="46" customHeight="1" spans="2:4">
       <c r="B31" s="4" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="D31" s="14"/>
     </row>
@@ -9450,14 +9561,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F21"/>
-  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9.14545454545454" defaultRowHeight="14.5" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="14.7142857142857" customWidth="1"/>
-    <col min="2" max="2" width="33.5714285714286" customWidth="1"/>
-    <col min="3" max="3" width="49.6666666666667" customWidth="1"/>
-    <col min="4" max="4" width="56.552380952381" customWidth="1"/>
-    <col min="5" max="5" width="53.2857142857143" customWidth="1"/>
-    <col min="6" max="6" width="47.5714285714286" customWidth="1"/>
+    <col min="1" max="1" width="14.7181818181818" customWidth="1"/>
+    <col min="2" max="2" width="33.5727272727273" customWidth="1"/>
+    <col min="3" max="3" width="49.6636363636364" customWidth="1"/>
+    <col min="4" max="4" width="56.5545454545455" customWidth="1"/>
+    <col min="5" max="5" width="53.2818181818182" customWidth="1"/>
+    <col min="6" max="6" width="47.5727272727273" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" spans="1:6">
@@ -9474,18 +9585,18 @@
         <v>11</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
     </row>
     <row r="2" ht="17" customHeight="1" spans="1:6">
       <c r="A2" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="3"/>
@@ -9498,7 +9609,7 @@
         <v>14</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -9510,7 +9621,7 @@
         <v>17</v>
       </c>
       <c r="D4" t="s">
-        <v>410</v>
+        <v>414</v>
       </c>
     </row>
     <row r="5" customFormat="1" spans="1:6">
@@ -9519,18 +9630,18 @@
         <v>19</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="D5" s="4"/>
       <c r="E5" s="4"/>
       <c r="F5" s="4"/>
     </row>
-    <row r="6" customFormat="1" ht="30" spans="2:6">
+    <row r="6" customFormat="1" ht="29" spans="2:6">
       <c r="B6" s="17" t="s">
         <v>22</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="D6" s="4"/>
       <c r="E6" s="4"/>
@@ -9538,170 +9649,170 @@
     </row>
     <row r="7" spans="2:6">
       <c r="B7" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="D7" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="8" ht="150" spans="2:5">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="8" ht="145" spans="2:5">
       <c r="B8" s="5" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="D8" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="E8" s="11" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
     </row>
     <row r="9" ht="409" customHeight="1" spans="2:5">
       <c r="B9" s="5" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="D9" s="10" t="s">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>413</v>
-      </c>
-    </row>
-    <row r="10" ht="165" spans="2:5">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="10" ht="159.5" spans="2:5">
       <c r="B10" s="5" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="E10" s="18" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="11" ht="180" spans="2:5">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="11" ht="159.5" spans="2:5">
       <c r="B11" s="5" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="C11" s="4"/>
       <c r="E11" s="11" t="s">
-        <v>416</v>
-      </c>
-    </row>
-    <row r="12" ht="150" spans="2:5">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="12" ht="145" spans="2:5">
       <c r="B12" s="5" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="C12" s="4"/>
       <c r="E12" s="11" t="s">
-        <v>417</v>
-      </c>
-    </row>
-    <row r="13" ht="75" spans="2:4">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="13" ht="58" spans="2:4">
       <c r="B13" s="5" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="C13" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="D13" s="10" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="14" ht="30" spans="2:3">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="14" ht="29" spans="2:3">
       <c r="B14" s="5" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="15" ht="45" spans="2:4">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="15" ht="43.5" spans="2:4">
       <c r="B15" s="5" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="C15" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="16" ht="225" spans="2:5">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="16" ht="203" spans="2:5">
       <c r="B16" s="5" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="C16" s="4"/>
       <c r="D16" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="E16" s="18" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="17" ht="45" spans="2:4">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="17" ht="43.5" spans="2:4">
       <c r="B17" s="5" t="s">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
     </row>
     <row r="18" spans="2:6">
       <c r="B18" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="D18" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="E18" s="8" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="F18" s="15" t="s">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="19" ht="165" spans="2:5">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="19" ht="159.5" spans="2:5">
       <c r="B19" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="E19" t="s">
-        <v>421</v>
+        <v>425</v>
       </c>
     </row>
     <row r="20" spans="2:4">
       <c r="B20" s="4" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="D20" s="14" t="s">
-        <v>409</v>
+        <v>413</v>
       </c>
     </row>
     <row r="21" ht="46" customHeight="1" spans="2:4">
       <c r="B21" s="4" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="D21" s="14"/>
     </row>

--- a/support/specifications/ccda/CCDA to FHIR Conversion Spec - Epic.xlsx
+++ b/support/specifications/ccda/CCDA to FHIR Conversion Spec - Epic.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="8000" tabRatio="709" activeTab="1"/>
+    <workbookView windowWidth="28800" windowHeight="12180" tabRatio="709" activeTab="9"/>
   </bookViews>
   <sheets>
     <sheet name="Epic" sheetId="11" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="696" uniqueCount="446">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="697" uniqueCount="447">
   <si>
     <t>Epic CCDA</t>
   </si>
@@ -122,6 +122,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>If the header variable `</t>
     </r>
     <r>
@@ -604,13 +611,11 @@
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">
-HP -&gt; home  
-H -&gt; home  
-WP -&gt; work  
-TMP -&gt; temp  
-OLD -&gt; old  
-BAD -&gt; old  
-All Others -&gt; patientRole.addr.use</t>
+WP, DIR, PUB -&gt; work
+BA -&gt; billing
+TMP -&gt; temp
+OLD, BAD -&gt; old
+All Others -&gt; home</t>
     </r>
   </si>
   <si>
@@ -701,18 +706,12 @@
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">
-AS -&gt; work  
-DIR -&gt; work  
-PUB -&gt; work  
-WP -&gt; work  
-BAD -&gt; old  
-H -&gt; home  
-HP -&gt; home  
-HV -&gt; home  
-MC -&gt; mobile  
-PG -&gt; mobile  
-TMP -&gt; temp  
-All Others -&gt; patient.telecom.use</t>
+AS, DIR, PUB, WP, WPN -&gt; work
+H, HP, HV, PRN, ORN, PRS -&gt; home
+MC, PG -&gt; mobile
+TMP -&gt; temp
+BAD -&gt; old
+All others -&gt; home</t>
     </r>
   </si>
   <si>
@@ -3546,6 +3545,35 @@
     <t>Document.author.assignedAuthor.representedOrganization.telecom.use</t>
   </si>
   <si>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>telecom -&gt; use Mapping</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+AS, DIR, PUB, WP, WPN -&gt; work
+MC, PG -&gt; mobile
+TMP -&gt; temp
+BAD -&gt; old
+All others -&gt; work</t>
+    </r>
+  </si>
+  <si>
     <t>Document.author.assignedAuthor.representedOrganization.addr.streetAddressLine
 Document.author.assignedAuthor.representedOrganization.addr.city
 Document.author.assignedAuthor.representedOrganization.addr.state,
@@ -3564,6 +3592,35 @@
   </si>
   <si>
     <t>Document.author.assignedAuthor.representedOrganization.addr.use</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>addr.use -&gt; use Mapping</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+WP, DIR, PUB -&gt; work
+BA -&gt; billing
+TMP -&gt; temp
+OLD, BAD -&gt; old
+All Others -&gt; work</t>
+    </r>
   </si>
   <si>
     <t>Document.author.assignedAuthor.representedOrganization.addr.streetAddressLine</t>
@@ -5196,37 +5253,6 @@
   </si>
   <si>
     <t>addr.use</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <u/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>addr.use -&gt; use Mapping</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-HP -&gt; home  
-H -&gt; home  
-WP -&gt; work  
-TMP -&gt; temp  
-OLD -&gt; old  
-BAD -&gt; old  
-All Others -&gt;addr.use</t>
-    </r>
   </si>
   <si>
     <t>addr.streetAddressLine
@@ -5519,6 +5545,7 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color rgb="FFC00000"/>
       <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -5526,15 +5553,14 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <i/>
       <sz val="11"/>
-      <color rgb="FFC00000"/>
+      <color rgb="FF00B050"/>
       <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -5566,9 +5592,9 @@
       <charset val="134"/>
     </font>
     <font>
-      <i/>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF00B050"/>
+      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -6036,7 +6062,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -6104,6 +6130,9 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -6676,20 +6705,20 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultColWidth="8.88181818181818" defaultRowHeight="14.5" outlineLevelRow="6" outlineLevelCol="2"/>
+  <sheetFormatPr defaultColWidth="8.88571428571429" defaultRowHeight="15" outlineLevelRow="6" outlineLevelCol="2"/>
   <cols>
-    <col min="1" max="1" width="8.88181818181818" style="31"/>
-    <col min="2" max="2" width="35.2181818181818" customWidth="1"/>
-    <col min="3" max="3" width="92.6636363636364" customWidth="1"/>
+    <col min="1" max="1" width="8.88571428571429" style="32"/>
+    <col min="2" max="2" width="35.2190476190476" customWidth="1"/>
+    <col min="3" max="3" width="92.6666666666667" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:2">
-      <c r="B1" s="32" t="s">
+      <c r="B1" s="33" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:3">
-      <c r="A3" s="31">
+      <c r="A3" s="32">
         <v>1</v>
       </c>
       <c r="B3" s="5" t="s">
@@ -6700,7 +6729,7 @@
       </c>
     </row>
     <row r="4" spans="1:3">
-      <c r="A4" s="31">
+      <c r="A4" s="32">
         <v>2</v>
       </c>
       <c r="B4" s="9" t="s">
@@ -6711,7 +6740,7 @@
       </c>
     </row>
     <row r="5" spans="1:3">
-      <c r="A5" s="31">
+      <c r="A5" s="32">
         <v>3</v>
       </c>
       <c r="B5" s="15" t="s">
@@ -6722,10 +6751,10 @@
       </c>
     </row>
     <row r="6" spans="1:3">
-      <c r="A6" s="31">
+      <c r="A6" s="32">
         <v>4</v>
       </c>
-      <c r="B6" s="25" t="s">
+      <c r="B6" s="26" t="s">
         <v>3</v>
       </c>
       <c r="C6" t="s">
@@ -6733,10 +6762,10 @@
       </c>
     </row>
     <row r="7" spans="1:3">
-      <c r="A7" s="31">
+      <c r="A7" s="32">
         <v>5</v>
       </c>
-      <c r="B7" s="33" t="s">
+      <c r="B7" s="34" t="s">
         <v>3</v>
       </c>
       <c r="C7" t="s">
@@ -6753,14 +6782,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F21"/>
-  <sheetFormatPr defaultColWidth="9.14545454545454" defaultRowHeight="14.5" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="14.7181818181818" customWidth="1"/>
-    <col min="2" max="2" width="33.5727272727273" customWidth="1"/>
-    <col min="3" max="3" width="49.6636363636364" customWidth="1"/>
-    <col min="4" max="4" width="56.5545454545455" customWidth="1"/>
-    <col min="5" max="5" width="53.2818181818182" customWidth="1"/>
-    <col min="6" max="6" width="47.5727272727273" customWidth="1"/>
+    <col min="1" max="1" width="14.7142857142857" customWidth="1"/>
+    <col min="2" max="2" width="33.5714285714286" customWidth="1"/>
+    <col min="3" max="3" width="49.6666666666667" customWidth="1"/>
+    <col min="4" max="4" width="56.552380952381" customWidth="1"/>
+    <col min="5" max="5" width="53.2857142857143" customWidth="1"/>
+    <col min="6" max="6" width="47.5714285714286" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" spans="1:6">
@@ -6788,7 +6817,7 @@
         <v>47</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="3"/>
@@ -6800,10 +6829,10 @@
         <v>14</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>427</v>
-      </c>
-    </row>
-    <row r="4" ht="43.5" spans="2:6">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="4" ht="60" spans="2:6">
       <c r="B4" s="5" t="s">
         <v>16</v>
       </c>
@@ -6811,7 +6840,7 @@
         <v>17</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="F4" s="7"/>
     </row>
@@ -6825,19 +6854,19 @@
       <c r="D5"/>
       <c r="E5" s="8"/>
     </row>
-    <row r="6" customFormat="1" ht="29" spans="2:6">
+    <row r="6" customFormat="1" ht="30" spans="2:6">
       <c r="B6" s="5" t="s">
         <v>22</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="D6"/>
       <c r="E6" s="4" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="F6" s="9" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
     </row>
     <row r="7" spans="2:6">
@@ -6845,34 +6874,34 @@
         <v>324</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="D7" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="E7" s="11"/>
       <c r="F7" s="4"/>
     </row>
-    <row r="8" ht="116" spans="2:5">
+    <row r="8" ht="90" spans="2:5">
       <c r="B8" s="4" t="s">
         <v>84</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="D8" s="12" t="s">
         <v>86</v>
       </c>
       <c r="E8" s="13" t="s">
-        <v>435</v>
-      </c>
-    </row>
-    <row r="9" ht="58" spans="2:5">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="9" ht="60" spans="2:5">
       <c r="B9" s="4" t="s">
         <v>88</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="D9" s="12"/>
       <c r="E9" s="4"/>
@@ -6882,7 +6911,7 @@
         <v>90</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="D10" s="12"/>
       <c r="E10" s="4"/>
@@ -6892,7 +6921,7 @@
         <v>92</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="D11" s="12"/>
       <c r="E11" s="4"/>
@@ -6902,7 +6931,7 @@
         <v>94</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="D12" s="12"/>
       <c r="E12" s="4"/>
@@ -6912,7 +6941,7 @@
         <v>96</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="D13" s="12"/>
       <c r="E13" s="4"/>
@@ -6922,17 +6951,17 @@
         <v>98</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="D14" s="12"/>
       <c r="E14" s="4"/>
     </row>
     <row r="15" spans="2:5">
       <c r="B15" s="4" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="D15" s="12"/>
       <c r="E15" s="4"/>
@@ -6945,7 +6974,7 @@
         <v>193</v>
       </c>
       <c r="D16" s="14" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="E16" s="8"/>
       <c r="F16" s="4"/>
@@ -6955,7 +6984,7 @@
         <v>195</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="D17" s="14"/>
       <c r="E17" s="8"/>
@@ -6993,14 +7022,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:G23"/>
-  <sheetFormatPr defaultColWidth="9.14545454545454" defaultRowHeight="14.5" outlineLevelCol="6"/>
+  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="14.7181818181818" customWidth="1"/>
-    <col min="2" max="2" width="28.3363636363636" customWidth="1"/>
-    <col min="3" max="3" width="65.4545454545455" customWidth="1"/>
-    <col min="4" max="4" width="46.2181818181818" customWidth="1"/>
-    <col min="5" max="5" width="61.2818181818182" customWidth="1"/>
-    <col min="6" max="6" width="46.2818181818182" customWidth="1"/>
+    <col min="1" max="1" width="14.7142857142857" customWidth="1"/>
+    <col min="2" max="2" width="28.3333333333333" customWidth="1"/>
+    <col min="3" max="3" width="65.4571428571429" customWidth="1"/>
+    <col min="4" max="4" width="46.2190476190476" customWidth="1"/>
+    <col min="5" max="5" width="61.2857142857143" customWidth="1"/>
+    <col min="6" max="6" width="46.2857142857143" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" spans="1:6">
@@ -7049,37 +7078,37 @@
         <v>18</v>
       </c>
     </row>
-    <row r="5" s="26" customFormat="1" ht="61" customHeight="1" spans="1:4">
-      <c r="A5" s="27"/>
-      <c r="B5" s="27" t="s">
+    <row r="5" s="27" customFormat="1" ht="61" customHeight="1" spans="1:4">
+      <c r="A5" s="28"/>
+      <c r="B5" s="28" t="s">
         <v>19</v>
       </c>
-      <c r="C5" s="27" t="s">
+      <c r="C5" s="28" t="s">
         <v>20</v>
       </c>
-      <c r="D5" s="28" t="s">
+      <c r="D5" s="29" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="6" s="26" customFormat="1" ht="49" customHeight="1" spans="1:4">
-      <c r="A6" s="27"/>
-      <c r="B6" s="27" t="s">
+    <row r="6" s="27" customFormat="1" ht="49" customHeight="1" spans="1:4">
+      <c r="A6" s="28"/>
+      <c r="B6" s="28" t="s">
         <v>22</v>
       </c>
-      <c r="C6" s="27" t="s">
+      <c r="C6" s="28" t="s">
         <v>23</v>
       </c>
-      <c r="D6" s="28"/>
-    </row>
-    <row r="7" s="26" customFormat="1" ht="86" customHeight="1" spans="1:4">
-      <c r="A7" s="27"/>
-      <c r="B7" s="27" t="s">
+      <c r="D6" s="29"/>
+    </row>
+    <row r="7" s="27" customFormat="1" ht="86" customHeight="1" spans="1:4">
+      <c r="A7" s="28"/>
+      <c r="B7" s="28" t="s">
         <v>24</v>
       </c>
-      <c r="C7" s="29" t="s">
+      <c r="C7" s="30" t="s">
         <v>25</v>
       </c>
-      <c r="D7" s="28"/>
+      <c r="D7" s="29"/>
     </row>
     <row r="8" spans="2:4">
       <c r="B8" t="s">
@@ -7098,7 +7127,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="10" ht="29" spans="2:3">
+    <row r="10" ht="30" spans="2:3">
       <c r="B10" t="s">
         <v>30</v>
       </c>
@@ -7119,7 +7148,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="17" ht="72.5" spans="2:3">
+    <row r="17" ht="75" spans="2:3">
       <c r="B17" t="s">
         <v>35</v>
       </c>
@@ -7135,7 +7164,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="19" ht="72.5" spans="2:5">
+    <row r="19" ht="75" spans="2:5">
       <c r="B19" t="s">
         <v>39</v>
       </c>
@@ -7146,7 +7175,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="20" ht="29" spans="2:5">
+    <row r="20" ht="45" spans="2:5">
       <c r="B20" s="4" t="s">
         <v>42</v>
       </c>
@@ -7155,7 +7184,7 @@
       </c>
       <c r="E20" s="10"/>
     </row>
-    <row r="21" ht="58" spans="2:5">
+    <row r="21" ht="60" spans="2:5">
       <c r="B21" t="s">
         <v>44</v>
       </c>
@@ -7164,14 +7193,14 @@
       </c>
       <c r="E21" s="10"/>
     </row>
-    <row r="22" ht="29" spans="2:5">
+    <row r="22" ht="30" spans="2:5">
       <c r="B22" s="4" t="s">
         <v>46</v>
       </c>
       <c r="E22" s="8"/>
     </row>
-    <row r="23" ht="101.5" spans="2:7">
-      <c r="B23" s="30" t="s">
+    <row r="23" ht="105" spans="2:7">
+      <c r="B23" s="31" t="s">
         <v>47</v>
       </c>
       <c r="C23" s="10" t="s">
@@ -7198,13 +7227,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F68"/>
-  <sheetFormatPr defaultColWidth="8.88181818181818" defaultRowHeight="14.5" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="8.88571428571429" defaultRowHeight="15" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="14.7181818181818" customWidth="1"/>
-    <col min="2" max="2" width="41.7818181818182" style="4" customWidth="1"/>
-    <col min="3" max="3" width="63.8818181818182" style="4" customWidth="1"/>
-    <col min="4" max="4" width="81.2818181818182" style="4" customWidth="1"/>
-    <col min="5" max="5" width="48.4272727272727" style="4" customWidth="1"/>
+    <col min="1" max="1" width="14.7142857142857" customWidth="1"/>
+    <col min="2" max="2" width="41.7809523809524" style="4" customWidth="1"/>
+    <col min="3" max="3" width="63.8857142857143" style="4" customWidth="1"/>
+    <col min="4" max="4" width="81.2857142857143" style="4" customWidth="1"/>
+    <col min="5" max="5" width="48.4285714285714" style="4" customWidth="1"/>
     <col min="6" max="6" width="45" customWidth="1"/>
   </cols>
   <sheetData>
@@ -7212,19 +7241,19 @@
       <c r="A1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="23" t="s">
+      <c r="B1" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="C1" s="23" t="s">
+      <c r="C1" s="24" t="s">
         <v>10</v>
       </c>
-      <c r="D1" s="23" t="s">
+      <c r="D1" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="E1" s="23" t="s">
+      <c r="E1" s="24" t="s">
         <v>49</v>
       </c>
-      <c r="F1" s="23" t="s">
+      <c r="F1" s="24" t="s">
         <v>50</v>
       </c>
     </row>
@@ -7270,7 +7299,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="7" ht="29" spans="2:4">
+    <row r="7" ht="30" spans="2:4">
       <c r="B7" s="4" t="s">
         <v>55</v>
       </c>
@@ -7281,7 +7310,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="8" ht="58" spans="2:5">
+    <row r="8" ht="60" spans="2:5">
       <c r="B8" s="4" t="s">
         <v>58</v>
       </c>
@@ -7337,7 +7366,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="13" ht="58" spans="2:4">
+    <row r="13" ht="60" spans="2:4">
       <c r="B13" s="4" t="s">
         <v>72</v>
       </c>
@@ -7348,7 +7377,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="14" ht="29" spans="2:4">
+    <row r="14" ht="30" spans="2:4">
       <c r="B14" s="4" t="s">
         <v>75</v>
       </c>
@@ -7359,7 +7388,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="15" ht="29" spans="2:4">
+    <row r="15" ht="30" spans="2:4">
       <c r="B15" s="4" t="s">
         <v>78</v>
       </c>
@@ -7381,7 +7410,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="17" ht="116" spans="2:5">
+    <row r="17" ht="90" spans="2:5">
       <c r="B17" s="4" t="s">
         <v>84</v>
       </c>
@@ -7395,7 +7424,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="18" ht="58" spans="2:4">
+    <row r="18" ht="60" spans="2:4">
       <c r="B18" s="4" t="s">
         <v>88</v>
       </c>
@@ -7468,18 +7497,18 @@
         <v>104</v>
       </c>
     </row>
-    <row r="26" ht="198" customHeight="1" spans="2:5">
+    <row r="26" ht="105" spans="2:5">
       <c r="B26" s="4" t="s">
         <v>105</v>
       </c>
       <c r="C26" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="E26" s="13" t="s">
+      <c r="E26" s="23" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="27" ht="43.5" spans="2:5">
+    <row r="27" ht="45" spans="2:5">
       <c r="B27" s="4" t="s">
         <v>108</v>
       </c>
@@ -7493,7 +7522,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="28" spans="2:5">
+    <row r="28" ht="30" spans="2:5">
       <c r="B28" s="4" t="s">
         <v>112</v>
       </c>
@@ -7513,7 +7542,7 @@
       <c r="D29" s="14"/>
       <c r="E29" s="8"/>
     </row>
-    <row r="30" spans="2:5">
+    <row r="30" ht="30" spans="2:5">
       <c r="B30" s="4" t="s">
         <v>116</v>
       </c>
@@ -7533,7 +7562,7 @@
       <c r="D31" s="14"/>
       <c r="E31" s="8"/>
     </row>
-    <row r="32" ht="43.5" spans="2:5">
+    <row r="32" ht="45" spans="2:5">
       <c r="B32" s="4" t="s">
         <v>108</v>
       </c>
@@ -7547,7 +7576,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="33" spans="2:4">
+    <row r="33" ht="30" spans="2:4">
       <c r="B33" s="4" t="s">
         <v>112</v>
       </c>
@@ -7565,7 +7594,7 @@
       </c>
       <c r="D34" s="14"/>
     </row>
-    <row r="35" spans="2:4">
+    <row r="35" ht="30" spans="2:4">
       <c r="B35" s="4" t="s">
         <v>116</v>
       </c>
@@ -7594,7 +7623,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="38" ht="43.5" spans="2:5">
+    <row r="38" ht="45" spans="2:5">
       <c r="B38" s="4" t="s">
         <v>128</v>
       </c>
@@ -7602,11 +7631,11 @@
         <v>79</v>
       </c>
       <c r="D38" s="14"/>
-      <c r="E38" s="34" t="s">
+      <c r="E38" s="35" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="39" ht="116" spans="2:6">
+    <row r="39" ht="120" spans="2:6">
       <c r="B39" s="4" t="s">
         <v>130</v>
       </c>
@@ -7617,7 +7646,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="40" ht="116" spans="2:6">
+    <row r="40" ht="120" spans="2:6">
       <c r="B40" s="4" t="s">
         <v>133</v>
       </c>
@@ -7664,7 +7693,7 @@
       </c>
       <c r="D44" s="10"/>
     </row>
-    <row r="45" ht="188.5" spans="2:5">
+    <row r="45" ht="195" spans="2:5">
       <c r="B45" s="17" t="s">
         <v>143</v>
       </c>
@@ -7678,7 +7707,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="46" ht="188.5" spans="2:5">
+    <row r="46" ht="195" spans="2:5">
       <c r="B46" s="17" t="s">
         <v>147</v>
       </c>
@@ -7692,7 +7721,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="47" ht="188.5" spans="2:5">
+    <row r="47" ht="195" spans="2:5">
       <c r="B47" s="17" t="s">
         <v>151</v>
       </c>
@@ -7702,7 +7731,7 @@
       <c r="D47" s="10" t="s">
         <v>153</v>
       </c>
-      <c r="E47" s="24"/>
+      <c r="E47" s="25"/>
     </row>
     <row r="48" customFormat="1" spans="2:5">
       <c r="B48" s="4" t="s">
@@ -7744,7 +7773,7 @@
       <c r="D51" s="10"/>
       <c r="E51" s="4"/>
     </row>
-    <row r="52" ht="145" spans="2:5">
+    <row r="52" ht="150" spans="2:5">
       <c r="B52" s="10" t="s">
         <v>160</v>
       </c>
@@ -7818,7 +7847,7 @@
       <c r="D58" s="10"/>
       <c r="E58" s="8"/>
     </row>
-    <row r="59" ht="174" spans="2:5">
+    <row r="59" ht="180" spans="2:5">
       <c r="B59" s="10" t="s">
         <v>174</v>
       </c>
@@ -7832,7 +7861,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="60" ht="246.5" spans="2:6">
+    <row r="60" ht="255" spans="2:6">
       <c r="B60" s="4" t="s">
         <v>177</v>
       </c>
@@ -7863,7 +7892,7 @@
       <c r="D62" s="10"/>
       <c r="F62" s="4"/>
     </row>
-    <row r="63" ht="203" spans="2:6">
+    <row r="63" ht="210" spans="2:6">
       <c r="B63" s="4" t="s">
         <v>184</v>
       </c>
@@ -7941,14 +7970,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:G22"/>
-  <sheetFormatPr defaultColWidth="9.14545454545454" defaultRowHeight="14.5" outlineLevelCol="6"/>
+  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="14.7181818181818" customWidth="1"/>
-    <col min="2" max="2" width="30.8545454545455" customWidth="1"/>
-    <col min="3" max="3" width="63.4272727272727" customWidth="1"/>
-    <col min="4" max="4" width="70.7181818181818" customWidth="1"/>
-    <col min="5" max="5" width="52.4272727272727" customWidth="1"/>
-    <col min="6" max="6" width="57.5727272727273" customWidth="1"/>
+    <col min="1" max="1" width="14.7142857142857" customWidth="1"/>
+    <col min="2" max="2" width="30.8571428571429" customWidth="1"/>
+    <col min="3" max="3" width="63.4285714285714" customWidth="1"/>
+    <col min="4" max="4" width="70.7142857142857" customWidth="1"/>
+    <col min="5" max="5" width="52.4285714285714" customWidth="1"/>
+    <col min="6" max="6" width="57.5714285714286" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" spans="1:6">
@@ -7990,7 +8019,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="4" ht="58" spans="2:7">
+    <row r="4" ht="60" spans="2:7">
       <c r="B4" s="5" t="s">
         <v>16</v>
       </c>
@@ -8019,9 +8048,9 @@
       <c r="C6" t="s">
         <v>201</v>
       </c>
-      <c r="E6" s="25"/>
-    </row>
-    <row r="7" ht="116" spans="2:6">
+      <c r="E6" s="26"/>
+    </row>
+    <row r="7" ht="120" spans="2:6">
       <c r="B7" s="5" t="s">
         <v>202</v>
       </c>
@@ -8074,7 +8103,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="11" ht="203" spans="2:5">
+    <row r="11" ht="225" spans="2:5">
       <c r="B11" s="5" t="s">
         <v>214</v>
       </c>
@@ -8110,7 +8139,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="14" ht="29" spans="2:5">
+    <row r="14" ht="30" spans="2:5">
       <c r="B14" s="5" t="s">
         <v>221</v>
       </c>
@@ -8124,7 +8153,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="15" ht="43.5" spans="2:5">
+    <row r="15" ht="45" spans="2:5">
       <c r="B15" s="5" t="s">
         <v>225</v>
       </c>
@@ -8138,7 +8167,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="16" ht="43.5" spans="2:5">
+    <row r="16" ht="45" spans="2:5">
       <c r="B16" s="5" t="s">
         <v>229</v>
       </c>
@@ -8150,7 +8179,7 @@
       </c>
       <c r="E16" s="8"/>
     </row>
-    <row r="17" ht="43.5" spans="2:5">
+    <row r="17" ht="45" spans="2:5">
       <c r="B17" s="5" t="s">
         <v>232</v>
       </c>
@@ -8162,7 +8191,7 @@
       </c>
       <c r="E17" s="8"/>
     </row>
-    <row r="18" ht="43.5" spans="2:5">
+    <row r="18" ht="45" spans="2:5">
       <c r="B18" t="s">
         <v>235</v>
       </c>
@@ -8176,7 +8205,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="19" ht="58" spans="2:5">
+    <row r="19" ht="60" spans="2:5">
       <c r="B19" s="5" t="s">
         <v>238</v>
       </c>
@@ -8241,14 +8270,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F26"/>
-  <sheetFormatPr defaultColWidth="9.14545454545454" defaultRowHeight="14.5" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="14.7181818181818" customWidth="1"/>
-    <col min="2" max="2" width="35.1454545454545" customWidth="1"/>
-    <col min="3" max="3" width="42.2818181818182" style="4" customWidth="1"/>
-    <col min="4" max="4" width="73.5727272727273" customWidth="1"/>
+    <col min="1" max="1" width="14.7142857142857" customWidth="1"/>
+    <col min="2" max="2" width="35.1428571428571" customWidth="1"/>
+    <col min="3" max="3" width="42.2857142857143" style="4" customWidth="1"/>
+    <col min="4" max="4" width="73.5714285714286" customWidth="1"/>
     <col min="5" max="5" width="53" customWidth="1"/>
-    <col min="6" max="6" width="51.7181818181818" customWidth="1"/>
+    <col min="6" max="6" width="51.7142857142857" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" spans="1:6">
@@ -8258,7 +8287,7 @@
       <c r="B1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C1" s="23" t="s">
+      <c r="C1" s="24" t="s">
         <v>10</v>
       </c>
       <c r="D1" s="2" t="s">
@@ -8290,7 +8319,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="4" ht="72.5" spans="1:5">
+    <row r="4" ht="75" spans="1:5">
       <c r="A4" s="1"/>
       <c r="B4" s="5" t="s">
         <v>16</v>
@@ -8317,7 +8346,7 @@
       <c r="E5" s="4"/>
       <c r="F5" s="4"/>
     </row>
-    <row r="6" customFormat="1" ht="29" spans="2:6">
+    <row r="6" customFormat="1" ht="30" spans="2:6">
       <c r="B6" s="17" t="s">
         <v>22</v>
       </c>
@@ -8328,7 +8357,7 @@
       <c r="E6" s="4"/>
       <c r="F6" s="4"/>
     </row>
-    <row r="7" ht="159.5" spans="2:5">
+    <row r="7" ht="165" spans="2:5">
       <c r="B7" s="5" t="s">
         <v>202</v>
       </c>
@@ -8354,7 +8383,7 @@
       </c>
       <c r="E8" s="9"/>
     </row>
-    <row r="9" ht="29" spans="2:5">
+    <row r="9" ht="30" spans="2:5">
       <c r="B9" s="5" t="s">
         <v>256</v>
       </c>
@@ -8362,7 +8391,7 @@
         <v>257</v>
       </c>
       <c r="D9" s="10"/>
-      <c r="E9" s="24"/>
+      <c r="E9" s="25"/>
     </row>
     <row r="10" spans="2:5">
       <c r="B10" s="5" t="s">
@@ -8374,7 +8403,7 @@
       <c r="D10" s="10"/>
       <c r="E10" s="9"/>
     </row>
-    <row r="11" ht="29" spans="2:4">
+    <row r="11" ht="30" spans="2:4">
       <c r="B11" s="5" t="s">
         <v>260</v>
       </c>
@@ -8385,7 +8414,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="12" ht="58" spans="2:5">
+    <row r="12" ht="60" spans="2:5">
       <c r="B12" s="5" t="s">
         <v>263</v>
       </c>
@@ -8411,7 +8440,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="15" customFormat="1" ht="58" spans="2:4">
+    <row r="15" customFormat="1" ht="60" spans="2:4">
       <c r="B15" s="5" t="s">
         <v>269</v>
       </c>
@@ -8422,7 +8451,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="16" customFormat="1" ht="29" spans="2:3">
+    <row r="16" customFormat="1" ht="30" spans="2:3">
       <c r="B16" s="5" t="s">
         <v>271</v>
       </c>
@@ -8430,7 +8459,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="17" ht="58" spans="2:4">
+    <row r="17" ht="60" spans="2:4">
       <c r="B17" t="s">
         <v>273</v>
       </c>
@@ -8449,7 +8478,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="19" ht="43.5" spans="2:5">
+    <row r="19" ht="45" spans="2:5">
       <c r="B19" t="s">
         <v>278</v>
       </c>
@@ -8483,7 +8512,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="22" ht="58" spans="2:5">
+    <row r="22" ht="60" spans="2:5">
       <c r="B22" t="s">
         <v>287</v>
       </c>
@@ -8552,14 +8581,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F32"/>
-  <sheetFormatPr defaultColWidth="9.14545454545454" defaultRowHeight="14.5" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="14.7181818181818" customWidth="1"/>
-    <col min="2" max="2" width="27.3363636363636" customWidth="1"/>
-    <col min="3" max="3" width="50.8818181818182" customWidth="1"/>
-    <col min="4" max="4" width="72.8545454545455" customWidth="1"/>
-    <col min="5" max="5" width="46.4272727272727" customWidth="1"/>
-    <col min="6" max="6" width="45.7181818181818" customWidth="1"/>
+    <col min="1" max="1" width="14.7142857142857" customWidth="1"/>
+    <col min="2" max="2" width="27.3333333333333" customWidth="1"/>
+    <col min="3" max="3" width="50.8857142857143" customWidth="1"/>
+    <col min="4" max="4" width="72.8571428571429" customWidth="1"/>
+    <col min="5" max="5" width="46.4285714285714" customWidth="1"/>
+    <col min="6" max="6" width="45.7142857142857" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" spans="1:6">
@@ -8617,7 +8646,7 @@
       </c>
       <c r="F5" s="4"/>
     </row>
-    <row r="6" customFormat="1" ht="29" spans="2:6">
+    <row r="6" customFormat="1" ht="30" spans="2:6">
       <c r="B6" s="4" t="s">
         <v>22</v>
       </c>
@@ -8666,7 +8695,7 @@
       <c r="D9" s="10"/>
       <c r="E9" s="8"/>
     </row>
-    <row r="10" ht="29" spans="2:5">
+    <row r="10" ht="30" spans="2:5">
       <c r="B10" s="4" t="s">
         <v>309</v>
       </c>
@@ -8676,7 +8705,7 @@
       <c r="D10" s="10"/>
       <c r="E10" s="8"/>
     </row>
-    <row r="11" ht="29" spans="2:5">
+    <row r="11" ht="30" spans="2:5">
       <c r="B11" s="4" t="s">
         <v>311</v>
       </c>
@@ -8686,7 +8715,7 @@
       <c r="D11" s="10"/>
       <c r="E11" s="8"/>
     </row>
-    <row r="12" ht="29" spans="2:5">
+    <row r="12" ht="30" spans="2:5">
       <c r="B12" s="4" t="s">
         <v>312</v>
       </c>
@@ -8720,7 +8749,7 @@
       <c r="D14" s="10"/>
       <c r="E14" s="22"/>
     </row>
-    <row r="15" customFormat="1" ht="29" spans="2:5">
+    <row r="15" customFormat="1" ht="30" spans="2:5">
       <c r="B15" s="4" t="s">
         <v>319</v>
       </c>
@@ -8730,7 +8759,7 @@
       <c r="D15" s="10"/>
       <c r="E15" s="22"/>
     </row>
-    <row r="16" customFormat="1" ht="29" spans="2:5">
+    <row r="16" customFormat="1" ht="30" spans="2:5">
       <c r="B16" s="4" t="s">
         <v>321</v>
       </c>
@@ -8740,7 +8769,7 @@
       <c r="D16" s="10"/>
       <c r="E16" s="4"/>
     </row>
-    <row r="17" customFormat="1" ht="29" spans="2:4">
+    <row r="17" customFormat="1" ht="30" spans="2:4">
       <c r="B17" s="4" t="s">
         <v>322</v>
       </c>
@@ -8749,7 +8778,7 @@
       </c>
       <c r="D17" s="10"/>
     </row>
-    <row r="18" ht="58" spans="2:5">
+    <row r="18" ht="60" spans="2:5">
       <c r="B18" s="5" t="s">
         <v>324</v>
       </c>
@@ -8797,7 +8826,7 @@
       </c>
       <c r="F21" s="4"/>
     </row>
-    <row r="22" customFormat="1" ht="29" spans="2:6">
+    <row r="22" customFormat="1" ht="30" spans="2:6">
       <c r="B22" s="4" t="s">
         <v>103</v>
       </c>
@@ -8807,7 +8836,7 @@
       <c r="D22" s="10"/>
       <c r="F22" s="4"/>
     </row>
-    <row r="23" customFormat="1" ht="188.5" spans="2:6">
+    <row r="23" customFormat="1" ht="90" spans="2:6">
       <c r="B23" s="4" t="s">
         <v>105</v>
       </c>
@@ -8815,85 +8844,87 @@
         <v>335</v>
       </c>
       <c r="D23" s="10"/>
-      <c r="E23" s="13" t="s">
-        <v>107</v>
+      <c r="E23" s="23" t="s">
+        <v>336</v>
       </c>
       <c r="F23" s="4"/>
     </row>
-    <row r="24" customFormat="1" ht="116" spans="2:6">
+    <row r="24" customFormat="1" ht="120" spans="2:6">
       <c r="B24" s="4" t="s">
         <v>88</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="D24" s="10" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="E24" s="4"/>
       <c r="F24" s="4"/>
     </row>
-    <row r="25" customFormat="1" ht="29" spans="2:6">
+    <row r="25" customFormat="1" ht="90" spans="2:6">
       <c r="B25" s="4" t="s">
         <v>84</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="D25" s="10"/>
-      <c r="E25" s="4"/>
+      <c r="E25" s="13" t="s">
+        <v>340</v>
+      </c>
       <c r="F25" s="4"/>
     </row>
-    <row r="26" customFormat="1" ht="29" spans="2:6">
+    <row r="26" customFormat="1" ht="30" spans="2:6">
       <c r="B26" s="4" t="s">
         <v>90</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="D26" s="10"/>
       <c r="E26" s="4"/>
       <c r="F26" s="4"/>
     </row>
-    <row r="27" customFormat="1" ht="29" spans="2:6">
+    <row r="27" customFormat="1" ht="30" spans="2:6">
       <c r="B27" s="4" t="s">
         <v>92</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="D27" s="10"/>
       <c r="E27" s="4"/>
       <c r="F27" s="4"/>
     </row>
-    <row r="28" customFormat="1" ht="29" spans="2:6">
+    <row r="28" customFormat="1" ht="30" spans="2:6">
       <c r="B28" s="4" t="s">
         <v>94</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="D28" s="10"/>
       <c r="E28" s="4"/>
       <c r="F28" s="4"/>
     </row>
-    <row r="29" customFormat="1" ht="29" spans="2:6">
+    <row r="29" customFormat="1" ht="30" spans="2:6">
       <c r="B29" s="4" t="s">
         <v>96</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="D29" s="10"/>
       <c r="E29" s="4"/>
       <c r="F29" s="4"/>
     </row>
-    <row r="30" customFormat="1" ht="29" spans="2:6">
+    <row r="30" customFormat="1" ht="30" spans="2:6">
       <c r="B30" s="4" t="s">
         <v>98</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="D30" s="10"/>
       <c r="E30" s="4"/>
@@ -8907,7 +8938,7 @@
         <v>193</v>
       </c>
       <c r="D31" s="14" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
     </row>
     <row r="32" customFormat="1" ht="46" customHeight="1" spans="2:4">
@@ -8915,7 +8946,7 @@
         <v>195</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="D32" s="14"/>
     </row>
@@ -8937,13 +8968,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F21"/>
-  <sheetFormatPr defaultColWidth="8.88181818181818" defaultRowHeight="14.5" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="8.88571428571429" defaultRowHeight="15" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="14.7181818181818" customWidth="1"/>
-    <col min="2" max="2" width="33.8818181818182" customWidth="1"/>
-    <col min="3" max="3" width="46.8545454545455" customWidth="1"/>
-    <col min="4" max="4" width="57.1181818181818" customWidth="1"/>
-    <col min="5" max="5" width="54.7181818181818" customWidth="1"/>
+    <col min="1" max="1" width="14.7142857142857" customWidth="1"/>
+    <col min="2" max="2" width="33.8857142857143" customWidth="1"/>
+    <col min="3" max="3" width="46.8571428571429" customWidth="1"/>
+    <col min="4" max="4" width="57.1142857142857" customWidth="1"/>
+    <col min="5" max="5" width="54.7142857142857" customWidth="1"/>
     <col min="6" max="6" width="38" customWidth="1"/>
   </cols>
   <sheetData>
@@ -8967,9 +8998,9 @@
         <v>50</v>
       </c>
     </row>
-    <row r="2" ht="43.5" spans="1:1">
+    <row r="2" ht="45" spans="1:1">
       <c r="A2" s="21" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -8978,7 +9009,7 @@
         <v>14</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -8990,7 +9021,7 @@
         <v>17</v>
       </c>
       <c r="D4" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -9005,12 +9036,12 @@
       <c r="E5" s="4"/>
       <c r="F5" s="4"/>
     </row>
-    <row r="6" ht="29" spans="2:6">
+    <row r="6" ht="30" spans="2:6">
       <c r="B6" s="17" t="s">
         <v>22</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="D6" s="4"/>
       <c r="E6" s="4"/>
@@ -9024,46 +9055,46 @@
         <v>57</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="8" ht="145" spans="2:5">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="8" ht="150" spans="2:5">
       <c r="B8" s="5" t="s">
         <v>202</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="D8" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="E8" s="11" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
     </row>
     <row r="9" ht="70" customHeight="1" spans="2:4">
       <c r="B9" s="5" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="D9" s="10" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="10" ht="29" spans="2:4">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="10" ht="30" spans="2:4">
       <c r="B10" s="5" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="D10" s="10"/>
     </row>
     <row r="11" spans="2:5">
       <c r="B11" s="5" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="C11" s="4" t="s">
         <v>220</v>
@@ -9071,48 +9102,48 @@
       <c r="D11" s="10"/>
       <c r="E11" s="8"/>
     </row>
-    <row r="12" ht="29" spans="2:4">
+    <row r="12" ht="30" spans="2:4">
       <c r="B12" s="5" t="s">
+        <v>362</v>
+      </c>
+      <c r="C12" s="4" t="s">
         <v>360</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>358</v>
       </c>
       <c r="D12" s="10"/>
     </row>
     <row r="13" ht="38" customHeight="1" spans="2:4">
       <c r="B13" s="4" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="D13" s="10" t="s">
-        <v>363</v>
-      </c>
-    </row>
-    <row r="14" ht="29" spans="2:4">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="14" ht="30" spans="2:4">
       <c r="B14" s="4" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="D14" s="10"/>
     </row>
     <row r="15" ht="153" customHeight="1" spans="2:5">
       <c r="B15" s="4" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="D15" s="10"/>
       <c r="E15" s="8" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="16" ht="58" spans="2:4">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="16" ht="75" spans="2:4">
       <c r="B16" s="5" t="s">
         <v>269</v>
       </c>
@@ -9123,7 +9154,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="17" ht="29" spans="2:3">
+    <row r="17" ht="30" spans="2:3">
       <c r="B17" s="5" t="s">
         <v>271</v>
       </c>
@@ -9131,29 +9162,29 @@
         <v>272</v>
       </c>
     </row>
-    <row r="18" ht="87" spans="2:5">
+    <row r="18" ht="90" spans="2:5">
       <c r="B18" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="D18" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
     </row>
     <row r="19" spans="2:6">
       <c r="B19" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="D19" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="F19" s="15" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
     </row>
     <row r="20" spans="2:4">
@@ -9164,7 +9195,7 @@
         <v>193</v>
       </c>
       <c r="D20" s="14" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
     </row>
     <row r="21" ht="45" customHeight="1" spans="2:4">
@@ -9172,7 +9203,7 @@
         <v>195</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="D21" s="14"/>
     </row>
@@ -9191,14 +9222,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F31"/>
-  <sheetFormatPr defaultColWidth="9.14545454545454" defaultRowHeight="14.5" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="14.7181818181818" customWidth="1"/>
-    <col min="2" max="2" width="34.5727272727273" customWidth="1"/>
-    <col min="3" max="3" width="49.6636363636364" customWidth="1"/>
-    <col min="4" max="4" width="58.7181818181818" customWidth="1"/>
-    <col min="5" max="5" width="53.2818181818182" customWidth="1"/>
-    <col min="6" max="6" width="50.2818181818182" customWidth="1"/>
+    <col min="1" max="1" width="14.7142857142857" customWidth="1"/>
+    <col min="2" max="2" width="34.5714285714286" customWidth="1"/>
+    <col min="3" max="3" width="49.6666666666667" customWidth="1"/>
+    <col min="4" max="4" width="58.7142857142857" customWidth="1"/>
+    <col min="5" max="5" width="53.2857142857143" customWidth="1"/>
+    <col min="6" max="6" width="50.2857142857143" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" spans="1:6">
@@ -9226,7 +9257,7 @@
         <v>44</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="3"/>
@@ -9239,19 +9270,19 @@
         <v>14</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="4" ht="82.5" spans="1:4">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="4" ht="78" spans="1:4">
       <c r="A4" s="1"/>
       <c r="B4" s="5" t="s">
         <v>16</v>
       </c>
       <c r="C4" s="18" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
     </row>
     <row r="5" customFormat="1" spans="1:6">
@@ -9266,12 +9297,12 @@
       <c r="E5" s="4"/>
       <c r="F5" s="4"/>
     </row>
-    <row r="6" customFormat="1" ht="29" spans="2:6">
+    <row r="6" customFormat="1" ht="30" spans="2:6">
       <c r="B6" s="17" t="s">
         <v>22</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="D6" s="4"/>
       <c r="E6" s="4"/>
@@ -9285,88 +9316,88 @@
         <v>57</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="8" ht="145" spans="2:5">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="8" ht="150" spans="2:5">
       <c r="B8" s="5" t="s">
         <v>202</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="D8" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="E8" s="11" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
     </row>
     <row r="9" ht="139" customHeight="1" spans="2:5">
       <c r="B9" s="5" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="E9" s="18" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="10" ht="43.5" spans="2:5">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="10" ht="45" spans="2:5">
       <c r="B10" s="5" t="s">
         <v>219</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="D10" s="6"/>
       <c r="E10" s="8" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="11" ht="203" spans="2:5">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="11" ht="210" spans="2:5">
       <c r="B11" s="5" t="s">
         <v>214</v>
       </c>
       <c r="D11" s="6"/>
       <c r="E11" s="11" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="12" ht="203" spans="2:5">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="12" ht="210" spans="2:5">
       <c r="B12" s="5" t="s">
         <v>217</v>
       </c>
       <c r="D12" s="6"/>
       <c r="E12" s="11" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
     </row>
     <row r="13" spans="2:5">
       <c r="B13" s="5" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="D13" s="6"/>
       <c r="E13" s="8" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
     </row>
     <row r="14" ht="84" customHeight="1" spans="2:5">
       <c r="B14" s="5" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="C14" s="4" t="s">
         <v>254</v>
       </c>
       <c r="D14" s="10" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="E14" s="9"/>
     </row>
     <row r="15" spans="2:5">
       <c r="B15" s="5" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="C15" s="4" t="s">
         <v>259</v>
@@ -9376,7 +9407,7 @@
     </row>
     <row r="16" spans="2:5">
       <c r="B16" s="5" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="C16" s="4" t="s">
         <v>220</v>
@@ -9384,43 +9415,43 @@
       <c r="D16" s="10"/>
       <c r="E16" s="9"/>
     </row>
-    <row r="17" ht="29" spans="2:5">
+    <row r="17" ht="30" spans="2:5">
       <c r="B17" s="5" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="D17" s="10"/>
       <c r="E17" s="8" t="s">
-        <v>394</v>
-      </c>
-    </row>
-    <row r="18" ht="101.5" spans="2:5">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="18" ht="105" spans="2:5">
       <c r="B18" s="4" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="D18" s="10" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="E18" s="18" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="19" ht="29" spans="2:3">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="19" ht="30" spans="2:3">
       <c r="B19" s="4" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="20" ht="29" spans="2:3">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="20" ht="30" spans="2:3">
       <c r="B20" s="4" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="C20" t="s">
         <v>220</v>
@@ -9428,38 +9459,38 @@
     </row>
     <row r="21" ht="37" customHeight="1" spans="2:5">
       <c r="B21" s="5" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="D21" s="12" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="E21" s="8"/>
     </row>
-    <row r="22" ht="72.5" spans="2:5">
+    <row r="22" ht="75" spans="2:5">
       <c r="B22" s="5" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="C22" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="D22" s="12"/>
       <c r="E22" s="20" t="s">
-        <v>404</v>
-      </c>
-    </row>
-    <row r="23" ht="43.5" spans="2:5">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="23" ht="45" spans="2:5">
       <c r="B23" s="5" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="D23" s="12"/>
       <c r="E23" s="11" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="24" ht="58" spans="2:4">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="24" ht="60" spans="2:4">
       <c r="B24" s="5" t="s">
         <v>269</v>
       </c>
@@ -9470,7 +9501,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="25" ht="29" spans="2:3">
+    <row r="25" ht="30" spans="2:3">
       <c r="B25" s="5" t="s">
         <v>271</v>
       </c>
@@ -9478,50 +9509,50 @@
         <v>272</v>
       </c>
     </row>
-    <row r="26" ht="43.5" spans="2:4">
+    <row r="26" ht="45" spans="2:4">
       <c r="B26" s="5" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="C26" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>409</v>
-      </c>
-    </row>
-    <row r="27" ht="203" spans="2:5">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="27" ht="225" spans="2:5">
       <c r="B27" s="5" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="C27" s="4"/>
       <c r="D27" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="E27" s="18" t="s">
-        <v>410</v>
-      </c>
-    </row>
-    <row r="28" ht="43.5" spans="2:4">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="28" ht="45" spans="2:4">
       <c r="B28" s="5" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="C28" s="4" t="s">
         <v>233</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
     </row>
     <row r="29" spans="2:6">
       <c r="B29" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="D29" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="E29" s="8"/>
       <c r="F29" s="8" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
     </row>
     <row r="30" spans="2:4">
@@ -9532,7 +9563,7 @@
         <v>193</v>
       </c>
       <c r="D30" s="14" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
     </row>
     <row r="31" ht="46" customHeight="1" spans="2:4">
@@ -9540,7 +9571,7 @@
         <v>195</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="D31" s="14"/>
     </row>
@@ -9561,14 +9592,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F21"/>
-  <sheetFormatPr defaultColWidth="9.14545454545454" defaultRowHeight="14.5" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="14.7181818181818" customWidth="1"/>
-    <col min="2" max="2" width="33.5727272727273" customWidth="1"/>
-    <col min="3" max="3" width="49.6636363636364" customWidth="1"/>
-    <col min="4" max="4" width="56.5545454545455" customWidth="1"/>
-    <col min="5" max="5" width="53.2818181818182" customWidth="1"/>
-    <col min="6" max="6" width="47.5727272727273" customWidth="1"/>
+    <col min="1" max="1" width="14.7142857142857" customWidth="1"/>
+    <col min="2" max="2" width="33.5714285714286" customWidth="1"/>
+    <col min="3" max="3" width="49.6666666666667" customWidth="1"/>
+    <col min="4" max="4" width="56.552380952381" customWidth="1"/>
+    <col min="5" max="5" width="53.2857142857143" customWidth="1"/>
+    <col min="6" max="6" width="47.5714285714286" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" spans="1:6">
@@ -9596,7 +9627,7 @@
         <v>44</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="3"/>
@@ -9609,7 +9640,7 @@
         <v>14</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -9621,7 +9652,7 @@
         <v>17</v>
       </c>
       <c r="D4" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
     </row>
     <row r="5" customFormat="1" spans="1:6">
@@ -9636,12 +9667,12 @@
       <c r="E5" s="4"/>
       <c r="F5" s="4"/>
     </row>
-    <row r="6" customFormat="1" ht="29" spans="2:6">
+    <row r="6" customFormat="1" ht="30" spans="2:6">
       <c r="B6" s="17" t="s">
         <v>22</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="D6" s="4"/>
       <c r="E6" s="4"/>
@@ -9655,70 +9686,70 @@
         <v>57</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="8" ht="145" spans="2:5">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="8" ht="150" spans="2:5">
       <c r="B8" s="5" t="s">
         <v>202</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="D8" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="E8" s="11" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
     </row>
     <row r="9" ht="409" customHeight="1" spans="2:5">
       <c r="B9" s="5" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="D9" s="10" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>417</v>
-      </c>
-    </row>
-    <row r="10" ht="159.5" spans="2:5">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="10" ht="165" spans="2:5">
       <c r="B10" s="5" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="C10" s="4" t="s">
         <v>254</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="E10" s="18" t="s">
-        <v>419</v>
-      </c>
-    </row>
-    <row r="11" ht="159.5" spans="2:5">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="11" ht="180" spans="2:5">
       <c r="B11" s="5" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="C11" s="4"/>
       <c r="E11" s="11" t="s">
-        <v>420</v>
-      </c>
-    </row>
-    <row r="12" ht="145" spans="2:5">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="12" ht="150" spans="2:5">
       <c r="B12" s="5" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="C12" s="4"/>
       <c r="E12" s="11" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="13" ht="58" spans="2:4">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="13" ht="75" spans="2:4">
       <c r="B13" s="5" t="s">
         <v>269</v>
       </c>
@@ -9729,7 +9760,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="14" ht="29" spans="2:3">
+    <row r="14" ht="30" spans="2:3">
       <c r="B14" s="5" t="s">
         <v>271</v>
       </c>
@@ -9737,63 +9768,63 @@
         <v>272</v>
       </c>
     </row>
-    <row r="15" ht="43.5" spans="2:4">
+    <row r="15" ht="45" spans="2:4">
       <c r="B15" s="5" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="C15" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>409</v>
-      </c>
-    </row>
-    <row r="16" ht="203" spans="2:5">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="16" ht="225" spans="2:5">
       <c r="B16" s="5" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="C16" s="4"/>
       <c r="D16" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="E16" s="18" t="s">
-        <v>410</v>
-      </c>
-    </row>
-    <row r="17" ht="43.5" spans="2:4">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="17" ht="45" spans="2:4">
       <c r="B17" s="5" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="C17" s="4" t="s">
         <v>233</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
     </row>
     <row r="18" spans="2:6">
       <c r="B18" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="D18" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="E18" s="8" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="F18" s="15" t="s">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="19" ht="159.5" spans="2:5">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="19" ht="165" spans="2:5">
       <c r="B19" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="E19" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
     </row>
     <row r="20" spans="2:4">
@@ -9804,7 +9835,7 @@
         <v>193</v>
       </c>
       <c r="D20" s="14" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
     </row>
     <row r="21" ht="46" customHeight="1" spans="2:4">
@@ -9812,7 +9843,7 @@
         <v>195</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="D21" s="14"/>
     </row>

--- a/support/specifications/ccda/CCDA to FHIR Conversion Spec - Epic.xlsx
+++ b/support/specifications/ccda/CCDA to FHIR Conversion Spec - Epic.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12180" tabRatio="709" activeTab="9"/>
+    <workbookView windowWidth="28800" windowHeight="12180" tabRatio="709" activeTab="7"/>
   </bookViews>
   <sheets>
     <sheet name="Epic" sheetId="11" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="697" uniqueCount="447">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="697" uniqueCount="449">
   <si>
     <t>Epic CCDA</t>
   </si>
@@ -591,15 +591,6 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <b/>
-        <u/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
       <t>addr.use -&gt; use Mapping</t>
     </r>
     <r>
@@ -612,9 +603,8 @@
       </rPr>
       <t xml:space="preserve">
 WP, DIR, PUB -&gt; work
-BA -&gt; billing
 TMP -&gt; temp
-OLD, BAD -&gt; old
+BAD -&gt; old
 All Others -&gt; home</t>
     </r>
   </si>
@@ -706,8 +696,8 @@
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">
-AS, DIR, PUB, WP, WPN -&gt; work
-H, HP, HV, PRN, ORN, PRS -&gt; home
+AS, DIR, PUB, WP -&gt; work
+H, HP, HV, EC -&gt; home
 MC, PG -&gt; mobile
 TMP -&gt; temp
 BAD -&gt; old
@@ -3566,7 +3556,7 @@
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">
-AS, DIR, PUB, WP, WPN -&gt; work
+AS, DIR, PUB, WP -&gt; work
 MC, PG -&gt; mobile
 TMP -&gt; temp
 BAD -&gt; old
@@ -3616,9 +3606,8 @@
       </rPr>
       <t xml:space="preserve">
 WP, DIR, PUB -&gt; work
-BA -&gt; billing
 TMP -&gt; temp
-OLD, BAD -&gt; old
+BAD -&gt; old
 All Others -&gt; work</t>
     </r>
   </si>
@@ -4095,6 +4084,27 @@
   </si>
   <si>
     <t>statusCode.code</t>
+  </si>
+  <si>
+    <r>
+      <t>statusCode.code -&gt; status Mapping</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+completed -&gt; final 
+final -&gt; final 
+aborted -&gt; entered-in-error  
+cancelled -&gt; entered-in-error  
+nullified -&gt; entered-in-error 
+All Others -&gt; unknown</t>
+    </r>
   </si>
   <si>
     <t>category</t>
@@ -4794,13 +4804,6 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF00B050"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
       <t xml:space="preserve">For </t>
     </r>
     <r>
@@ -5253,6 +5256,35 @@
   </si>
   <si>
     <t>addr.use</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>addr.use -&gt; use Mapping</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+WP, DIR, PUB -&gt; work
+BA -&gt; billing
+TMP -&gt; temp
+BAD -&gt; old
+All Others -&gt; work</t>
+    </r>
   </si>
   <si>
     <t>addr.streetAddressLine
@@ -5369,17 +5401,17 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <u/>
       <sz val="11"/>
-      <color rgb="FF7030A0"/>
+      <color rgb="FF00B050"/>
       <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF00B050"/>
+      <color rgb="FF7030A0"/>
       <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -5567,6 +5599,14 @@
     </font>
     <font>
       <b/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="9"/>
       <color rgb="FF00B050"/>
       <name val="Consolas"/>
@@ -5590,14 +5630,6 @@
       <color rgb="FF00B050"/>
       <name val="Segoe UI"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="35">
@@ -6117,14 +6149,14 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -6817,7 +6849,7 @@
         <v>47</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="3"/>
@@ -6829,7 +6861,7 @@
         <v>14</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="4" ht="60" spans="2:6">
@@ -6840,7 +6872,7 @@
         <v>17</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="F4" s="7"/>
     </row>
@@ -6859,14 +6891,14 @@
         <v>22</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="D6"/>
       <c r="E6" s="4" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="F6" s="9" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="7" spans="2:6">
@@ -6874,10 +6906,10 @@
         <v>324</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="D7" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="E7" s="11"/>
       <c r="F7" s="4"/>
@@ -6887,13 +6919,13 @@
         <v>84</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="D8" s="12" t="s">
         <v>86</v>
       </c>
       <c r="E8" s="13" t="s">
-        <v>340</v>
+        <v>438</v>
       </c>
     </row>
     <row r="9" ht="60" spans="2:5">
@@ -6901,7 +6933,7 @@
         <v>88</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="D9" s="12"/>
       <c r="E9" s="4"/>
@@ -6911,7 +6943,7 @@
         <v>90</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="D10" s="12"/>
       <c r="E10" s="4"/>
@@ -6921,7 +6953,7 @@
         <v>92</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="D11" s="12"/>
       <c r="E11" s="4"/>
@@ -6931,7 +6963,7 @@
         <v>94</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="D12" s="12"/>
       <c r="E12" s="4"/>
@@ -6941,7 +6973,7 @@
         <v>96</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="D13" s="12"/>
       <c r="E13" s="4"/>
@@ -6951,17 +6983,17 @@
         <v>98</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="D14" s="12"/>
       <c r="E14" s="4"/>
     </row>
     <row r="15" spans="2:5">
       <c r="B15" s="4" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="D15" s="12"/>
       <c r="E15" s="4"/>
@@ -6974,7 +7006,7 @@
         <v>193</v>
       </c>
       <c r="D16" s="14" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="E16" s="8"/>
       <c r="F16" s="4"/>
@@ -6984,7 +7016,7 @@
         <v>195</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="D17" s="14"/>
       <c r="E17" s="8"/>
@@ -7171,7 +7203,7 @@
       <c r="C19" t="s">
         <v>40</v>
       </c>
-      <c r="E19" s="18" t="s">
+      <c r="E19" s="19" t="s">
         <v>41</v>
       </c>
     </row>
@@ -7410,7 +7442,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="17" ht="90" spans="2:5">
+    <row r="17" ht="75" spans="2:5">
       <c r="B17" s="4" t="s">
         <v>84</v>
       </c>
@@ -7703,7 +7735,7 @@
       <c r="D45" s="10" t="s">
         <v>145</v>
       </c>
-      <c r="E45" s="18" t="s">
+      <c r="E45" s="19" t="s">
         <v>146</v>
       </c>
     </row>
@@ -7711,7 +7743,7 @@
       <c r="B46" s="17" t="s">
         <v>147</v>
       </c>
-      <c r="C46" s="18" t="s">
+      <c r="C46" s="19" t="s">
         <v>148</v>
       </c>
       <c r="D46" s="10" t="s">
@@ -7777,7 +7809,7 @@
       <c r="B52" s="10" t="s">
         <v>160</v>
       </c>
-      <c r="C52" s="18" t="s">
+      <c r="C52" s="19" t="s">
         <v>161</v>
       </c>
       <c r="D52" s="10" t="s">
@@ -7857,7 +7889,7 @@
       <c r="D59" s="10" t="s">
         <v>175</v>
       </c>
-      <c r="E59" s="18" t="s">
+      <c r="E59" s="19" t="s">
         <v>176</v>
       </c>
     </row>
@@ -8361,7 +8393,7 @@
       <c r="B7" s="5" t="s">
         <v>202</v>
       </c>
-      <c r="C7" s="18" t="s">
+      <c r="C7" s="19" t="s">
         <v>250</v>
       </c>
       <c r="D7" t="s">
@@ -8407,7 +8439,7 @@
       <c r="B11" s="5" t="s">
         <v>260</v>
       </c>
-      <c r="C11" s="18" t="s">
+      <c r="C11" s="19" t="s">
         <v>261</v>
       </c>
       <c r="D11" s="12" t="s">
@@ -8675,7 +8707,7 @@
       <c r="B8" t="s">
         <v>303</v>
       </c>
-      <c r="C8" s="18" t="s">
+      <c r="C8" s="19" t="s">
         <v>304</v>
       </c>
       <c r="D8" s="10" t="s">
@@ -8729,7 +8761,7 @@
       <c r="B13" t="s">
         <v>314</v>
       </c>
-      <c r="C13" s="18" t="s">
+      <c r="C13" s="19" t="s">
         <v>315</v>
       </c>
       <c r="D13" s="10" t="s">
@@ -8782,7 +8814,7 @@
       <c r="B18" s="5" t="s">
         <v>324</v>
       </c>
-      <c r="C18" s="18" t="s">
+      <c r="C18" s="19" t="s">
         <v>325</v>
       </c>
       <c r="D18" s="10" t="s">
@@ -8862,7 +8894,7 @@
       <c r="E24" s="4"/>
       <c r="F24" s="4"/>
     </row>
-    <row r="25" customFormat="1" ht="90" spans="2:6">
+    <row r="25" customFormat="1" ht="75" spans="2:6">
       <c r="B25" s="4" t="s">
         <v>84</v>
       </c>
@@ -9262,7 +9294,7 @@
       <c r="C2" s="3"/>
       <c r="D2" s="3"/>
       <c r="E2" s="3"/>
-      <c r="F2" s="19"/>
+      <c r="F2" s="20"/>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="1"/>
@@ -9278,7 +9310,7 @@
       <c r="B4" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="C4" s="18" t="s">
+      <c r="C4" s="19" t="s">
         <v>381</v>
       </c>
       <c r="D4" s="4" t="s">
@@ -9319,7 +9351,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="8" ht="150" spans="2:5">
+    <row r="8" ht="105" spans="2:5">
       <c r="B8" s="5" t="s">
         <v>202</v>
       </c>
@@ -9329,19 +9361,19 @@
       <c r="D8" t="s">
         <v>354</v>
       </c>
-      <c r="E8" s="11" t="s">
-        <v>355</v>
+      <c r="E8" s="18" t="s">
+        <v>385</v>
       </c>
     </row>
     <row r="9" ht="139" customHeight="1" spans="2:5">
       <c r="B9" s="5" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>386</v>
-      </c>
-      <c r="E9" s="18" t="s">
         <v>387</v>
+      </c>
+      <c r="E9" s="19" t="s">
+        <v>388</v>
       </c>
     </row>
     <row r="10" ht="45" spans="2:5">
@@ -9349,11 +9381,11 @@
         <v>219</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="D10" s="6"/>
       <c r="E10" s="8" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="11" ht="210" spans="2:5">
@@ -9362,7 +9394,7 @@
       </c>
       <c r="D11" s="6"/>
       <c r="E11" s="11" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="12" ht="210" spans="2:5">
@@ -9371,16 +9403,16 @@
       </c>
       <c r="D12" s="6"/>
       <c r="E12" s="11" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="13" spans="2:5">
       <c r="B13" s="5" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="D13" s="6"/>
       <c r="E13" s="8" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="14" ht="84" customHeight="1" spans="2:5">
@@ -9391,7 +9423,7 @@
         <v>254</v>
       </c>
       <c r="D14" s="10" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="E14" s="9"/>
     </row>
@@ -9420,11 +9452,11 @@
         <v>362</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="D17" s="10"/>
       <c r="E17" s="8" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="18" ht="105" spans="2:5">
@@ -9432,13 +9464,13 @@
         <v>363</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="D18" s="10" t="s">
-        <v>398</v>
-      </c>
-      <c r="E18" s="18" t="s">
         <v>399</v>
+      </c>
+      <c r="E18" s="19" t="s">
+        <v>400</v>
       </c>
     </row>
     <row r="19" ht="30" spans="2:3">
@@ -9446,7 +9478,7 @@
         <v>366</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="20" ht="30" spans="2:3">
@@ -9459,35 +9491,35 @@
     </row>
     <row r="21" ht="37" customHeight="1" spans="2:5">
       <c r="B21" s="5" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="D21" s="12" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="E21" s="8"/>
     </row>
     <row r="22" ht="75" spans="2:5">
       <c r="B22" s="5" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="C22" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="D22" s="12"/>
-      <c r="E22" s="20" t="s">
-        <v>406</v>
+      <c r="E22" s="18" t="s">
+        <v>407</v>
       </c>
     </row>
     <row r="23" ht="45" spans="2:5">
       <c r="B23" s="5" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="D23" s="12"/>
       <c r="E23" s="11" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="24" ht="60" spans="2:4">
@@ -9511,13 +9543,13 @@
     </row>
     <row r="26" ht="45" spans="2:4">
       <c r="B26" s="5" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="C26" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="27" ht="225" spans="2:5">
@@ -9528,19 +9560,19 @@
       <c r="D27" t="s">
         <v>373</v>
       </c>
-      <c r="E27" s="18" t="s">
-        <v>412</v>
+      <c r="E27" s="19" t="s">
+        <v>413</v>
       </c>
     </row>
     <row r="28" ht="45" spans="2:4">
       <c r="B28" s="5" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C28" s="4" t="s">
         <v>233</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="29" spans="2:6">
@@ -9563,7 +9595,7 @@
         <v>193</v>
       </c>
       <c r="D30" s="14" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="31" ht="46" customHeight="1" spans="2:4">
@@ -9652,7 +9684,7 @@
         <v>17</v>
       </c>
       <c r="D4" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="5" customFormat="1" spans="1:6">
@@ -9686,13 +9718,13 @@
         <v>57</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="F7" s="8" t="s">
         <v>352</v>
       </c>
     </row>
-    <row r="8" ht="150" spans="2:5">
+    <row r="8" ht="105" spans="2:5">
       <c r="B8" s="5" t="s">
         <v>202</v>
       </c>
@@ -9702,19 +9734,19 @@
       <c r="D8" t="s">
         <v>354</v>
       </c>
-      <c r="E8" s="11" t="s">
-        <v>355</v>
+      <c r="E8" s="18" t="s">
+        <v>385</v>
       </c>
     </row>
     <row r="9" ht="409" customHeight="1" spans="2:5">
       <c r="B9" s="5" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="D9" s="10" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="10" ht="165" spans="2:5">
@@ -9725,10 +9757,10 @@
         <v>254</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>420</v>
-      </c>
-      <c r="E10" s="18" t="s">
         <v>421</v>
+      </c>
+      <c r="E10" s="19" t="s">
+        <v>422</v>
       </c>
     </row>
     <row r="11" ht="180" spans="2:5">
@@ -9737,7 +9769,7 @@
       </c>
       <c r="C11" s="4"/>
       <c r="E11" s="11" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="12" ht="150" spans="2:5">
@@ -9746,7 +9778,7 @@
       </c>
       <c r="C12" s="4"/>
       <c r="E12" s="11" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="13" ht="75" spans="2:4">
@@ -9770,13 +9802,13 @@
     </row>
     <row r="15" ht="45" spans="2:4">
       <c r="B15" s="5" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="C15" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="16" ht="225" spans="2:5">
@@ -9787,19 +9819,19 @@
       <c r="D16" t="s">
         <v>373</v>
       </c>
-      <c r="E16" s="18" t="s">
-        <v>412</v>
+      <c r="E16" s="19" t="s">
+        <v>413</v>
       </c>
     </row>
     <row r="17" ht="45" spans="2:4">
       <c r="B17" s="5" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C17" s="4" t="s">
         <v>233</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="18" spans="2:6">
@@ -9810,7 +9842,7 @@
         <v>376</v>
       </c>
       <c r="E18" s="8" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="F18" s="15" t="s">
         <v>377</v>
@@ -9818,13 +9850,13 @@
     </row>
     <row r="19" ht="165" spans="2:5">
       <c r="B19" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="E19" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="20" spans="2:4">
@@ -9835,7 +9867,7 @@
         <v>193</v>
       </c>
       <c r="D20" s="14" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="21" ht="46" customHeight="1" spans="2:4">

--- a/support/specifications/ccda/CCDA to FHIR Conversion Spec - Epic.xlsx
+++ b/support/specifications/ccda/CCDA to FHIR Conversion Spec - Epic.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12180" tabRatio="709" activeTab="7"/>
+    <workbookView windowWidth="19200" windowHeight="8000" tabRatio="709" firstSheet="2" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Epic" sheetId="11" r:id="rId1"/>
@@ -605,7 +605,7 @@
 WP, DIR, PUB -&gt; work
 TMP -&gt; temp
 BAD -&gt; old
-All Others -&gt; home</t>
+All Others (H, HP, HV, AS, EC, MC, PG) -&gt; home</t>
     </r>
   </si>
   <si>
@@ -676,15 +676,6 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <b/>
-        <u/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
       <t>telecom -&gt; use Mapping</t>
     </r>
     <r>
@@ -700,8 +691,7 @@
 H, HP, HV, EC -&gt; home
 MC, PG -&gt; mobile
 TMP -&gt; temp
-BAD -&gt; old
-All others -&gt; home</t>
+BAD -&gt; old</t>
     </r>
   </si>
   <si>
@@ -3536,15 +3526,6 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <b/>
-        <u/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
       <t>telecom -&gt; use Mapping</t>
     </r>
     <r>
@@ -3560,7 +3541,7 @@
 MC, PG -&gt; mobile
 TMP -&gt; temp
 BAD -&gt; old
-All others -&gt; work</t>
+All others (H, HP, HV, EC) -&gt; work</t>
     </r>
   </si>
   <si>
@@ -3585,15 +3566,6 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <b/>
-        <u/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
       <t>addr.use -&gt; use Mapping</t>
     </r>
     <r>
@@ -3608,7 +3580,7 @@
 WP, DIR, PUB -&gt; work
 TMP -&gt; temp
 BAD -&gt; old
-All Others -&gt; work</t>
+All Others (H, HP, HV, AS, EC, MC, PG) -&gt; work</t>
     </r>
   </si>
   <si>
@@ -4087,6 +4059,15 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>statusCode.code -&gt; status Mapping</t>
     </r>
     <r>
@@ -4804,6 +4785,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">For </t>
     </r>
     <r>
@@ -5259,15 +5247,6 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <b/>
-        <u/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
       <t>addr.use -&gt; use Mapping</t>
     </r>
     <r>
@@ -5280,10 +5259,9 @@
       </rPr>
       <t xml:space="preserve">
 WP, DIR, PUB -&gt; work
-BA -&gt; billing
 TMP -&gt; temp
 BAD -&gt; old
-All Others -&gt; work</t>
+All Others (H, HP, HV, AS, EC, MC, PG, BA) -&gt; work</t>
     </r>
   </si>
   <si>
@@ -5567,17 +5545,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <i/>
       <sz val="11"/>
       <color rgb="FF00B050"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFC00000"/>
       <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -5590,7 +5560,7 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
+      <b/>
       <sz val="11"/>
       <color rgb="FF00B050"/>
       <name val="Calibri"/>
@@ -5600,7 +5570,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FFC00000"/>
       <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -5630,6 +5600,14 @@
       <color rgb="FF00B050"/>
       <name val="Segoe UI"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="35">
@@ -6737,11 +6715,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultColWidth="8.88571428571429" defaultRowHeight="15" outlineLevelRow="6" outlineLevelCol="2"/>
+  <sheetFormatPr defaultColWidth="8.88181818181818" defaultRowHeight="14.5" outlineLevelRow="6" outlineLevelCol="2"/>
   <cols>
-    <col min="1" max="1" width="8.88571428571429" style="32"/>
-    <col min="2" max="2" width="35.2190476190476" customWidth="1"/>
-    <col min="3" max="3" width="92.6666666666667" customWidth="1"/>
+    <col min="1" max="1" width="8.88181818181818" style="32"/>
+    <col min="2" max="2" width="35.2181818181818" customWidth="1"/>
+    <col min="3" max="3" width="92.6636363636364" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:2">
@@ -6814,14 +6792,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F21"/>
-  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9.14545454545454" defaultRowHeight="14.5" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="14.7142857142857" customWidth="1"/>
-    <col min="2" max="2" width="33.5714285714286" customWidth="1"/>
-    <col min="3" max="3" width="49.6666666666667" customWidth="1"/>
-    <col min="4" max="4" width="56.552380952381" customWidth="1"/>
-    <col min="5" max="5" width="53.2857142857143" customWidth="1"/>
-    <col min="6" max="6" width="47.5714285714286" customWidth="1"/>
+    <col min="1" max="1" width="14.7181818181818" customWidth="1"/>
+    <col min="2" max="2" width="33.5727272727273" customWidth="1"/>
+    <col min="3" max="3" width="49.6636363636364" customWidth="1"/>
+    <col min="4" max="4" width="56.5545454545455" customWidth="1"/>
+    <col min="5" max="5" width="53.2818181818182" customWidth="1"/>
+    <col min="6" max="6" width="47.5727272727273" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" spans="1:6">
@@ -6864,7 +6842,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="4" ht="60" spans="2:6">
+    <row r="4" ht="43.5" spans="2:6">
       <c r="B4" s="5" t="s">
         <v>16</v>
       </c>
@@ -6886,7 +6864,7 @@
       <c r="D5"/>
       <c r="E5" s="8"/>
     </row>
-    <row r="6" customFormat="1" ht="30" spans="2:6">
+    <row r="6" customFormat="1" ht="29" spans="2:6">
       <c r="B6" s="5" t="s">
         <v>22</v>
       </c>
@@ -6914,7 +6892,7 @@
       <c r="E7" s="11"/>
       <c r="F7" s="4"/>
     </row>
-    <row r="8" ht="90" spans="2:5">
+    <row r="8" ht="72.5" spans="2:5">
       <c r="B8" s="4" t="s">
         <v>84</v>
       </c>
@@ -6928,7 +6906,7 @@
         <v>438</v>
       </c>
     </row>
-    <row r="9" ht="60" spans="2:5">
+    <row r="9" ht="58" spans="2:5">
       <c r="B9" s="4" t="s">
         <v>88</v>
       </c>
@@ -7054,14 +7032,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:G23"/>
-  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelCol="6"/>
+  <sheetFormatPr defaultColWidth="9.14545454545454" defaultRowHeight="14.5" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="14.7142857142857" customWidth="1"/>
-    <col min="2" max="2" width="28.3333333333333" customWidth="1"/>
-    <col min="3" max="3" width="65.4571428571429" customWidth="1"/>
-    <col min="4" max="4" width="46.2190476190476" customWidth="1"/>
-    <col min="5" max="5" width="61.2857142857143" customWidth="1"/>
-    <col min="6" max="6" width="46.2857142857143" customWidth="1"/>
+    <col min="1" max="1" width="14.7181818181818" customWidth="1"/>
+    <col min="2" max="2" width="28.3363636363636" customWidth="1"/>
+    <col min="3" max="3" width="65.4545454545455" customWidth="1"/>
+    <col min="4" max="4" width="46.2181818181818" customWidth="1"/>
+    <col min="5" max="5" width="61.2818181818182" customWidth="1"/>
+    <col min="6" max="6" width="46.2818181818182" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" spans="1:6">
@@ -7159,7 +7137,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="10" ht="30" spans="2:3">
+    <row r="10" ht="29" spans="2:3">
       <c r="B10" t="s">
         <v>30</v>
       </c>
@@ -7180,7 +7158,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="17" ht="75" spans="2:3">
+    <row r="17" ht="72.5" spans="2:3">
       <c r="B17" t="s">
         <v>35</v>
       </c>
@@ -7196,7 +7174,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="19" ht="75" spans="2:5">
+    <row r="19" ht="72.5" spans="2:5">
       <c r="B19" t="s">
         <v>39</v>
       </c>
@@ -7207,7 +7185,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="20" ht="45" spans="2:5">
+    <row r="20" ht="29" spans="2:5">
       <c r="B20" s="4" t="s">
         <v>42</v>
       </c>
@@ -7216,7 +7194,7 @@
       </c>
       <c r="E20" s="10"/>
     </row>
-    <row r="21" ht="60" spans="2:5">
+    <row r="21" ht="58" spans="2:5">
       <c r="B21" t="s">
         <v>44</v>
       </c>
@@ -7225,13 +7203,13 @@
       </c>
       <c r="E21" s="10"/>
     </row>
-    <row r="22" ht="30" spans="2:5">
+    <row r="22" ht="29" spans="2:5">
       <c r="B22" s="4" t="s">
         <v>46</v>
       </c>
       <c r="E22" s="8"/>
     </row>
-    <row r="23" ht="105" spans="2:7">
+    <row r="23" ht="101.5" spans="2:7">
       <c r="B23" s="31" t="s">
         <v>47</v>
       </c>
@@ -7259,13 +7237,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F68"/>
-  <sheetFormatPr defaultColWidth="8.88571428571429" defaultRowHeight="15" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="8.88181818181818" defaultRowHeight="14.5" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="14.7142857142857" customWidth="1"/>
-    <col min="2" max="2" width="41.7809523809524" style="4" customWidth="1"/>
-    <col min="3" max="3" width="63.8857142857143" style="4" customWidth="1"/>
-    <col min="4" max="4" width="81.2857142857143" style="4" customWidth="1"/>
-    <col min="5" max="5" width="48.4285714285714" style="4" customWidth="1"/>
+    <col min="1" max="1" width="14.7181818181818" customWidth="1"/>
+    <col min="2" max="2" width="41.7818181818182" style="4" customWidth="1"/>
+    <col min="3" max="3" width="63.8818181818182" style="4" customWidth="1"/>
+    <col min="4" max="4" width="81.2818181818182" style="4" customWidth="1"/>
+    <col min="5" max="5" width="48.4272727272727" style="4" customWidth="1"/>
     <col min="6" max="6" width="45" customWidth="1"/>
   </cols>
   <sheetData>
@@ -7331,7 +7309,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="7" ht="30" spans="2:4">
+    <row r="7" ht="29" spans="2:4">
       <c r="B7" s="4" t="s">
         <v>55</v>
       </c>
@@ -7342,7 +7320,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="8" ht="60" spans="2:5">
+    <row r="8" ht="58" spans="2:5">
       <c r="B8" s="4" t="s">
         <v>58</v>
       </c>
@@ -7398,7 +7376,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="13" ht="60" spans="2:4">
+    <row r="13" ht="58" spans="2:4">
       <c r="B13" s="4" t="s">
         <v>72</v>
       </c>
@@ -7409,7 +7387,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="14" ht="30" spans="2:4">
+    <row r="14" ht="29" spans="2:4">
       <c r="B14" s="4" t="s">
         <v>75</v>
       </c>
@@ -7420,7 +7398,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="15" ht="30" spans="2:4">
+    <row r="15" ht="29" spans="2:4">
       <c r="B15" s="4" t="s">
         <v>78</v>
       </c>
@@ -7442,7 +7420,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="17" ht="75" spans="2:5">
+    <row r="17" ht="72.5" spans="2:5">
       <c r="B17" s="4" t="s">
         <v>84</v>
       </c>
@@ -7456,7 +7434,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="18" ht="60" spans="2:4">
+    <row r="18" ht="58" spans="2:4">
       <c r="B18" s="4" t="s">
         <v>88</v>
       </c>
@@ -7529,7 +7507,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="26" ht="105" spans="2:5">
+    <row r="26" ht="87" spans="2:5">
       <c r="B26" s="4" t="s">
         <v>105</v>
       </c>
@@ -7540,7 +7518,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="27" ht="45" spans="2:5">
+    <row r="27" ht="43.5" spans="2:5">
       <c r="B27" s="4" t="s">
         <v>108</v>
       </c>
@@ -7554,7 +7532,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="28" ht="30" spans="2:5">
+    <row r="28" spans="2:5">
       <c r="B28" s="4" t="s">
         <v>112</v>
       </c>
@@ -7574,7 +7552,7 @@
       <c r="D29" s="14"/>
       <c r="E29" s="8"/>
     </row>
-    <row r="30" ht="30" spans="2:5">
+    <row r="30" spans="2:5">
       <c r="B30" s="4" t="s">
         <v>116</v>
       </c>
@@ -7594,7 +7572,7 @@
       <c r="D31" s="14"/>
       <c r="E31" s="8"/>
     </row>
-    <row r="32" ht="45" spans="2:5">
+    <row r="32" ht="43.5" spans="2:5">
       <c r="B32" s="4" t="s">
         <v>108</v>
       </c>
@@ -7608,7 +7586,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="33" ht="30" spans="2:4">
+    <row r="33" spans="2:4">
       <c r="B33" s="4" t="s">
         <v>112</v>
       </c>
@@ -7626,7 +7604,7 @@
       </c>
       <c r="D34" s="14"/>
     </row>
-    <row r="35" ht="30" spans="2:4">
+    <row r="35" spans="2:4">
       <c r="B35" s="4" t="s">
         <v>116</v>
       </c>
@@ -7655,7 +7633,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="38" ht="45" spans="2:5">
+    <row r="38" ht="43.5" spans="2:5">
       <c r="B38" s="4" t="s">
         <v>128</v>
       </c>
@@ -7667,7 +7645,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="39" ht="120" spans="2:6">
+    <row r="39" ht="116" spans="2:6">
       <c r="B39" s="4" t="s">
         <v>130</v>
       </c>
@@ -7678,7 +7656,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="40" ht="120" spans="2:6">
+    <row r="40" ht="116" spans="2:6">
       <c r="B40" s="4" t="s">
         <v>133</v>
       </c>
@@ -7725,7 +7703,7 @@
       </c>
       <c r="D44" s="10"/>
     </row>
-    <row r="45" ht="195" spans="2:5">
+    <row r="45" ht="188.5" spans="2:5">
       <c r="B45" s="17" t="s">
         <v>143</v>
       </c>
@@ -7739,7 +7717,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="46" ht="195" spans="2:5">
+    <row r="46" ht="188.5" spans="2:5">
       <c r="B46" s="17" t="s">
         <v>147</v>
       </c>
@@ -7753,7 +7731,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="47" ht="195" spans="2:5">
+    <row r="47" ht="188.5" spans="2:5">
       <c r="B47" s="17" t="s">
         <v>151</v>
       </c>
@@ -7805,7 +7783,7 @@
       <c r="D51" s="10"/>
       <c r="E51" s="4"/>
     </row>
-    <row r="52" ht="150" spans="2:5">
+    <row r="52" ht="145" spans="2:5">
       <c r="B52" s="10" t="s">
         <v>160</v>
       </c>
@@ -7879,7 +7857,7 @@
       <c r="D58" s="10"/>
       <c r="E58" s="8"/>
     </row>
-    <row r="59" ht="180" spans="2:5">
+    <row r="59" ht="174" spans="2:5">
       <c r="B59" s="10" t="s">
         <v>174</v>
       </c>
@@ -7893,7 +7871,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="60" ht="255" spans="2:6">
+    <row r="60" ht="246.5" spans="2:6">
       <c r="B60" s="4" t="s">
         <v>177</v>
       </c>
@@ -7924,7 +7902,7 @@
       <c r="D62" s="10"/>
       <c r="F62" s="4"/>
     </row>
-    <row r="63" ht="210" spans="2:6">
+    <row r="63" ht="203" spans="2:6">
       <c r="B63" s="4" t="s">
         <v>184</v>
       </c>
@@ -8002,14 +7980,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:G22"/>
-  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelCol="6"/>
+  <sheetFormatPr defaultColWidth="9.14545454545454" defaultRowHeight="14.5" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="14.7142857142857" customWidth="1"/>
-    <col min="2" max="2" width="30.8571428571429" customWidth="1"/>
-    <col min="3" max="3" width="63.4285714285714" customWidth="1"/>
-    <col min="4" max="4" width="70.7142857142857" customWidth="1"/>
-    <col min="5" max="5" width="52.4285714285714" customWidth="1"/>
-    <col min="6" max="6" width="57.5714285714286" customWidth="1"/>
+    <col min="1" max="1" width="14.7181818181818" customWidth="1"/>
+    <col min="2" max="2" width="30.8545454545455" customWidth="1"/>
+    <col min="3" max="3" width="63.4272727272727" customWidth="1"/>
+    <col min="4" max="4" width="70.7181818181818" customWidth="1"/>
+    <col min="5" max="5" width="52.4272727272727" customWidth="1"/>
+    <col min="6" max="6" width="57.5727272727273" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" spans="1:6">
@@ -8051,7 +8029,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="4" ht="60" spans="2:7">
+    <row r="4" ht="58" spans="2:7">
       <c r="B4" s="5" t="s">
         <v>16</v>
       </c>
@@ -8082,7 +8060,7 @@
       </c>
       <c r="E6" s="26"/>
     </row>
-    <row r="7" ht="120" spans="2:6">
+    <row r="7" ht="116" spans="2:6">
       <c r="B7" s="5" t="s">
         <v>202</v>
       </c>
@@ -8135,7 +8113,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="11" ht="225" spans="2:5">
+    <row r="11" ht="203" spans="2:5">
       <c r="B11" s="5" t="s">
         <v>214</v>
       </c>
@@ -8171,7 +8149,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="14" ht="30" spans="2:5">
+    <row r="14" ht="29" spans="2:5">
       <c r="B14" s="5" t="s">
         <v>221</v>
       </c>
@@ -8185,7 +8163,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="15" ht="45" spans="2:5">
+    <row r="15" ht="43.5" spans="2:5">
       <c r="B15" s="5" t="s">
         <v>225</v>
       </c>
@@ -8199,7 +8177,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="16" ht="45" spans="2:5">
+    <row r="16" ht="43.5" spans="2:5">
       <c r="B16" s="5" t="s">
         <v>229</v>
       </c>
@@ -8211,7 +8189,7 @@
       </c>
       <c r="E16" s="8"/>
     </row>
-    <row r="17" ht="45" spans="2:5">
+    <row r="17" ht="43.5" spans="2:5">
       <c r="B17" s="5" t="s">
         <v>232</v>
       </c>
@@ -8223,7 +8201,7 @@
       </c>
       <c r="E17" s="8"/>
     </row>
-    <row r="18" ht="45" spans="2:5">
+    <row r="18" ht="43.5" spans="2:5">
       <c r="B18" t="s">
         <v>235</v>
       </c>
@@ -8237,7 +8215,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="19" ht="60" spans="2:5">
+    <row r="19" ht="58" spans="2:5">
       <c r="B19" s="5" t="s">
         <v>238</v>
       </c>
@@ -8302,14 +8280,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F26"/>
-  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9.14545454545454" defaultRowHeight="14.5" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="14.7142857142857" customWidth="1"/>
-    <col min="2" max="2" width="35.1428571428571" customWidth="1"/>
-    <col min="3" max="3" width="42.2857142857143" style="4" customWidth="1"/>
-    <col min="4" max="4" width="73.5714285714286" customWidth="1"/>
+    <col min="1" max="1" width="14.7181818181818" customWidth="1"/>
+    <col min="2" max="2" width="35.1454545454545" customWidth="1"/>
+    <col min="3" max="3" width="42.2818181818182" style="4" customWidth="1"/>
+    <col min="4" max="4" width="73.5727272727273" customWidth="1"/>
     <col min="5" max="5" width="53" customWidth="1"/>
-    <col min="6" max="6" width="51.7142857142857" customWidth="1"/>
+    <col min="6" max="6" width="51.7181818181818" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" spans="1:6">
@@ -8351,7 +8329,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="4" ht="75" spans="1:5">
+    <row r="4" ht="72.5" spans="1:5">
       <c r="A4" s="1"/>
       <c r="B4" s="5" t="s">
         <v>16</v>
@@ -8378,7 +8356,7 @@
       <c r="E5" s="4"/>
       <c r="F5" s="4"/>
     </row>
-    <row r="6" customFormat="1" ht="30" spans="2:6">
+    <row r="6" customFormat="1" ht="29" spans="2:6">
       <c r="B6" s="17" t="s">
         <v>22</v>
       </c>
@@ -8389,7 +8367,7 @@
       <c r="E6" s="4"/>
       <c r="F6" s="4"/>
     </row>
-    <row r="7" ht="165" spans="2:5">
+    <row r="7" ht="159.5" spans="2:5">
       <c r="B7" s="5" t="s">
         <v>202</v>
       </c>
@@ -8415,7 +8393,7 @@
       </c>
       <c r="E8" s="9"/>
     </row>
-    <row r="9" ht="30" spans="2:5">
+    <row r="9" ht="29" spans="2:5">
       <c r="B9" s="5" t="s">
         <v>256</v>
       </c>
@@ -8435,7 +8413,7 @@
       <c r="D10" s="10"/>
       <c r="E10" s="9"/>
     </row>
-    <row r="11" ht="30" spans="2:4">
+    <row r="11" ht="29" spans="2:4">
       <c r="B11" s="5" t="s">
         <v>260</v>
       </c>
@@ -8446,7 +8424,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="12" ht="60" spans="2:5">
+    <row r="12" ht="58" spans="2:5">
       <c r="B12" s="5" t="s">
         <v>263</v>
       </c>
@@ -8472,7 +8450,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="15" customFormat="1" ht="60" spans="2:4">
+    <row r="15" customFormat="1" ht="58" spans="2:4">
       <c r="B15" s="5" t="s">
         <v>269</v>
       </c>
@@ -8483,7 +8461,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="16" customFormat="1" ht="30" spans="2:3">
+    <row r="16" customFormat="1" ht="29" spans="2:3">
       <c r="B16" s="5" t="s">
         <v>271</v>
       </c>
@@ -8491,7 +8469,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="17" ht="60" spans="2:4">
+    <row r="17" ht="58" spans="2:4">
       <c r="B17" t="s">
         <v>273</v>
       </c>
@@ -8510,7 +8488,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="19" ht="45" spans="2:5">
+    <row r="19" ht="43.5" spans="2:5">
       <c r="B19" t="s">
         <v>278</v>
       </c>
@@ -8544,7 +8522,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="22" ht="60" spans="2:5">
+    <row r="22" ht="58" spans="2:5">
       <c r="B22" t="s">
         <v>287</v>
       </c>
@@ -8613,14 +8591,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F32"/>
-  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9.14545454545454" defaultRowHeight="14.5" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="14.7142857142857" customWidth="1"/>
-    <col min="2" max="2" width="27.3333333333333" customWidth="1"/>
-    <col min="3" max="3" width="50.8857142857143" customWidth="1"/>
-    <col min="4" max="4" width="72.8571428571429" customWidth="1"/>
-    <col min="5" max="5" width="46.4285714285714" customWidth="1"/>
-    <col min="6" max="6" width="45.7142857142857" customWidth="1"/>
+    <col min="1" max="1" width="14.7181818181818" customWidth="1"/>
+    <col min="2" max="2" width="27.3363636363636" customWidth="1"/>
+    <col min="3" max="3" width="50.8818181818182" customWidth="1"/>
+    <col min="4" max="4" width="72.8545454545455" customWidth="1"/>
+    <col min="5" max="5" width="46.4272727272727" customWidth="1"/>
+    <col min="6" max="6" width="45.7181818181818" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" spans="1:6">
@@ -8678,7 +8656,7 @@
       </c>
       <c r="F5" s="4"/>
     </row>
-    <row r="6" customFormat="1" ht="30" spans="2:6">
+    <row r="6" customFormat="1" ht="29" spans="2:6">
       <c r="B6" s="4" t="s">
         <v>22</v>
       </c>
@@ -8727,7 +8705,7 @@
       <c r="D9" s="10"/>
       <c r="E9" s="8"/>
     </row>
-    <row r="10" ht="30" spans="2:5">
+    <row r="10" ht="29" spans="2:5">
       <c r="B10" s="4" t="s">
         <v>309</v>
       </c>
@@ -8737,7 +8715,7 @@
       <c r="D10" s="10"/>
       <c r="E10" s="8"/>
     </row>
-    <row r="11" ht="30" spans="2:5">
+    <row r="11" ht="29" spans="2:5">
       <c r="B11" s="4" t="s">
         <v>311</v>
       </c>
@@ -8747,7 +8725,7 @@
       <c r="D11" s="10"/>
       <c r="E11" s="8"/>
     </row>
-    <row r="12" ht="30" spans="2:5">
+    <row r="12" ht="29" spans="2:5">
       <c r="B12" s="4" t="s">
         <v>312</v>
       </c>
@@ -8781,7 +8759,7 @@
       <c r="D14" s="10"/>
       <c r="E14" s="22"/>
     </row>
-    <row r="15" customFormat="1" ht="30" spans="2:5">
+    <row r="15" customFormat="1" ht="29" spans="2:5">
       <c r="B15" s="4" t="s">
         <v>319</v>
       </c>
@@ -8791,7 +8769,7 @@
       <c r="D15" s="10"/>
       <c r="E15" s="22"/>
     </row>
-    <row r="16" customFormat="1" ht="30" spans="2:5">
+    <row r="16" customFormat="1" ht="29" spans="2:5">
       <c r="B16" s="4" t="s">
         <v>321</v>
       </c>
@@ -8801,7 +8779,7 @@
       <c r="D16" s="10"/>
       <c r="E16" s="4"/>
     </row>
-    <row r="17" customFormat="1" ht="30" spans="2:4">
+    <row r="17" customFormat="1" ht="29" spans="2:4">
       <c r="B17" s="4" t="s">
         <v>322</v>
       </c>
@@ -8810,7 +8788,7 @@
       </c>
       <c r="D17" s="10"/>
     </row>
-    <row r="18" ht="60" spans="2:5">
+    <row r="18" ht="58" spans="2:5">
       <c r="B18" s="5" t="s">
         <v>324</v>
       </c>
@@ -8858,7 +8836,7 @@
       </c>
       <c r="F21" s="4"/>
     </row>
-    <row r="22" customFormat="1" ht="30" spans="2:6">
+    <row r="22" customFormat="1" ht="29" spans="2:6">
       <c r="B22" s="4" t="s">
         <v>103</v>
       </c>
@@ -8868,7 +8846,7 @@
       <c r="D22" s="10"/>
       <c r="F22" s="4"/>
     </row>
-    <row r="23" customFormat="1" ht="90" spans="2:6">
+    <row r="23" customFormat="1" ht="87" spans="2:6">
       <c r="B23" s="4" t="s">
         <v>105</v>
       </c>
@@ -8881,7 +8859,7 @@
       </c>
       <c r="F23" s="4"/>
     </row>
-    <row r="24" customFormat="1" ht="120" spans="2:6">
+    <row r="24" customFormat="1" ht="116" spans="2:6">
       <c r="B24" s="4" t="s">
         <v>88</v>
       </c>
@@ -8894,7 +8872,7 @@
       <c r="E24" s="4"/>
       <c r="F24" s="4"/>
     </row>
-    <row r="25" customFormat="1" ht="75" spans="2:6">
+    <row r="25" customFormat="1" ht="72.5" spans="2:6">
       <c r="B25" s="4" t="s">
         <v>84</v>
       </c>
@@ -8907,7 +8885,7 @@
       </c>
       <c r="F25" s="4"/>
     </row>
-    <row r="26" customFormat="1" ht="30" spans="2:6">
+    <row r="26" customFormat="1" ht="29" spans="2:6">
       <c r="B26" s="4" t="s">
         <v>90</v>
       </c>
@@ -8918,7 +8896,7 @@
       <c r="E26" s="4"/>
       <c r="F26" s="4"/>
     </row>
-    <row r="27" customFormat="1" ht="30" spans="2:6">
+    <row r="27" customFormat="1" ht="29" spans="2:6">
       <c r="B27" s="4" t="s">
         <v>92</v>
       </c>
@@ -8929,7 +8907,7 @@
       <c r="E27" s="4"/>
       <c r="F27" s="4"/>
     </row>
-    <row r="28" customFormat="1" ht="30" spans="2:6">
+    <row r="28" customFormat="1" ht="29" spans="2:6">
       <c r="B28" s="4" t="s">
         <v>94</v>
       </c>
@@ -8940,7 +8918,7 @@
       <c r="E28" s="4"/>
       <c r="F28" s="4"/>
     </row>
-    <row r="29" customFormat="1" ht="30" spans="2:6">
+    <row r="29" customFormat="1" ht="29" spans="2:6">
       <c r="B29" s="4" t="s">
         <v>96</v>
       </c>
@@ -8951,7 +8929,7 @@
       <c r="E29" s="4"/>
       <c r="F29" s="4"/>
     </row>
-    <row r="30" customFormat="1" ht="30" spans="2:6">
+    <row r="30" customFormat="1" ht="29" spans="2:6">
       <c r="B30" s="4" t="s">
         <v>98</v>
       </c>
@@ -9000,13 +8978,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F21"/>
-  <sheetFormatPr defaultColWidth="8.88571428571429" defaultRowHeight="15" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="8.88181818181818" defaultRowHeight="14.5" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="14.7142857142857" customWidth="1"/>
-    <col min="2" max="2" width="33.8857142857143" customWidth="1"/>
-    <col min="3" max="3" width="46.8571428571429" customWidth="1"/>
-    <col min="4" max="4" width="57.1142857142857" customWidth="1"/>
-    <col min="5" max="5" width="54.7142857142857" customWidth="1"/>
+    <col min="1" max="1" width="14.7181818181818" customWidth="1"/>
+    <col min="2" max="2" width="33.8818181818182" customWidth="1"/>
+    <col min="3" max="3" width="46.8545454545455" customWidth="1"/>
+    <col min="4" max="4" width="57.1181818181818" customWidth="1"/>
+    <col min="5" max="5" width="54.7181818181818" customWidth="1"/>
     <col min="6" max="6" width="38" customWidth="1"/>
   </cols>
   <sheetData>
@@ -9030,7 +9008,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="2" ht="45" spans="1:1">
+    <row r="2" ht="43.5" spans="1:1">
       <c r="A2" s="21" t="s">
         <v>348</v>
       </c>
@@ -9068,7 +9046,7 @@
       <c r="E5" s="4"/>
       <c r="F5" s="4"/>
     </row>
-    <row r="6" ht="30" spans="2:6">
+    <row r="6" ht="29" spans="2:6">
       <c r="B6" s="17" t="s">
         <v>22</v>
       </c>
@@ -9090,7 +9068,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="8" ht="150" spans="2:5">
+    <row r="8" ht="145" spans="2:5">
       <c r="B8" s="5" t="s">
         <v>202</v>
       </c>
@@ -9115,7 +9093,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="10" ht="30" spans="2:4">
+    <row r="10" ht="29" spans="2:4">
       <c r="B10" s="5" t="s">
         <v>359</v>
       </c>
@@ -9134,7 +9112,7 @@
       <c r="D11" s="10"/>
       <c r="E11" s="8"/>
     </row>
-    <row r="12" ht="30" spans="2:4">
+    <row r="12" ht="29" spans="2:4">
       <c r="B12" s="5" t="s">
         <v>362</v>
       </c>
@@ -9154,7 +9132,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="14" ht="30" spans="2:4">
+    <row r="14" ht="29" spans="2:4">
       <c r="B14" s="4" t="s">
         <v>366</v>
       </c>
@@ -9175,7 +9153,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="16" ht="75" spans="2:4">
+    <row r="16" ht="58" spans="2:4">
       <c r="B16" s="5" t="s">
         <v>269</v>
       </c>
@@ -9186,7 +9164,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="17" ht="30" spans="2:3">
+    <row r="17" ht="29" spans="2:3">
       <c r="B17" s="5" t="s">
         <v>271</v>
       </c>
@@ -9194,7 +9172,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="18" ht="90" spans="2:5">
+    <row r="18" ht="87" spans="2:5">
       <c r="B18" t="s">
         <v>371</v>
       </c>
@@ -9254,14 +9232,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F31"/>
-  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9.14545454545454" defaultRowHeight="14.5" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="14.7142857142857" customWidth="1"/>
-    <col min="2" max="2" width="34.5714285714286" customWidth="1"/>
-    <col min="3" max="3" width="49.6666666666667" customWidth="1"/>
-    <col min="4" max="4" width="58.7142857142857" customWidth="1"/>
-    <col min="5" max="5" width="53.2857142857143" customWidth="1"/>
-    <col min="6" max="6" width="50.2857142857143" customWidth="1"/>
+    <col min="1" max="1" width="14.7181818181818" customWidth="1"/>
+    <col min="2" max="2" width="34.5727272727273" customWidth="1"/>
+    <col min="3" max="3" width="49.6636363636364" customWidth="1"/>
+    <col min="4" max="4" width="58.7181818181818" customWidth="1"/>
+    <col min="5" max="5" width="53.2818181818182" customWidth="1"/>
+    <col min="6" max="6" width="50.2818181818182" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" spans="1:6">
@@ -9305,7 +9283,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="4" ht="78" spans="1:4">
+    <row r="4" ht="82.5" spans="1:4">
       <c r="A4" s="1"/>
       <c r="B4" s="5" t="s">
         <v>16</v>
@@ -9329,7 +9307,7 @@
       <c r="E5" s="4"/>
       <c r="F5" s="4"/>
     </row>
-    <row r="6" customFormat="1" ht="30" spans="2:6">
+    <row r="6" customFormat="1" ht="29" spans="2:6">
       <c r="B6" s="17" t="s">
         <v>22</v>
       </c>
@@ -9351,7 +9329,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="8" ht="105" spans="2:5">
+    <row r="8" ht="101.5" spans="2:5">
       <c r="B8" s="5" t="s">
         <v>202</v>
       </c>
@@ -9376,7 +9354,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="10" ht="45" spans="2:5">
+    <row r="10" ht="43.5" spans="2:5">
       <c r="B10" s="5" t="s">
         <v>219</v>
       </c>
@@ -9388,7 +9366,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="11" ht="210" spans="2:5">
+    <row r="11" ht="203" spans="2:5">
       <c r="B11" s="5" t="s">
         <v>214</v>
       </c>
@@ -9397,7 +9375,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="12" ht="210" spans="2:5">
+    <row r="12" ht="203" spans="2:5">
       <c r="B12" s="5" t="s">
         <v>217</v>
       </c>
@@ -9447,7 +9425,7 @@
       <c r="D16" s="10"/>
       <c r="E16" s="9"/>
     </row>
-    <row r="17" ht="30" spans="2:5">
+    <row r="17" ht="29" spans="2:5">
       <c r="B17" s="5" t="s">
         <v>362</v>
       </c>
@@ -9459,7 +9437,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="18" ht="105" spans="2:5">
+    <row r="18" ht="101.5" spans="2:5">
       <c r="B18" s="4" t="s">
         <v>363</v>
       </c>
@@ -9473,7 +9451,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="19" ht="30" spans="2:3">
+    <row r="19" ht="29" spans="2:3">
       <c r="B19" s="4" t="s">
         <v>366</v>
       </c>
@@ -9481,7 +9459,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="20" ht="30" spans="2:3">
+    <row r="20" ht="29" spans="2:3">
       <c r="B20" s="4" t="s">
         <v>368</v>
       </c>
@@ -9501,7 +9479,7 @@
       </c>
       <c r="E21" s="8"/>
     </row>
-    <row r="22" ht="75" spans="2:5">
+    <row r="22" ht="72.5" spans="2:5">
       <c r="B22" s="5" t="s">
         <v>405</v>
       </c>
@@ -9513,7 +9491,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="23" ht="45" spans="2:5">
+    <row r="23" ht="43.5" spans="2:5">
       <c r="B23" s="5" t="s">
         <v>408</v>
       </c>
@@ -9522,7 +9500,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="24" ht="60" spans="2:4">
+    <row r="24" ht="58" spans="2:4">
       <c r="B24" s="5" t="s">
         <v>269</v>
       </c>
@@ -9533,7 +9511,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="25" ht="30" spans="2:3">
+    <row r="25" ht="29" spans="2:3">
       <c r="B25" s="5" t="s">
         <v>271</v>
       </c>
@@ -9541,7 +9519,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="26" ht="45" spans="2:4">
+    <row r="26" ht="43.5" spans="2:4">
       <c r="B26" s="5" t="s">
         <v>410</v>
       </c>
@@ -9552,7 +9530,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="27" ht="225" spans="2:5">
+    <row r="27" ht="203" spans="2:5">
       <c r="B27" s="5" t="s">
         <v>371</v>
       </c>
@@ -9564,7 +9542,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="28" ht="45" spans="2:4">
+    <row r="28" ht="43.5" spans="2:4">
       <c r="B28" s="5" t="s">
         <v>414</v>
       </c>
@@ -9624,14 +9602,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F21"/>
-  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9.14545454545454" defaultRowHeight="14.5" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="14.7142857142857" customWidth="1"/>
-    <col min="2" max="2" width="33.5714285714286" customWidth="1"/>
-    <col min="3" max="3" width="49.6666666666667" customWidth="1"/>
-    <col min="4" max="4" width="56.552380952381" customWidth="1"/>
-    <col min="5" max="5" width="53.2857142857143" customWidth="1"/>
-    <col min="6" max="6" width="47.5714285714286" customWidth="1"/>
+    <col min="1" max="1" width="14.7181818181818" customWidth="1"/>
+    <col min="2" max="2" width="33.5727272727273" customWidth="1"/>
+    <col min="3" max="3" width="49.6636363636364" customWidth="1"/>
+    <col min="4" max="4" width="56.5545454545455" customWidth="1"/>
+    <col min="5" max="5" width="53.2818181818182" customWidth="1"/>
+    <col min="6" max="6" width="47.5727272727273" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" spans="1:6">
@@ -9699,7 +9677,7 @@
       <c r="E5" s="4"/>
       <c r="F5" s="4"/>
     </row>
-    <row r="6" customFormat="1" ht="30" spans="2:6">
+    <row r="6" customFormat="1" ht="29" spans="2:6">
       <c r="B6" s="17" t="s">
         <v>22</v>
       </c>
@@ -9724,7 +9702,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="8" ht="105" spans="2:5">
+    <row r="8" ht="101.5" spans="2:5">
       <c r="B8" s="5" t="s">
         <v>202</v>
       </c>
@@ -9749,7 +9727,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="10" ht="165" spans="2:5">
+    <row r="10" ht="159.5" spans="2:5">
       <c r="B10" s="5" t="s">
         <v>356</v>
       </c>
@@ -9763,7 +9741,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="11" ht="180" spans="2:5">
+    <row r="11" ht="159.5" spans="2:5">
       <c r="B11" s="5" t="s">
         <v>359</v>
       </c>
@@ -9772,7 +9750,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="12" ht="150" spans="2:5">
+    <row r="12" ht="145" spans="2:5">
       <c r="B12" s="5" t="s">
         <v>361</v>
       </c>
@@ -9781,7 +9759,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="13" ht="75" spans="2:4">
+    <row r="13" ht="58" spans="2:4">
       <c r="B13" s="5" t="s">
         <v>269</v>
       </c>
@@ -9792,7 +9770,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="14" ht="30" spans="2:3">
+    <row r="14" ht="29" spans="2:3">
       <c r="B14" s="5" t="s">
         <v>271</v>
       </c>
@@ -9800,7 +9778,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="15" ht="45" spans="2:4">
+    <row r="15" ht="43.5" spans="2:4">
       <c r="B15" s="5" t="s">
         <v>410</v>
       </c>
@@ -9811,7 +9789,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="16" ht="225" spans="2:5">
+    <row r="16" ht="203" spans="2:5">
       <c r="B16" s="5" t="s">
         <v>371</v>
       </c>
@@ -9823,7 +9801,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="17" ht="45" spans="2:4">
+    <row r="17" ht="43.5" spans="2:4">
       <c r="B17" s="5" t="s">
         <v>414</v>
       </c>
@@ -9848,7 +9826,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="19" ht="165" spans="2:5">
+    <row r="19" ht="159.5" spans="2:5">
       <c r="B19" t="s">
         <v>426</v>
       </c>

--- a/support/specifications/ccda/CCDA to FHIR Conversion Spec - Epic.xlsx
+++ b/support/specifications/ccda/CCDA to FHIR Conversion Spec - Epic.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="8000" tabRatio="709" firstSheet="2" activeTab="2"/>
+    <workbookView windowWidth="28800" windowHeight="12180" tabRatio="709" firstSheet="2" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="Epic" sheetId="11" r:id="rId1"/>
@@ -591,6 +591,15 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>addr.use -&gt; use Mapping</t>
     </r>
     <r>
@@ -658,9 +667,37 @@
       }],</t>
   </si>
   <si>
-    <t>If telecom.value contains "tel:" then "phone".
-If telecom.value contains "mailto:" then "email".
-Otherwise "other"</t>
+    <r>
+      <t xml:space="preserve">If </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>telecom.value</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> contains 
+  "tel:" then "phone",
+  "mailto:" then "email",
+  "fax:" then "fax",
+  "pager:" then "pager",
+  "sms:" then "sms",
+  "http://" or "https://" or "www." then "url",
+  All Others "other".</t>
+    </r>
   </si>
   <si>
     <t>telecom -&gt; value</t>
@@ -676,6 +713,15 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>telecom -&gt; use Mapping</t>
     </r>
     <r>
@@ -3526,6 +3572,15 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>telecom -&gt; use Mapping</t>
     </r>
     <r>
@@ -3566,6 +3621,15 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>addr.use -&gt; use Mapping</t>
     </r>
     <r>
@@ -5247,6 +5311,15 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>addr.use -&gt; use Mapping</t>
     </r>
     <r>
@@ -5545,7 +5618,7 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
+      <b/>
       <sz val="11"/>
       <color rgb="FF00B050"/>
       <name val="Calibri"/>
@@ -5562,6 +5635,14 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color rgb="FFC00000"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
       <color rgb="FF00B050"/>
       <name val="Calibri"/>
       <charset val="134"/>
@@ -5570,7 +5651,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFC00000"/>
+      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -5600,14 +5681,6 @@
       <color rgb="FF00B050"/>
       <name val="Segoe UI"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="35">
@@ -6715,11 +6788,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultColWidth="8.88181818181818" defaultRowHeight="14.5" outlineLevelRow="6" outlineLevelCol="2"/>
+  <sheetFormatPr defaultColWidth="8.88571428571429" defaultRowHeight="15" outlineLevelRow="6" outlineLevelCol="2"/>
   <cols>
-    <col min="1" max="1" width="8.88181818181818" style="32"/>
-    <col min="2" max="2" width="35.2181818181818" customWidth="1"/>
-    <col min="3" max="3" width="92.6636363636364" customWidth="1"/>
+    <col min="1" max="1" width="8.88571428571429" style="32"/>
+    <col min="2" max="2" width="35.2190476190476" customWidth="1"/>
+    <col min="3" max="3" width="92.6666666666667" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:2">
@@ -6792,14 +6865,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F21"/>
-  <sheetFormatPr defaultColWidth="9.14545454545454" defaultRowHeight="14.5" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="14.7181818181818" customWidth="1"/>
-    <col min="2" max="2" width="33.5727272727273" customWidth="1"/>
-    <col min="3" max="3" width="49.6636363636364" customWidth="1"/>
-    <col min="4" max="4" width="56.5545454545455" customWidth="1"/>
-    <col min="5" max="5" width="53.2818181818182" customWidth="1"/>
-    <col min="6" max="6" width="47.5727272727273" customWidth="1"/>
+    <col min="1" max="1" width="14.7142857142857" customWidth="1"/>
+    <col min="2" max="2" width="33.5714285714286" customWidth="1"/>
+    <col min="3" max="3" width="49.6666666666667" customWidth="1"/>
+    <col min="4" max="4" width="56.552380952381" customWidth="1"/>
+    <col min="5" max="5" width="53.2857142857143" customWidth="1"/>
+    <col min="6" max="6" width="47.5714285714286" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" spans="1:6">
@@ -6842,7 +6915,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="4" ht="43.5" spans="2:6">
+    <row r="4" ht="60" spans="2:6">
       <c r="B4" s="5" t="s">
         <v>16</v>
       </c>
@@ -6864,7 +6937,7 @@
       <c r="D5"/>
       <c r="E5" s="8"/>
     </row>
-    <row r="6" customFormat="1" ht="29" spans="2:6">
+    <row r="6" customFormat="1" ht="30" spans="2:6">
       <c r="B6" s="5" t="s">
         <v>22</v>
       </c>
@@ -6892,7 +6965,7 @@
       <c r="E7" s="11"/>
       <c r="F7" s="4"/>
     </row>
-    <row r="8" ht="72.5" spans="2:5">
+    <row r="8" ht="75" spans="2:5">
       <c r="B8" s="4" t="s">
         <v>84</v>
       </c>
@@ -6906,7 +6979,7 @@
         <v>438</v>
       </c>
     </row>
-    <row r="9" ht="58" spans="2:5">
+    <row r="9" ht="60" spans="2:5">
       <c r="B9" s="4" t="s">
         <v>88</v>
       </c>
@@ -7032,14 +7105,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:G23"/>
-  <sheetFormatPr defaultColWidth="9.14545454545454" defaultRowHeight="14.5" outlineLevelCol="6"/>
+  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="14.7181818181818" customWidth="1"/>
-    <col min="2" max="2" width="28.3363636363636" customWidth="1"/>
-    <col min="3" max="3" width="65.4545454545455" customWidth="1"/>
-    <col min="4" max="4" width="46.2181818181818" customWidth="1"/>
-    <col min="5" max="5" width="61.2818181818182" customWidth="1"/>
-    <col min="6" max="6" width="46.2818181818182" customWidth="1"/>
+    <col min="1" max="1" width="14.7142857142857" customWidth="1"/>
+    <col min="2" max="2" width="28.3333333333333" customWidth="1"/>
+    <col min="3" max="3" width="65.4571428571429" customWidth="1"/>
+    <col min="4" max="4" width="46.2190476190476" customWidth="1"/>
+    <col min="5" max="5" width="61.2857142857143" customWidth="1"/>
+    <col min="6" max="6" width="46.2857142857143" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" spans="1:6">
@@ -7137,7 +7210,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="10" ht="29" spans="2:3">
+    <row r="10" ht="30" spans="2:3">
       <c r="B10" t="s">
         <v>30</v>
       </c>
@@ -7158,7 +7231,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="17" ht="72.5" spans="2:3">
+    <row r="17" ht="75" spans="2:3">
       <c r="B17" t="s">
         <v>35</v>
       </c>
@@ -7174,7 +7247,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="19" ht="72.5" spans="2:5">
+    <row r="19" ht="75" spans="2:5">
       <c r="B19" t="s">
         <v>39</v>
       </c>
@@ -7185,7 +7258,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="20" ht="29" spans="2:5">
+    <row r="20" ht="45" spans="2:5">
       <c r="B20" s="4" t="s">
         <v>42</v>
       </c>
@@ -7194,7 +7267,7 @@
       </c>
       <c r="E20" s="10"/>
     </row>
-    <row r="21" ht="58" spans="2:5">
+    <row r="21" ht="60" spans="2:5">
       <c r="B21" t="s">
         <v>44</v>
       </c>
@@ -7203,13 +7276,13 @@
       </c>
       <c r="E21" s="10"/>
     </row>
-    <row r="22" ht="29" spans="2:5">
+    <row r="22" ht="30" spans="2:5">
       <c r="B22" s="4" t="s">
         <v>46</v>
       </c>
       <c r="E22" s="8"/>
     </row>
-    <row r="23" ht="101.5" spans="2:7">
+    <row r="23" ht="105" spans="2:7">
       <c r="B23" s="31" t="s">
         <v>47</v>
       </c>
@@ -7237,13 +7310,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F68"/>
-  <sheetFormatPr defaultColWidth="8.88181818181818" defaultRowHeight="14.5" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="8.88571428571429" defaultRowHeight="15" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="14.7181818181818" customWidth="1"/>
-    <col min="2" max="2" width="41.7818181818182" style="4" customWidth="1"/>
-    <col min="3" max="3" width="63.8818181818182" style="4" customWidth="1"/>
-    <col min="4" max="4" width="81.2818181818182" style="4" customWidth="1"/>
-    <col min="5" max="5" width="48.4272727272727" style="4" customWidth="1"/>
+    <col min="1" max="1" width="14.7142857142857" customWidth="1"/>
+    <col min="2" max="2" width="41.7809523809524" style="4" customWidth="1"/>
+    <col min="3" max="3" width="63.8857142857143" style="4" customWidth="1"/>
+    <col min="4" max="4" width="81.2857142857143" style="4" customWidth="1"/>
+    <col min="5" max="5" width="48.4285714285714" style="4" customWidth="1"/>
     <col min="6" max="6" width="45" customWidth="1"/>
   </cols>
   <sheetData>
@@ -7309,7 +7382,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="7" ht="29" spans="2:4">
+    <row r="7" ht="30" spans="2:4">
       <c r="B7" s="4" t="s">
         <v>55</v>
       </c>
@@ -7320,7 +7393,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="8" ht="58" spans="2:5">
+    <row r="8" ht="60" spans="2:5">
       <c r="B8" s="4" t="s">
         <v>58</v>
       </c>
@@ -7376,7 +7449,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="13" ht="58" spans="2:4">
+    <row r="13" ht="60" spans="2:4">
       <c r="B13" s="4" t="s">
         <v>72</v>
       </c>
@@ -7387,7 +7460,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="14" ht="29" spans="2:4">
+    <row r="14" ht="30" spans="2:4">
       <c r="B14" s="4" t="s">
         <v>75</v>
       </c>
@@ -7398,7 +7471,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="15" ht="29" spans="2:4">
+    <row r="15" ht="30" spans="2:4">
       <c r="B15" s="4" t="s">
         <v>78</v>
       </c>
@@ -7420,7 +7493,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="17" ht="72.5" spans="2:5">
+    <row r="17" ht="75" spans="2:5">
       <c r="B17" s="4" t="s">
         <v>84</v>
       </c>
@@ -7434,7 +7507,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="18" ht="58" spans="2:4">
+    <row r="18" ht="60" spans="2:4">
       <c r="B18" s="4" t="s">
         <v>88</v>
       </c>
@@ -7488,14 +7561,14 @@
       </c>
       <c r="D23" s="12"/>
     </row>
-    <row r="24" ht="48" customHeight="1" spans="2:5">
+    <row r="24" ht="120" spans="2:5">
       <c r="B24" s="4" t="s">
         <v>100</v>
       </c>
       <c r="D24" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="E24" s="4" t="s">
+      <c r="E24" s="19" t="s">
         <v>102</v>
       </c>
     </row>
@@ -7507,7 +7580,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="26" ht="87" spans="2:5">
+    <row r="26" ht="90" spans="2:5">
       <c r="B26" s="4" t="s">
         <v>105</v>
       </c>
@@ -7518,7 +7591,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="27" ht="43.5" spans="2:5">
+    <row r="27" ht="45" spans="2:5">
       <c r="B27" s="4" t="s">
         <v>108</v>
       </c>
@@ -7532,7 +7605,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="28" spans="2:5">
+    <row r="28" ht="30" spans="2:5">
       <c r="B28" s="4" t="s">
         <v>112</v>
       </c>
@@ -7552,7 +7625,7 @@
       <c r="D29" s="14"/>
       <c r="E29" s="8"/>
     </row>
-    <row r="30" spans="2:5">
+    <row r="30" ht="30" spans="2:5">
       <c r="B30" s="4" t="s">
         <v>116</v>
       </c>
@@ -7572,7 +7645,7 @@
       <c r="D31" s="14"/>
       <c r="E31" s="8"/>
     </row>
-    <row r="32" ht="43.5" spans="2:5">
+    <row r="32" ht="45" spans="2:5">
       <c r="B32" s="4" t="s">
         <v>108</v>
       </c>
@@ -7586,7 +7659,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="33" spans="2:4">
+    <row r="33" ht="30" spans="2:4">
       <c r="B33" s="4" t="s">
         <v>112</v>
       </c>
@@ -7604,7 +7677,7 @@
       </c>
       <c r="D34" s="14"/>
     </row>
-    <row r="35" spans="2:4">
+    <row r="35" ht="30" spans="2:4">
       <c r="B35" s="4" t="s">
         <v>116</v>
       </c>
@@ -7633,7 +7706,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="38" ht="43.5" spans="2:5">
+    <row r="38" ht="45" spans="2:5">
       <c r="B38" s="4" t="s">
         <v>128</v>
       </c>
@@ -7645,7 +7718,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="39" ht="116" spans="2:6">
+    <row r="39" ht="120" spans="2:6">
       <c r="B39" s="4" t="s">
         <v>130</v>
       </c>
@@ -7656,7 +7729,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="40" ht="116" spans="2:6">
+    <row r="40" ht="120" spans="2:6">
       <c r="B40" s="4" t="s">
         <v>133</v>
       </c>
@@ -7703,7 +7776,7 @@
       </c>
       <c r="D44" s="10"/>
     </row>
-    <row r="45" ht="188.5" spans="2:5">
+    <row r="45" ht="195" spans="2:5">
       <c r="B45" s="17" t="s">
         <v>143</v>
       </c>
@@ -7717,7 +7790,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="46" ht="188.5" spans="2:5">
+    <row r="46" ht="195" spans="2:5">
       <c r="B46" s="17" t="s">
         <v>147</v>
       </c>
@@ -7731,7 +7804,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="47" ht="188.5" spans="2:5">
+    <row r="47" ht="195" spans="2:5">
       <c r="B47" s="17" t="s">
         <v>151</v>
       </c>
@@ -7783,7 +7856,7 @@
       <c r="D51" s="10"/>
       <c r="E51" s="4"/>
     </row>
-    <row r="52" ht="145" spans="2:5">
+    <row r="52" ht="150" spans="2:5">
       <c r="B52" s="10" t="s">
         <v>160</v>
       </c>
@@ -7857,7 +7930,7 @@
       <c r="D58" s="10"/>
       <c r="E58" s="8"/>
     </row>
-    <row r="59" ht="174" spans="2:5">
+    <row r="59" ht="180" spans="2:5">
       <c r="B59" s="10" t="s">
         <v>174</v>
       </c>
@@ -7871,7 +7944,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="60" ht="246.5" spans="2:6">
+    <row r="60" ht="255" spans="2:6">
       <c r="B60" s="4" t="s">
         <v>177</v>
       </c>
@@ -7902,7 +7975,7 @@
       <c r="D62" s="10"/>
       <c r="F62" s="4"/>
     </row>
-    <row r="63" ht="203" spans="2:6">
+    <row r="63" ht="210" spans="2:6">
       <c r="B63" s="4" t="s">
         <v>184</v>
       </c>
@@ -7980,14 +8053,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:G22"/>
-  <sheetFormatPr defaultColWidth="9.14545454545454" defaultRowHeight="14.5" outlineLevelCol="6"/>
+  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="14.7181818181818" customWidth="1"/>
-    <col min="2" max="2" width="30.8545454545455" customWidth="1"/>
-    <col min="3" max="3" width="63.4272727272727" customWidth="1"/>
-    <col min="4" max="4" width="70.7181818181818" customWidth="1"/>
-    <col min="5" max="5" width="52.4272727272727" customWidth="1"/>
-    <col min="6" max="6" width="57.5727272727273" customWidth="1"/>
+    <col min="1" max="1" width="14.7142857142857" customWidth="1"/>
+    <col min="2" max="2" width="30.8571428571429" customWidth="1"/>
+    <col min="3" max="3" width="63.4285714285714" customWidth="1"/>
+    <col min="4" max="4" width="70.7142857142857" customWidth="1"/>
+    <col min="5" max="5" width="52.4285714285714" customWidth="1"/>
+    <col min="6" max="6" width="57.5714285714286" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" spans="1:6">
@@ -8029,7 +8102,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="4" ht="58" spans="2:7">
+    <row r="4" ht="60" spans="2:7">
       <c r="B4" s="5" t="s">
         <v>16</v>
       </c>
@@ -8060,7 +8133,7 @@
       </c>
       <c r="E6" s="26"/>
     </row>
-    <row r="7" ht="116" spans="2:6">
+    <row r="7" ht="120" spans="2:6">
       <c r="B7" s="5" t="s">
         <v>202</v>
       </c>
@@ -8113,7 +8186,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="11" ht="203" spans="2:5">
+    <row r="11" ht="225" spans="2:5">
       <c r="B11" s="5" t="s">
         <v>214</v>
       </c>
@@ -8149,7 +8222,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="14" ht="29" spans="2:5">
+    <row r="14" ht="30" spans="2:5">
       <c r="B14" s="5" t="s">
         <v>221</v>
       </c>
@@ -8163,7 +8236,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="15" ht="43.5" spans="2:5">
+    <row r="15" ht="45" spans="2:5">
       <c r="B15" s="5" t="s">
         <v>225</v>
       </c>
@@ -8177,7 +8250,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="16" ht="43.5" spans="2:5">
+    <row r="16" ht="45" spans="2:5">
       <c r="B16" s="5" t="s">
         <v>229</v>
       </c>
@@ -8189,7 +8262,7 @@
       </c>
       <c r="E16" s="8"/>
     </row>
-    <row r="17" ht="43.5" spans="2:5">
+    <row r="17" ht="45" spans="2:5">
       <c r="B17" s="5" t="s">
         <v>232</v>
       </c>
@@ -8201,7 +8274,7 @@
       </c>
       <c r="E17" s="8"/>
     </row>
-    <row r="18" ht="43.5" spans="2:5">
+    <row r="18" ht="45" spans="2:5">
       <c r="B18" t="s">
         <v>235</v>
       </c>
@@ -8215,7 +8288,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="19" ht="58" spans="2:5">
+    <row r="19" ht="60" spans="2:5">
       <c r="B19" s="5" t="s">
         <v>238</v>
       </c>
@@ -8280,14 +8353,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F26"/>
-  <sheetFormatPr defaultColWidth="9.14545454545454" defaultRowHeight="14.5" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="14.7181818181818" customWidth="1"/>
-    <col min="2" max="2" width="35.1454545454545" customWidth="1"/>
-    <col min="3" max="3" width="42.2818181818182" style="4" customWidth="1"/>
-    <col min="4" max="4" width="73.5727272727273" customWidth="1"/>
+    <col min="1" max="1" width="14.7142857142857" customWidth="1"/>
+    <col min="2" max="2" width="35.1428571428571" customWidth="1"/>
+    <col min="3" max="3" width="42.2857142857143" style="4" customWidth="1"/>
+    <col min="4" max="4" width="73.5714285714286" customWidth="1"/>
     <col min="5" max="5" width="53" customWidth="1"/>
-    <col min="6" max="6" width="51.7181818181818" customWidth="1"/>
+    <col min="6" max="6" width="51.7142857142857" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" spans="1:6">
@@ -8329,7 +8402,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="4" ht="72.5" spans="1:5">
+    <row r="4" ht="75" spans="1:5">
       <c r="A4" s="1"/>
       <c r="B4" s="5" t="s">
         <v>16</v>
@@ -8356,7 +8429,7 @@
       <c r="E5" s="4"/>
       <c r="F5" s="4"/>
     </row>
-    <row r="6" customFormat="1" ht="29" spans="2:6">
+    <row r="6" customFormat="1" ht="30" spans="2:6">
       <c r="B6" s="17" t="s">
         <v>22</v>
       </c>
@@ -8367,7 +8440,7 @@
       <c r="E6" s="4"/>
       <c r="F6" s="4"/>
     </row>
-    <row r="7" ht="159.5" spans="2:5">
+    <row r="7" ht="165" spans="2:5">
       <c r="B7" s="5" t="s">
         <v>202</v>
       </c>
@@ -8393,7 +8466,7 @@
       </c>
       <c r="E8" s="9"/>
     </row>
-    <row r="9" ht="29" spans="2:5">
+    <row r="9" ht="30" spans="2:5">
       <c r="B9" s="5" t="s">
         <v>256</v>
       </c>
@@ -8413,7 +8486,7 @@
       <c r="D10" s="10"/>
       <c r="E10" s="9"/>
     </row>
-    <row r="11" ht="29" spans="2:4">
+    <row r="11" ht="30" spans="2:4">
       <c r="B11" s="5" t="s">
         <v>260</v>
       </c>
@@ -8424,7 +8497,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="12" ht="58" spans="2:5">
+    <row r="12" ht="60" spans="2:5">
       <c r="B12" s="5" t="s">
         <v>263</v>
       </c>
@@ -8450,7 +8523,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="15" customFormat="1" ht="58" spans="2:4">
+    <row r="15" customFormat="1" ht="60" spans="2:4">
       <c r="B15" s="5" t="s">
         <v>269</v>
       </c>
@@ -8461,7 +8534,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="16" customFormat="1" ht="29" spans="2:3">
+    <row r="16" customFormat="1" ht="30" spans="2:3">
       <c r="B16" s="5" t="s">
         <v>271</v>
       </c>
@@ -8469,7 +8542,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="17" ht="58" spans="2:4">
+    <row r="17" ht="60" spans="2:4">
       <c r="B17" t="s">
         <v>273</v>
       </c>
@@ -8488,7 +8561,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="19" ht="43.5" spans="2:5">
+    <row r="19" ht="45" spans="2:5">
       <c r="B19" t="s">
         <v>278</v>
       </c>
@@ -8522,7 +8595,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="22" ht="58" spans="2:5">
+    <row r="22" ht="60" spans="2:5">
       <c r="B22" t="s">
         <v>287</v>
       </c>
@@ -8591,14 +8664,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F32"/>
-  <sheetFormatPr defaultColWidth="9.14545454545454" defaultRowHeight="14.5" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="14.7181818181818" customWidth="1"/>
-    <col min="2" max="2" width="27.3363636363636" customWidth="1"/>
-    <col min="3" max="3" width="50.8818181818182" customWidth="1"/>
-    <col min="4" max="4" width="72.8545454545455" customWidth="1"/>
-    <col min="5" max="5" width="46.4272727272727" customWidth="1"/>
-    <col min="6" max="6" width="45.7181818181818" customWidth="1"/>
+    <col min="1" max="1" width="14.7142857142857" customWidth="1"/>
+    <col min="2" max="2" width="27.3333333333333" customWidth="1"/>
+    <col min="3" max="3" width="50.8857142857143" customWidth="1"/>
+    <col min="4" max="4" width="72.8571428571429" customWidth="1"/>
+    <col min="5" max="5" width="46.4285714285714" customWidth="1"/>
+    <col min="6" max="6" width="45.7142857142857" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" spans="1:6">
@@ -8656,7 +8729,7 @@
       </c>
       <c r="F5" s="4"/>
     </row>
-    <row r="6" customFormat="1" ht="29" spans="2:6">
+    <row r="6" customFormat="1" ht="30" spans="2:6">
       <c r="B6" s="4" t="s">
         <v>22</v>
       </c>
@@ -8705,7 +8778,7 @@
       <c r="D9" s="10"/>
       <c r="E9" s="8"/>
     </row>
-    <row r="10" ht="29" spans="2:5">
+    <row r="10" ht="30" spans="2:5">
       <c r="B10" s="4" t="s">
         <v>309</v>
       </c>
@@ -8715,7 +8788,7 @@
       <c r="D10" s="10"/>
       <c r="E10" s="8"/>
     </row>
-    <row r="11" ht="29" spans="2:5">
+    <row r="11" ht="30" spans="2:5">
       <c r="B11" s="4" t="s">
         <v>311</v>
       </c>
@@ -8725,7 +8798,7 @@
       <c r="D11" s="10"/>
       <c r="E11" s="8"/>
     </row>
-    <row r="12" ht="29" spans="2:5">
+    <row r="12" ht="30" spans="2:5">
       <c r="B12" s="4" t="s">
         <v>312</v>
       </c>
@@ -8759,7 +8832,7 @@
       <c r="D14" s="10"/>
       <c r="E14" s="22"/>
     </row>
-    <row r="15" customFormat="1" ht="29" spans="2:5">
+    <row r="15" customFormat="1" ht="30" spans="2:5">
       <c r="B15" s="4" t="s">
         <v>319</v>
       </c>
@@ -8769,7 +8842,7 @@
       <c r="D15" s="10"/>
       <c r="E15" s="22"/>
     </row>
-    <row r="16" customFormat="1" ht="29" spans="2:5">
+    <row r="16" customFormat="1" ht="30" spans="2:5">
       <c r="B16" s="4" t="s">
         <v>321</v>
       </c>
@@ -8779,7 +8852,7 @@
       <c r="D16" s="10"/>
       <c r="E16" s="4"/>
     </row>
-    <row r="17" customFormat="1" ht="29" spans="2:4">
+    <row r="17" customFormat="1" ht="30" spans="2:4">
       <c r="B17" s="4" t="s">
         <v>322</v>
       </c>
@@ -8788,7 +8861,7 @@
       </c>
       <c r="D17" s="10"/>
     </row>
-    <row r="18" ht="58" spans="2:5">
+    <row r="18" ht="60" spans="2:5">
       <c r="B18" s="5" t="s">
         <v>324</v>
       </c>
@@ -8823,7 +8896,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="21" customFormat="1" ht="50" customHeight="1" spans="2:6">
+    <row r="21" customFormat="1" ht="120" spans="2:6">
       <c r="B21" s="4" t="s">
         <v>100</v>
       </c>
@@ -8831,12 +8904,12 @@
       <c r="D21" s="10" t="s">
         <v>333</v>
       </c>
-      <c r="E21" s="4" t="s">
+      <c r="E21" s="19" t="s">
         <v>102</v>
       </c>
       <c r="F21" s="4"/>
     </row>
-    <row r="22" customFormat="1" ht="29" spans="2:6">
+    <row r="22" customFormat="1" ht="30" spans="2:6">
       <c r="B22" s="4" t="s">
         <v>103</v>
       </c>
@@ -8846,7 +8919,7 @@
       <c r="D22" s="10"/>
       <c r="F22" s="4"/>
     </row>
-    <row r="23" customFormat="1" ht="87" spans="2:6">
+    <row r="23" customFormat="1" ht="90" spans="2:6">
       <c r="B23" s="4" t="s">
         <v>105</v>
       </c>
@@ -8859,7 +8932,7 @@
       </c>
       <c r="F23" s="4"/>
     </row>
-    <row r="24" customFormat="1" ht="116" spans="2:6">
+    <row r="24" customFormat="1" ht="120" spans="2:6">
       <c r="B24" s="4" t="s">
         <v>88</v>
       </c>
@@ -8872,7 +8945,7 @@
       <c r="E24" s="4"/>
       <c r="F24" s="4"/>
     </row>
-    <row r="25" customFormat="1" ht="72.5" spans="2:6">
+    <row r="25" customFormat="1" ht="75" spans="2:6">
       <c r="B25" s="4" t="s">
         <v>84</v>
       </c>
@@ -8885,7 +8958,7 @@
       </c>
       <c r="F25" s="4"/>
     </row>
-    <row r="26" customFormat="1" ht="29" spans="2:6">
+    <row r="26" customFormat="1" ht="30" spans="2:6">
       <c r="B26" s="4" t="s">
         <v>90</v>
       </c>
@@ -8896,7 +8969,7 @@
       <c r="E26" s="4"/>
       <c r="F26" s="4"/>
     </row>
-    <row r="27" customFormat="1" ht="29" spans="2:6">
+    <row r="27" customFormat="1" ht="30" spans="2:6">
       <c r="B27" s="4" t="s">
         <v>92</v>
       </c>
@@ -8907,7 +8980,7 @@
       <c r="E27" s="4"/>
       <c r="F27" s="4"/>
     </row>
-    <row r="28" customFormat="1" ht="29" spans="2:6">
+    <row r="28" customFormat="1" ht="30" spans="2:6">
       <c r="B28" s="4" t="s">
         <v>94</v>
       </c>
@@ -8918,7 +8991,7 @@
       <c r="E28" s="4"/>
       <c r="F28" s="4"/>
     </row>
-    <row r="29" customFormat="1" ht="29" spans="2:6">
+    <row r="29" customFormat="1" ht="30" spans="2:6">
       <c r="B29" s="4" t="s">
         <v>96</v>
       </c>
@@ -8929,7 +9002,7 @@
       <c r="E29" s="4"/>
       <c r="F29" s="4"/>
     </row>
-    <row r="30" customFormat="1" ht="29" spans="2:6">
+    <row r="30" customFormat="1" ht="30" spans="2:6">
       <c r="B30" s="4" t="s">
         <v>98</v>
       </c>
@@ -8978,13 +9051,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F21"/>
-  <sheetFormatPr defaultColWidth="8.88181818181818" defaultRowHeight="14.5" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="8.88571428571429" defaultRowHeight="15" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="14.7181818181818" customWidth="1"/>
-    <col min="2" max="2" width="33.8818181818182" customWidth="1"/>
-    <col min="3" max="3" width="46.8545454545455" customWidth="1"/>
-    <col min="4" max="4" width="57.1181818181818" customWidth="1"/>
-    <col min="5" max="5" width="54.7181818181818" customWidth="1"/>
+    <col min="1" max="1" width="14.7142857142857" customWidth="1"/>
+    <col min="2" max="2" width="33.8857142857143" customWidth="1"/>
+    <col min="3" max="3" width="46.8571428571429" customWidth="1"/>
+    <col min="4" max="4" width="57.1142857142857" customWidth="1"/>
+    <col min="5" max="5" width="54.7142857142857" customWidth="1"/>
     <col min="6" max="6" width="38" customWidth="1"/>
   </cols>
   <sheetData>
@@ -9008,7 +9081,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="2" ht="43.5" spans="1:1">
+    <row r="2" ht="45" spans="1:1">
       <c r="A2" s="21" t="s">
         <v>348</v>
       </c>
@@ -9046,7 +9119,7 @@
       <c r="E5" s="4"/>
       <c r="F5" s="4"/>
     </row>
-    <row r="6" ht="29" spans="2:6">
+    <row r="6" ht="30" spans="2:6">
       <c r="B6" s="17" t="s">
         <v>22</v>
       </c>
@@ -9068,7 +9141,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="8" ht="145" spans="2:5">
+    <row r="8" ht="150" spans="2:5">
       <c r="B8" s="5" t="s">
         <v>202</v>
       </c>
@@ -9093,7 +9166,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="10" ht="29" spans="2:4">
+    <row r="10" ht="30" spans="2:4">
       <c r="B10" s="5" t="s">
         <v>359</v>
       </c>
@@ -9112,7 +9185,7 @@
       <c r="D11" s="10"/>
       <c r="E11" s="8"/>
     </row>
-    <row r="12" ht="29" spans="2:4">
+    <row r="12" ht="30" spans="2:4">
       <c r="B12" s="5" t="s">
         <v>362</v>
       </c>
@@ -9132,7 +9205,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="14" ht="29" spans="2:4">
+    <row r="14" ht="30" spans="2:4">
       <c r="B14" s="4" t="s">
         <v>366</v>
       </c>
@@ -9153,7 +9226,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="16" ht="58" spans="2:4">
+    <row r="16" ht="75" spans="2:4">
       <c r="B16" s="5" t="s">
         <v>269</v>
       </c>
@@ -9164,7 +9237,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="17" ht="29" spans="2:3">
+    <row r="17" ht="30" spans="2:3">
       <c r="B17" s="5" t="s">
         <v>271</v>
       </c>
@@ -9172,7 +9245,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="18" ht="87" spans="2:5">
+    <row r="18" ht="90" spans="2:5">
       <c r="B18" t="s">
         <v>371</v>
       </c>
@@ -9232,14 +9305,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F31"/>
-  <sheetFormatPr defaultColWidth="9.14545454545454" defaultRowHeight="14.5" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="14.7181818181818" customWidth="1"/>
-    <col min="2" max="2" width="34.5727272727273" customWidth="1"/>
-    <col min="3" max="3" width="49.6636363636364" customWidth="1"/>
-    <col min="4" max="4" width="58.7181818181818" customWidth="1"/>
-    <col min="5" max="5" width="53.2818181818182" customWidth="1"/>
-    <col min="6" max="6" width="50.2818181818182" customWidth="1"/>
+    <col min="1" max="1" width="14.7142857142857" customWidth="1"/>
+    <col min="2" max="2" width="34.5714285714286" customWidth="1"/>
+    <col min="3" max="3" width="49.6666666666667" customWidth="1"/>
+    <col min="4" max="4" width="58.7142857142857" customWidth="1"/>
+    <col min="5" max="5" width="53.2857142857143" customWidth="1"/>
+    <col min="6" max="6" width="50.2857142857143" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" spans="1:6">
@@ -9283,7 +9356,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="4" ht="82.5" spans="1:4">
+    <row r="4" ht="78" spans="1:4">
       <c r="A4" s="1"/>
       <c r="B4" s="5" t="s">
         <v>16</v>
@@ -9307,7 +9380,7 @@
       <c r="E5" s="4"/>
       <c r="F5" s="4"/>
     </row>
-    <row r="6" customFormat="1" ht="29" spans="2:6">
+    <row r="6" customFormat="1" ht="30" spans="2:6">
       <c r="B6" s="17" t="s">
         <v>22</v>
       </c>
@@ -9329,7 +9402,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="8" ht="101.5" spans="2:5">
+    <row r="8" ht="105" spans="2:5">
       <c r="B8" s="5" t="s">
         <v>202</v>
       </c>
@@ -9354,7 +9427,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="10" ht="43.5" spans="2:5">
+    <row r="10" ht="45" spans="2:5">
       <c r="B10" s="5" t="s">
         <v>219</v>
       </c>
@@ -9366,7 +9439,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="11" ht="203" spans="2:5">
+    <row r="11" ht="210" spans="2:5">
       <c r="B11" s="5" t="s">
         <v>214</v>
       </c>
@@ -9375,7 +9448,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="12" ht="203" spans="2:5">
+    <row r="12" ht="210" spans="2:5">
       <c r="B12" s="5" t="s">
         <v>217</v>
       </c>
@@ -9425,7 +9498,7 @@
       <c r="D16" s="10"/>
       <c r="E16" s="9"/>
     </row>
-    <row r="17" ht="29" spans="2:5">
+    <row r="17" ht="30" spans="2:5">
       <c r="B17" s="5" t="s">
         <v>362</v>
       </c>
@@ -9437,7 +9510,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="18" ht="101.5" spans="2:5">
+    <row r="18" ht="105" spans="2:5">
       <c r="B18" s="4" t="s">
         <v>363</v>
       </c>
@@ -9451,7 +9524,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="19" ht="29" spans="2:3">
+    <row r="19" ht="30" spans="2:3">
       <c r="B19" s="4" t="s">
         <v>366</v>
       </c>
@@ -9459,7 +9532,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="20" ht="29" spans="2:3">
+    <row r="20" ht="30" spans="2:3">
       <c r="B20" s="4" t="s">
         <v>368</v>
       </c>
@@ -9479,7 +9552,7 @@
       </c>
       <c r="E21" s="8"/>
     </row>
-    <row r="22" ht="72.5" spans="2:5">
+    <row r="22" ht="75" spans="2:5">
       <c r="B22" s="5" t="s">
         <v>405</v>
       </c>
@@ -9491,7 +9564,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="23" ht="43.5" spans="2:5">
+    <row r="23" ht="45" spans="2:5">
       <c r="B23" s="5" t="s">
         <v>408</v>
       </c>
@@ -9500,7 +9573,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="24" ht="58" spans="2:4">
+    <row r="24" ht="60" spans="2:4">
       <c r="B24" s="5" t="s">
         <v>269</v>
       </c>
@@ -9511,7 +9584,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="25" ht="29" spans="2:3">
+    <row r="25" ht="30" spans="2:3">
       <c r="B25" s="5" t="s">
         <v>271</v>
       </c>
@@ -9519,7 +9592,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="26" ht="43.5" spans="2:4">
+    <row r="26" ht="45" spans="2:4">
       <c r="B26" s="5" t="s">
         <v>410</v>
       </c>
@@ -9530,7 +9603,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="27" ht="203" spans="2:5">
+    <row r="27" ht="225" spans="2:5">
       <c r="B27" s="5" t="s">
         <v>371</v>
       </c>
@@ -9542,7 +9615,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="28" ht="43.5" spans="2:4">
+    <row r="28" ht="45" spans="2:4">
       <c r="B28" s="5" t="s">
         <v>414</v>
       </c>
@@ -9602,14 +9675,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F21"/>
-  <sheetFormatPr defaultColWidth="9.14545454545454" defaultRowHeight="14.5" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="14.7181818181818" customWidth="1"/>
-    <col min="2" max="2" width="33.5727272727273" customWidth="1"/>
-    <col min="3" max="3" width="49.6636363636364" customWidth="1"/>
-    <col min="4" max="4" width="56.5545454545455" customWidth="1"/>
-    <col min="5" max="5" width="53.2818181818182" customWidth="1"/>
-    <col min="6" max="6" width="47.5727272727273" customWidth="1"/>
+    <col min="1" max="1" width="14.7142857142857" customWidth="1"/>
+    <col min="2" max="2" width="33.5714285714286" customWidth="1"/>
+    <col min="3" max="3" width="49.6666666666667" customWidth="1"/>
+    <col min="4" max="4" width="56.552380952381" customWidth="1"/>
+    <col min="5" max="5" width="53.2857142857143" customWidth="1"/>
+    <col min="6" max="6" width="47.5714285714286" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" spans="1:6">
@@ -9677,7 +9750,7 @@
       <c r="E5" s="4"/>
       <c r="F5" s="4"/>
     </row>
-    <row r="6" customFormat="1" ht="29" spans="2:6">
+    <row r="6" customFormat="1" ht="30" spans="2:6">
       <c r="B6" s="17" t="s">
         <v>22</v>
       </c>
@@ -9702,7 +9775,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="8" ht="101.5" spans="2:5">
+    <row r="8" ht="105" spans="2:5">
       <c r="B8" s="5" t="s">
         <v>202</v>
       </c>
@@ -9727,7 +9800,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="10" ht="159.5" spans="2:5">
+    <row r="10" ht="165" spans="2:5">
       <c r="B10" s="5" t="s">
         <v>356</v>
       </c>
@@ -9741,7 +9814,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="11" ht="159.5" spans="2:5">
+    <row r="11" ht="180" spans="2:5">
       <c r="B11" s="5" t="s">
         <v>359</v>
       </c>
@@ -9750,7 +9823,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="12" ht="145" spans="2:5">
+    <row r="12" ht="150" spans="2:5">
       <c r="B12" s="5" t="s">
         <v>361</v>
       </c>
@@ -9759,7 +9832,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="13" ht="58" spans="2:4">
+    <row r="13" ht="75" spans="2:4">
       <c r="B13" s="5" t="s">
         <v>269</v>
       </c>
@@ -9770,7 +9843,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="14" ht="29" spans="2:3">
+    <row r="14" ht="30" spans="2:3">
       <c r="B14" s="5" t="s">
         <v>271</v>
       </c>
@@ -9778,7 +9851,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="15" ht="43.5" spans="2:4">
+    <row r="15" ht="45" spans="2:4">
       <c r="B15" s="5" t="s">
         <v>410</v>
       </c>
@@ -9789,7 +9862,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="16" ht="203" spans="2:5">
+    <row r="16" ht="225" spans="2:5">
       <c r="B16" s="5" t="s">
         <v>371</v>
       </c>
@@ -9801,7 +9874,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="17" ht="43.5" spans="2:4">
+    <row r="17" ht="45" spans="2:4">
       <c r="B17" s="5" t="s">
         <v>414</v>
       </c>
@@ -9826,7 +9899,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="19" ht="159.5" spans="2:5">
+    <row r="19" ht="165" spans="2:5">
       <c r="B19" t="s">
         <v>426</v>
       </c>

--- a/support/specifications/ccda/CCDA to FHIR Conversion Spec - Epic.xlsx
+++ b/support/specifications/ccda/CCDA to FHIR Conversion Spec - Epic.xlsx
@@ -668,6 +668,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">If </t>
     </r>
     <r>
@@ -2189,13 +2196,6 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF00B050"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
       <t xml:space="preserve">For </t>
     </r>
     <r>
@@ -3377,7 +3377,7 @@
     <t>name</t>
   </si>
   <si>
-    <t>ClinicalDocument.component.structuredBody.component.section[@ID='encounters'].entry[1].encounter.participant[@typeCode='LOC'].participantRole[@classCode='SDLOC'].playingEntity.name</t>
+    <t>ClinicalDocument.component.structuredBody.component.section[code[@code='46240-8']].entry[1].encounter.participant[@typeCode='LOC'].participantRole[@classCode='SDLOC'].playingEntity.name</t>
   </si>
   <si>
     <t>"name" : "Care Ridge SCN",</t>
@@ -5635,22 +5635,6 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFC00000"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF00B050"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <charset val="134"/>
@@ -5681,6 +5665,22 @@
       <color rgb="FF00B050"/>
       <name val="Segoe UI"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFC00000"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF00B050"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="35">
@@ -6267,7 +6267,7 @@
     <cellStyle name="Note" xfId="8" builtinId="10"/>
     <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
     <cellStyle name="Title" xfId="10" builtinId="15"/>
-    <cellStyle name="CExplanatory Text" xfId="11" builtinId="53"/>
+    <cellStyle name="Explanatory Text" xfId="11" builtinId="53"/>
     <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
     <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
     <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
@@ -6795,7 +6795,7 @@
     <col min="3" max="3" width="92.6666666666667" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:2">
+    <row r="1" spans="1:3">
       <c r="B1" s="33" t="s">
         <v>0</v>
       </c>
@@ -6907,7 +6907,7 @@
       <c r="E2" s="3"/>
       <c r="F2" s="3"/>
     </row>
-    <row r="3" spans="2:3">
+    <row r="3" spans="1:6">
       <c r="B3" s="4" t="s">
         <v>14</v>
       </c>
@@ -6915,7 +6915,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="4" ht="60" spans="2:6">
+    <row r="4" ht="60" spans="1:6">
       <c r="B4" s="5" t="s">
         <v>16</v>
       </c>
@@ -6927,7 +6927,7 @@
       </c>
       <c r="F4" s="7"/>
     </row>
-    <row r="5" customFormat="1" spans="2:5">
+    <row r="5" customFormat="1" spans="1:6">
       <c r="B5" s="5" t="s">
         <v>19</v>
       </c>
@@ -6937,7 +6937,7 @@
       <c r="D5"/>
       <c r="E5" s="8"/>
     </row>
-    <row r="6" customFormat="1" ht="30" spans="2:6">
+    <row r="6" customFormat="1" ht="30" spans="1:6">
       <c r="B6" s="5" t="s">
         <v>22</v>
       </c>
@@ -6952,7 +6952,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="7" spans="2:6">
+    <row r="7" spans="1:6">
       <c r="B7" s="5" t="s">
         <v>324</v>
       </c>
@@ -6965,7 +6965,7 @@
       <c r="E7" s="11"/>
       <c r="F7" s="4"/>
     </row>
-    <row r="8" ht="75" spans="2:5">
+    <row r="8" ht="75" spans="1:6">
       <c r="B8" s="4" t="s">
         <v>84</v>
       </c>
@@ -6979,7 +6979,7 @@
         <v>438</v>
       </c>
     </row>
-    <row r="9" ht="60" spans="2:5">
+    <row r="9" ht="60" spans="1:6">
       <c r="B9" s="4" t="s">
         <v>88</v>
       </c>
@@ -6989,7 +6989,7 @@
       <c r="D9" s="12"/>
       <c r="E9" s="4"/>
     </row>
-    <row r="10" spans="2:5">
+    <row r="10" spans="1:6">
       <c r="B10" s="4" t="s">
         <v>90</v>
       </c>
@@ -6999,7 +6999,7 @@
       <c r="D10" s="12"/>
       <c r="E10" s="4"/>
     </row>
-    <row r="11" spans="2:5">
+    <row r="11" spans="1:6">
       <c r="B11" s="4" t="s">
         <v>92</v>
       </c>
@@ -7009,7 +7009,7 @@
       <c r="D11" s="12"/>
       <c r="E11" s="4"/>
     </row>
-    <row r="12" spans="2:5">
+    <row r="12" spans="1:6">
       <c r="B12" s="4" t="s">
         <v>94</v>
       </c>
@@ -7019,7 +7019,7 @@
       <c r="D12" s="12"/>
       <c r="E12" s="4"/>
     </row>
-    <row r="13" spans="2:5">
+    <row r="13" spans="1:6">
       <c r="B13" s="4" t="s">
         <v>96</v>
       </c>
@@ -7029,7 +7029,7 @@
       <c r="D13" s="12"/>
       <c r="E13" s="4"/>
     </row>
-    <row r="14" spans="2:5">
+    <row r="14" spans="1:6">
       <c r="B14" s="4" t="s">
         <v>98</v>
       </c>
@@ -7039,7 +7039,7 @@
       <c r="D14" s="12"/>
       <c r="E14" s="4"/>
     </row>
-    <row r="15" spans="2:5">
+    <row r="15" spans="1:6">
       <c r="B15" s="4" t="s">
         <v>445</v>
       </c>
@@ -7049,7 +7049,7 @@
       <c r="D15" s="12"/>
       <c r="E15" s="4"/>
     </row>
-    <row r="16" spans="2:6">
+    <row r="16" spans="1:6">
       <c r="B16" s="4" t="s">
         <v>192</v>
       </c>
@@ -7073,19 +7073,19 @@
       <c r="E17" s="8"/>
       <c r="F17" s="4"/>
     </row>
-    <row r="18" spans="5:6">
+    <row r="18" spans="2:6">
       <c r="E18" s="8"/>
       <c r="F18" s="15"/>
     </row>
-    <row r="19" spans="4:4">
+    <row r="19" spans="2:6">
       <c r="D19" s="4"/>
     </row>
-    <row r="20" spans="2:4">
+    <row r="20" spans="2:6">
       <c r="B20" s="4"/>
       <c r="C20" s="4"/>
       <c r="D20" s="16"/>
     </row>
-    <row r="21" spans="2:4">
+    <row r="21" spans="2:6">
       <c r="B21" s="4"/>
       <c r="C21" s="4"/>
       <c r="D21" s="16"/>
@@ -7135,12 +7135,12 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:1">
+    <row r="2" spans="1:6">
       <c r="A2" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:6">
       <c r="A3" s="1"/>
       <c r="B3" t="s">
         <v>14</v>
@@ -7149,7 +7149,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:4">
+    <row r="4" spans="1:6">
       <c r="A4" s="1"/>
       <c r="B4" t="s">
         <v>16</v>
@@ -7161,7 +7161,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="5" s="27" customFormat="1" ht="61" customHeight="1" spans="1:4">
+    <row r="5" s="27" customFormat="1" ht="61" customHeight="1" spans="1:6">
       <c r="A5" s="28"/>
       <c r="B5" s="28" t="s">
         <v>19</v>
@@ -7173,7 +7173,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="6" s="27" customFormat="1" ht="49" customHeight="1" spans="1:4">
+    <row r="6" s="27" customFormat="1" ht="49" customHeight="1" spans="1:6">
       <c r="A6" s="28"/>
       <c r="B6" s="28" t="s">
         <v>22</v>
@@ -7183,7 +7183,7 @@
       </c>
       <c r="D6" s="29"/>
     </row>
-    <row r="7" s="27" customFormat="1" ht="86" customHeight="1" spans="1:4">
+    <row r="7" s="27" customFormat="1" ht="86" customHeight="1" spans="1:6">
       <c r="A7" s="28"/>
       <c r="B7" s="28" t="s">
         <v>24</v>
@@ -7193,7 +7193,7 @@
       </c>
       <c r="D7" s="29"/>
     </row>
-    <row r="8" spans="2:4">
+    <row r="8" spans="1:6">
       <c r="B8" t="s">
         <v>26</v>
       </c>
@@ -7202,7 +7202,7 @@
       </c>
       <c r="D8" s="4"/>
     </row>
-    <row r="9" spans="2:3">
+    <row r="9" spans="1:6">
       <c r="B9" t="s">
         <v>28</v>
       </c>
@@ -7210,7 +7210,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="10" ht="30" spans="2:3">
+    <row r="10" ht="30" spans="1:6">
       <c r="B10" t="s">
         <v>30</v>
       </c>
@@ -7218,12 +7218,12 @@
         <v>31</v>
       </c>
     </row>
-    <row r="15" spans="1:1">
+    <row r="15" spans="1:6">
       <c r="A15" s="2" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="16" spans="2:3">
+    <row r="16" spans="1:6">
       <c r="B16" t="s">
         <v>33</v>
       </c>
@@ -7231,7 +7231,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="17" ht="75" spans="2:3">
+    <row r="17" ht="75" spans="2:7">
       <c r="B17" t="s">
         <v>35</v>
       </c>
@@ -7239,7 +7239,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="18" spans="2:3">
+    <row r="18" spans="2:7">
       <c r="B18" t="s">
         <v>37</v>
       </c>
@@ -7247,7 +7247,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="19" ht="75" spans="2:5">
+    <row r="19" ht="75" spans="2:7">
       <c r="B19" t="s">
         <v>39</v>
       </c>
@@ -7258,7 +7258,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="20" ht="45" spans="2:5">
+    <row r="20" ht="45" spans="2:7">
       <c r="B20" s="4" t="s">
         <v>42</v>
       </c>
@@ -7267,7 +7267,7 @@
       </c>
       <c r="E20" s="10"/>
     </row>
-    <row r="21" ht="60" spans="2:5">
+    <row r="21" ht="60" spans="2:7">
       <c r="B21" t="s">
         <v>44</v>
       </c>
@@ -7276,7 +7276,7 @@
       </c>
       <c r="E21" s="10"/>
     </row>
-    <row r="22" ht="30" spans="2:5">
+    <row r="22" ht="30" spans="2:7">
       <c r="B22" s="4" t="s">
         <v>46</v>
       </c>
@@ -7340,12 +7340,12 @@
         <v>50</v>
       </c>
     </row>
-    <row r="2" spans="1:1">
+    <row r="2" spans="1:6">
       <c r="A2" s="1" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:6">
       <c r="A3" s="1"/>
       <c r="B3" s="4" t="s">
         <v>14</v>
@@ -7354,7 +7354,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="4" spans="2:4">
+    <row r="4" spans="1:6">
       <c r="B4" s="17" t="s">
         <v>16</v>
       </c>
@@ -7365,7 +7365,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:6">
       <c r="A5" s="1"/>
       <c r="B5" s="17" t="s">
         <v>19</v>
@@ -7374,7 +7374,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="6" spans="2:3">
+    <row r="6" spans="1:6">
       <c r="B6" s="17" t="s">
         <v>22</v>
       </c>
@@ -7382,7 +7382,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="7" ht="30" spans="2:4">
+    <row r="7" ht="30" spans="1:6">
       <c r="B7" s="4" t="s">
         <v>55</v>
       </c>
@@ -7393,7 +7393,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="8" ht="60" spans="2:5">
+    <row r="8" ht="60" spans="1:6">
       <c r="B8" s="4" t="s">
         <v>58</v>
       </c>
@@ -7407,7 +7407,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="9" spans="2:4">
+    <row r="9" spans="1:6">
       <c r="B9" s="10" t="s">
         <v>62</v>
       </c>
@@ -7416,7 +7416,7 @@
       </c>
       <c r="D9" s="10"/>
     </row>
-    <row r="10" spans="2:4">
+    <row r="10" spans="1:6">
       <c r="B10" s="4" t="s">
         <v>64</v>
       </c>
@@ -7427,7 +7427,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="11" spans="2:4">
+    <row r="11" spans="1:6">
       <c r="B11" s="17" t="s">
         <v>67</v>
       </c>
@@ -7438,7 +7438,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="12" spans="2:4">
+    <row r="12" spans="1:6">
       <c r="B12" s="17" t="s">
         <v>70</v>
       </c>
@@ -7449,7 +7449,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="13" ht="60" spans="2:4">
+    <row r="13" ht="60" spans="1:6">
       <c r="B13" s="4" t="s">
         <v>72</v>
       </c>
@@ -7460,7 +7460,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="14" ht="30" spans="2:4">
+    <row r="14" ht="30" spans="1:6">
       <c r="B14" s="4" t="s">
         <v>75</v>
       </c>
@@ -7471,7 +7471,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="15" ht="30" spans="2:4">
+    <row r="15" ht="30" spans="1:6">
       <c r="B15" s="4" t="s">
         <v>78</v>
       </c>
@@ -7482,7 +7482,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="16" spans="2:4">
+    <row r="16" spans="1:6">
       <c r="B16" s="17" t="s">
         <v>81</v>
       </c>
@@ -7507,7 +7507,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="18" ht="60" spans="2:4">
+    <row r="18" ht="60" spans="2:5">
       <c r="B18" s="4" t="s">
         <v>88</v>
       </c>
@@ -7516,7 +7516,7 @@
       </c>
       <c r="D18" s="12"/>
     </row>
-    <row r="19" spans="2:4">
+    <row r="19" spans="2:5">
       <c r="B19" s="4" t="s">
         <v>90</v>
       </c>
@@ -7525,7 +7525,7 @@
       </c>
       <c r="D19" s="12"/>
     </row>
-    <row r="20" spans="2:4">
+    <row r="20" spans="2:5">
       <c r="B20" s="4" t="s">
         <v>92</v>
       </c>
@@ -7534,7 +7534,7 @@
       </c>
       <c r="D20" s="12"/>
     </row>
-    <row r="21" spans="2:4">
+    <row r="21" spans="2:5">
       <c r="B21" s="4" t="s">
         <v>94</v>
       </c>
@@ -7543,7 +7543,7 @@
       </c>
       <c r="D21" s="12"/>
     </row>
-    <row r="22" spans="2:4">
+    <row r="22" spans="2:5">
       <c r="B22" s="4" t="s">
         <v>96</v>
       </c>
@@ -7552,7 +7552,7 @@
       </c>
       <c r="D22" s="12"/>
     </row>
-    <row r="23" spans="2:4">
+    <row r="23" spans="2:5">
       <c r="B23" s="4" t="s">
         <v>98</v>
       </c>
@@ -7572,7 +7572,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="25" spans="2:3">
+    <row r="25" spans="2:5">
       <c r="B25" s="4" t="s">
         <v>103</v>
       </c>
@@ -7659,7 +7659,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="33" ht="30" spans="2:4">
+    <row r="33" ht="30" spans="2:6">
       <c r="B33" s="4" t="s">
         <v>112</v>
       </c>
@@ -7668,7 +7668,7 @@
       </c>
       <c r="D33" s="14"/>
     </row>
-    <row r="34" spans="2:4">
+    <row r="34" spans="2:6">
       <c r="B34" s="4" t="s">
         <v>114</v>
       </c>
@@ -7677,7 +7677,7 @@
       </c>
       <c r="D34" s="14"/>
     </row>
-    <row r="35" ht="30" spans="2:4">
+    <row r="35" ht="30" spans="2:6">
       <c r="B35" s="4" t="s">
         <v>116</v>
       </c>
@@ -7686,7 +7686,7 @@
       </c>
       <c r="D35" s="14"/>
     </row>
-    <row r="36" spans="2:4">
+    <row r="36" spans="2:6">
       <c r="B36" s="4" t="s">
         <v>118</v>
       </c>
@@ -7695,7 +7695,7 @@
       </c>
       <c r="D36" s="14"/>
     </row>
-    <row r="37" spans="2:4">
+    <row r="37" spans="2:6">
       <c r="B37" s="4" t="s">
         <v>118</v>
       </c>
@@ -7706,7 +7706,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="38" ht="45" spans="2:5">
+    <row r="38" ht="45" spans="2:6">
       <c r="B38" s="4" t="s">
         <v>128</v>
       </c>
@@ -7740,7 +7740,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="41" spans="2:4">
+    <row r="41" spans="2:6">
       <c r="B41" s="17" t="s">
         <v>136</v>
       </c>
@@ -7749,7 +7749,7 @@
       </c>
       <c r="D41" s="10"/>
     </row>
-    <row r="42" spans="2:4">
+    <row r="42" spans="2:6">
       <c r="B42" s="17" t="s">
         <v>138</v>
       </c>
@@ -7758,7 +7758,7 @@
       </c>
       <c r="D42" s="10"/>
     </row>
-    <row r="43" spans="2:4">
+    <row r="43" spans="2:6">
       <c r="B43" s="17" t="s">
         <v>140</v>
       </c>
@@ -7767,7 +7767,7 @@
       </c>
       <c r="D43" s="10"/>
     </row>
-    <row r="44" spans="2:4">
+    <row r="44" spans="2:6">
       <c r="B44" s="4" t="s">
         <v>142</v>
       </c>
@@ -7776,7 +7776,7 @@
       </c>
       <c r="D44" s="10"/>
     </row>
-    <row r="45" ht="195" spans="2:5">
+    <row r="45" ht="195" spans="2:6">
       <c r="B45" s="17" t="s">
         <v>143</v>
       </c>
@@ -7790,7 +7790,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="46" ht="195" spans="2:5">
+    <row r="46" ht="195" spans="2:6">
       <c r="B46" s="17" t="s">
         <v>147</v>
       </c>
@@ -7804,7 +7804,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="47" ht="195" spans="2:5">
+    <row r="47" ht="195" spans="2:6">
       <c r="B47" s="17" t="s">
         <v>151</v>
       </c>
@@ -7816,7 +7816,7 @@
       </c>
       <c r="E47" s="25"/>
     </row>
-    <row r="48" customFormat="1" spans="2:5">
+    <row r="48" customFormat="1" spans="2:6">
       <c r="B48" s="4" t="s">
         <v>154</v>
       </c>
@@ -7826,7 +7826,7 @@
       <c r="D48" s="10"/>
       <c r="E48" s="4"/>
     </row>
-    <row r="49" customFormat="1" spans="2:5">
+    <row r="49" customFormat="1" spans="2:6">
       <c r="B49" s="4" t="s">
         <v>155</v>
       </c>
@@ -7836,7 +7836,7 @@
       <c r="D49" s="10"/>
       <c r="E49" s="4"/>
     </row>
-    <row r="50" customFormat="1" spans="2:5">
+    <row r="50" customFormat="1" spans="2:6">
       <c r="B50" s="4" t="s">
         <v>157</v>
       </c>
@@ -7846,7 +7846,7 @@
       <c r="D50" s="10"/>
       <c r="E50" s="4"/>
     </row>
-    <row r="51" customFormat="1" spans="2:5">
+    <row r="51" customFormat="1" spans="2:6">
       <c r="B51" s="4" t="s">
         <v>159</v>
       </c>
@@ -7856,7 +7856,7 @@
       <c r="D51" s="10"/>
       <c r="E51" s="4"/>
     </row>
-    <row r="52" ht="150" spans="2:5">
+    <row r="52" ht="150" spans="2:6">
       <c r="B52" s="10" t="s">
         <v>160</v>
       </c>
@@ -7870,7 +7870,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="53" spans="2:5">
+    <row r="53" spans="2:6">
       <c r="B53" s="4" t="s">
         <v>164</v>
       </c>
@@ -7880,7 +7880,7 @@
       <c r="D53" s="10"/>
       <c r="E53" s="8"/>
     </row>
-    <row r="54" customFormat="1" spans="2:5">
+    <row r="54" customFormat="1" spans="2:6">
       <c r="B54" s="4" t="s">
         <v>166</v>
       </c>
@@ -7890,7 +7890,7 @@
       <c r="D54" s="10"/>
       <c r="E54" s="8"/>
     </row>
-    <row r="55" customFormat="1" spans="2:5">
+    <row r="55" customFormat="1" spans="2:6">
       <c r="B55" s="4" t="s">
         <v>167</v>
       </c>
@@ -7900,7 +7900,7 @@
       <c r="D55" s="10"/>
       <c r="E55" s="8"/>
     </row>
-    <row r="56" customFormat="1" spans="2:5">
+    <row r="56" customFormat="1" spans="2:6">
       <c r="B56" s="4" t="s">
         <v>169</v>
       </c>
@@ -7910,7 +7910,7 @@
       <c r="D56" s="10"/>
       <c r="E56" s="8"/>
     </row>
-    <row r="57" customFormat="1" spans="2:5">
+    <row r="57" customFormat="1" spans="2:6">
       <c r="B57" s="4" t="s">
         <v>171</v>
       </c>
@@ -7920,7 +7920,7 @@
       <c r="D57" s="10"/>
       <c r="E57" s="8"/>
     </row>
-    <row r="58" spans="2:5">
+    <row r="58" spans="2:6">
       <c r="B58" s="4" t="s">
         <v>172</v>
       </c>
@@ -7930,7 +7930,7 @@
       <c r="D58" s="10"/>
       <c r="E58" s="8"/>
     </row>
-    <row r="59" ht="180" spans="2:5">
+    <row r="59" ht="180" spans="2:6">
       <c r="B59" s="10" t="s">
         <v>174</v>
       </c>
@@ -8063,7 +8063,7 @@
     <col min="6" max="6" width="57.5714285714286" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:6">
+    <row r="1" s="1" customFormat="1" spans="1:7">
       <c r="A1" s="2" t="s">
         <v>8</v>
       </c>
@@ -8083,7 +8083,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="2" ht="33" customHeight="1" spans="1:5">
+    <row r="2" ht="33" customHeight="1" spans="1:7">
       <c r="A2" s="1" t="s">
         <v>39</v>
       </c>
@@ -8094,7 +8094,7 @@
       <c r="D2" s="3"/>
       <c r="E2" s="3"/>
     </row>
-    <row r="3" spans="2:3">
+    <row r="3" spans="1:7">
       <c r="B3" s="4" t="s">
         <v>14</v>
       </c>
@@ -8102,7 +8102,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="4" ht="60" spans="2:7">
+    <row r="4" ht="60" spans="1:7">
       <c r="B4" s="5" t="s">
         <v>16</v>
       </c>
@@ -8115,7 +8115,7 @@
       <c r="F4" s="7"/>
       <c r="G4" s="7"/>
     </row>
-    <row r="5" spans="2:5">
+    <row r="5" spans="1:7">
       <c r="B5" s="5" t="s">
         <v>19</v>
       </c>
@@ -8124,7 +8124,7 @@
       </c>
       <c r="E5" s="8"/>
     </row>
-    <row r="6" spans="2:5">
+    <row r="6" spans="1:7">
       <c r="B6" s="5" t="s">
         <v>22</v>
       </c>
@@ -8133,7 +8133,7 @@
       </c>
       <c r="E6" s="26"/>
     </row>
-    <row r="7" ht="120" spans="2:6">
+    <row r="7" ht="120" spans="1:7">
       <c r="B7" s="5" t="s">
         <v>202</v>
       </c>
@@ -8148,7 +8148,7 @@
       </c>
       <c r="F7" s="4"/>
     </row>
-    <row r="8" ht="94" customHeight="1" spans="2:5">
+    <row r="8" ht="94" customHeight="1" spans="1:7">
       <c r="B8" s="5" t="s">
         <v>206</v>
       </c>
@@ -8162,7 +8162,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="9" customFormat="1" spans="2:5">
+    <row r="9" customFormat="1" spans="1:7">
       <c r="B9" s="5" t="s">
         <v>210</v>
       </c>
@@ -8174,7 +8174,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="10" spans="2:5">
+    <row r="10" spans="1:7">
       <c r="B10" s="5" t="s">
         <v>212</v>
       </c>
@@ -8186,7 +8186,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="11" ht="225" spans="2:5">
+    <row r="11" ht="225" spans="1:7">
       <c r="B11" s="5" t="s">
         <v>214</v>
       </c>
@@ -8200,7 +8200,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="12" spans="2:5">
+    <row r="12" spans="1:7">
       <c r="B12" s="5" t="s">
         <v>217</v>
       </c>
@@ -8211,7 +8211,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="13" spans="2:5">
+    <row r="13" spans="1:7">
       <c r="B13" s="5" t="s">
         <v>219</v>
       </c>
@@ -8222,7 +8222,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="14" ht="30" spans="2:5">
+    <row r="14" ht="30" spans="1:7">
       <c r="B14" s="5" t="s">
         <v>221</v>
       </c>
@@ -8236,7 +8236,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="15" ht="45" spans="2:5">
+    <row r="15" ht="45" spans="1:7">
       <c r="B15" s="5" t="s">
         <v>225</v>
       </c>
@@ -8250,7 +8250,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="16" ht="45" spans="2:5">
+    <row r="16" ht="45" spans="1:7">
       <c r="B16" s="5" t="s">
         <v>229</v>
       </c>
@@ -8262,7 +8262,7 @@
       </c>
       <c r="E16" s="8"/>
     </row>
-    <row r="17" ht="45" spans="2:5">
+    <row r="17" ht="45" spans="2:6">
       <c r="B17" s="5" t="s">
         <v>232</v>
       </c>
@@ -8274,7 +8274,7 @@
       </c>
       <c r="E17" s="8"/>
     </row>
-    <row r="18" ht="45" spans="2:5">
+    <row r="18" ht="45" spans="2:6">
       <c r="B18" t="s">
         <v>235</v>
       </c>
@@ -8288,7 +8288,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="19" ht="60" spans="2:5">
+    <row r="19" ht="60" spans="2:6">
       <c r="B19" s="5" t="s">
         <v>238</v>
       </c>
@@ -8302,7 +8302,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="20" customFormat="1" spans="2:5">
+    <row r="20" customFormat="1" spans="2:6">
       <c r="B20" s="5" t="s">
         <v>241</v>
       </c>
@@ -8383,7 +8383,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" ht="35" customHeight="1" spans="1:5">
+    <row r="2" ht="35" customHeight="1" spans="1:6">
       <c r="A2" s="1" t="s">
         <v>35</v>
       </c>
@@ -8394,7 +8394,7 @@
       <c r="D2" s="3"/>
       <c r="E2" s="3"/>
     </row>
-    <row r="3" customFormat="1" spans="2:3">
+    <row r="3" customFormat="1" spans="1:6">
       <c r="B3" s="4" t="s">
         <v>14</v>
       </c>
@@ -8402,7 +8402,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="4" ht="75" spans="1:5">
+    <row r="4" ht="75" spans="1:6">
       <c r="A4" s="1"/>
       <c r="B4" s="5" t="s">
         <v>16</v>
@@ -8429,7 +8429,7 @@
       <c r="E5" s="4"/>
       <c r="F5" s="4"/>
     </row>
-    <row r="6" customFormat="1" ht="30" spans="2:6">
+    <row r="6" customFormat="1" ht="30" spans="1:6">
       <c r="B6" s="17" t="s">
         <v>22</v>
       </c>
@@ -8440,7 +8440,7 @@
       <c r="E6" s="4"/>
       <c r="F6" s="4"/>
     </row>
-    <row r="7" ht="165" spans="2:5">
+    <row r="7" ht="165" spans="1:6">
       <c r="B7" s="5" t="s">
         <v>202</v>
       </c>
@@ -8454,7 +8454,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="8" ht="71" customHeight="1" spans="2:5">
+    <row r="8" ht="71" customHeight="1" spans="1:6">
       <c r="B8" s="5" t="s">
         <v>253</v>
       </c>
@@ -8466,7 +8466,7 @@
       </c>
       <c r="E8" s="9"/>
     </row>
-    <row r="9" ht="30" spans="2:5">
+    <row r="9" ht="30" spans="1:6">
       <c r="B9" s="5" t="s">
         <v>256</v>
       </c>
@@ -8476,7 +8476,7 @@
       <c r="D9" s="10"/>
       <c r="E9" s="25"/>
     </row>
-    <row r="10" spans="2:5">
+    <row r="10" spans="1:6">
       <c r="B10" s="5" t="s">
         <v>258</v>
       </c>
@@ -8486,7 +8486,7 @@
       <c r="D10" s="10"/>
       <c r="E10" s="9"/>
     </row>
-    <row r="11" ht="30" spans="2:4">
+    <row r="11" ht="30" spans="1:6">
       <c r="B11" s="5" t="s">
         <v>260</v>
       </c>
@@ -8497,7 +8497,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="12" ht="60" spans="2:5">
+    <row r="12" ht="60" spans="1:6">
       <c r="B12" s="5" t="s">
         <v>263</v>
       </c>
@@ -8506,7 +8506,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="13" ht="33" customHeight="1" spans="2:4">
+    <row r="13" ht="33" customHeight="1" spans="1:6">
       <c r="B13" s="5" t="s">
         <v>265</v>
       </c>
@@ -8515,7 +8515,7 @@
       </c>
       <c r="D13" s="12"/>
     </row>
-    <row r="14" customFormat="1" spans="2:3">
+    <row r="14" customFormat="1" spans="1:6">
       <c r="B14" t="s">
         <v>267</v>
       </c>
@@ -8523,7 +8523,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="15" customFormat="1" ht="60" spans="2:4">
+    <row r="15" customFormat="1" ht="60" spans="1:6">
       <c r="B15" s="5" t="s">
         <v>269</v>
       </c>
@@ -8534,7 +8534,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="16" customFormat="1" ht="30" spans="2:3">
+    <row r="16" customFormat="1" ht="30" spans="1:6">
       <c r="B16" s="5" t="s">
         <v>271</v>
       </c>
@@ -8542,7 +8542,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="17" ht="60" spans="2:4">
+    <row r="17" ht="60" spans="2:5">
       <c r="B17" t="s">
         <v>273</v>
       </c>
@@ -8553,7 +8553,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="18" spans="2:3">
+    <row r="18" spans="2:5">
       <c r="B18" t="s">
         <v>276</v>
       </c>
@@ -8626,7 +8626,7 @@
       <c r="D24" s="10"/>
       <c r="E24" s="4"/>
     </row>
-    <row r="25" customFormat="1" spans="2:4">
+    <row r="25" customFormat="1" spans="2:5">
       <c r="B25" s="4" t="s">
         <v>192</v>
       </c>
@@ -8637,7 +8637,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="26" customFormat="1" ht="46" customHeight="1" spans="2:4">
+    <row r="26" customFormat="1" ht="46" customHeight="1" spans="2:5">
       <c r="B26" s="4" t="s">
         <v>195</v>
       </c>
@@ -8694,12 +8694,12 @@
         <v>50</v>
       </c>
     </row>
-    <row r="2" spans="1:1">
+    <row r="2" spans="1:6">
       <c r="A2" s="1" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="3" customFormat="1" spans="2:3">
+    <row r="3" customFormat="1" spans="1:6">
       <c r="B3" s="4" t="s">
         <v>14</v>
       </c>
@@ -8707,7 +8707,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="4" spans="2:3">
+    <row r="4" spans="1:6">
       <c r="B4" t="s">
         <v>16</v>
       </c>
@@ -8729,7 +8729,7 @@
       </c>
       <c r="F5" s="4"/>
     </row>
-    <row r="6" customFormat="1" ht="30" spans="2:6">
+    <row r="6" customFormat="1" ht="30" spans="1:6">
       <c r="B6" s="4" t="s">
         <v>22</v>
       </c>
@@ -8740,7 +8740,7 @@
       <c r="E6" s="4"/>
       <c r="F6" s="4"/>
     </row>
-    <row r="7" spans="2:6">
+    <row r="7" spans="1:6">
       <c r="B7" s="5" t="s">
         <v>299</v>
       </c>
@@ -8754,7 +8754,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="8" ht="63" customHeight="1" spans="2:6">
+    <row r="8" ht="63" customHeight="1" spans="1:6">
       <c r="B8" t="s">
         <v>303</v>
       </c>
@@ -8768,7 +8768,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="9" spans="2:5">
+    <row r="9" spans="1:6">
       <c r="B9" t="s">
         <v>307</v>
       </c>
@@ -8778,7 +8778,7 @@
       <c r="D9" s="10"/>
       <c r="E9" s="8"/>
     </row>
-    <row r="10" ht="30" spans="2:5">
+    <row r="10" ht="30" spans="1:6">
       <c r="B10" s="4" t="s">
         <v>309</v>
       </c>
@@ -8788,7 +8788,7 @@
       <c r="D10" s="10"/>
       <c r="E10" s="8"/>
     </row>
-    <row r="11" ht="30" spans="2:5">
+    <row r="11" ht="30" spans="1:6">
       <c r="B11" s="4" t="s">
         <v>311</v>
       </c>
@@ -8798,7 +8798,7 @@
       <c r="D11" s="10"/>
       <c r="E11" s="8"/>
     </row>
-    <row r="12" ht="30" spans="2:5">
+    <row r="12" ht="30" spans="1:6">
       <c r="B12" s="4" t="s">
         <v>312</v>
       </c>
@@ -8808,7 +8808,7 @@
       <c r="D12" s="10"/>
       <c r="E12" s="8"/>
     </row>
-    <row r="13" customFormat="1" ht="66" customHeight="1" spans="2:6">
+    <row r="13" customFormat="1" ht="66" customHeight="1" spans="1:6">
       <c r="B13" t="s">
         <v>314</v>
       </c>
@@ -8822,7 +8822,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="14" customFormat="1" spans="2:5">
+    <row r="14" customFormat="1" spans="1:6">
       <c r="B14" t="s">
         <v>317</v>
       </c>
@@ -8832,7 +8832,7 @@
       <c r="D14" s="10"/>
       <c r="E14" s="22"/>
     </row>
-    <row r="15" customFormat="1" ht="30" spans="2:5">
+    <row r="15" customFormat="1" ht="30" spans="1:6">
       <c r="B15" s="4" t="s">
         <v>319</v>
       </c>
@@ -8842,7 +8842,7 @@
       <c r="D15" s="10"/>
       <c r="E15" s="22"/>
     </row>
-    <row r="16" customFormat="1" ht="30" spans="2:5">
+    <row r="16" customFormat="1" ht="30" spans="1:6">
       <c r="B16" s="4" t="s">
         <v>321</v>
       </c>
@@ -8852,7 +8852,7 @@
       <c r="D16" s="10"/>
       <c r="E16" s="4"/>
     </row>
-    <row r="17" customFormat="1" ht="30" spans="2:4">
+    <row r="17" customFormat="1" ht="30" spans="2:6">
       <c r="B17" s="4" t="s">
         <v>322</v>
       </c>
@@ -8861,7 +8861,7 @@
       </c>
       <c r="D17" s="10"/>
     </row>
-    <row r="18" ht="60" spans="2:5">
+    <row r="18" ht="60" spans="2:6">
       <c r="B18" s="5" t="s">
         <v>324</v>
       </c>
@@ -9013,7 +9013,7 @@
       <c r="E30" s="4"/>
       <c r="F30" s="4"/>
     </row>
-    <row r="31" customFormat="1" spans="2:4">
+    <row r="31" customFormat="1" spans="2:6">
       <c r="B31" s="4" t="s">
         <v>192</v>
       </c>
@@ -9024,7 +9024,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="32" customFormat="1" ht="46" customHeight="1" spans="2:4">
+    <row r="32" customFormat="1" ht="46" customHeight="1" spans="2:6">
       <c r="B32" s="4" t="s">
         <v>195</v>
       </c>
@@ -9081,12 +9081,12 @@
         <v>50</v>
       </c>
     </row>
-    <row r="2" ht="45" spans="1:1">
+    <row r="2" ht="45" spans="1:6">
       <c r="A2" s="21" t="s">
         <v>348</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:6">
       <c r="A3" s="1"/>
       <c r="B3" s="4" t="s">
         <v>14</v>
@@ -9095,7 +9095,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="4" spans="1:4">
+    <row r="4" spans="1:6">
       <c r="A4" s="1"/>
       <c r="B4" s="5" t="s">
         <v>16</v>
@@ -9119,7 +9119,7 @@
       <c r="E5" s="4"/>
       <c r="F5" s="4"/>
     </row>
-    <row r="6" ht="30" spans="2:6">
+    <row r="6" ht="30" spans="1:6">
       <c r="B6" s="17" t="s">
         <v>22</v>
       </c>
@@ -9130,7 +9130,7 @@
       <c r="E6" s="4"/>
       <c r="F6" s="4"/>
     </row>
-    <row r="7" spans="2:6">
+    <row r="7" spans="1:6">
       <c r="B7" t="s">
         <v>55</v>
       </c>
@@ -9141,7 +9141,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="8" ht="150" spans="2:5">
+    <row r="8" ht="150" spans="1:6">
       <c r="B8" s="5" t="s">
         <v>202</v>
       </c>
@@ -9155,7 +9155,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="9" ht="70" customHeight="1" spans="2:4">
+    <row r="9" ht="70" customHeight="1" spans="1:6">
       <c r="B9" s="5" t="s">
         <v>356</v>
       </c>
@@ -9166,7 +9166,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="10" ht="30" spans="2:4">
+    <row r="10" ht="30" spans="1:6">
       <c r="B10" s="5" t="s">
         <v>359</v>
       </c>
@@ -9175,7 +9175,7 @@
       </c>
       <c r="D10" s="10"/>
     </row>
-    <row r="11" spans="2:5">
+    <row r="11" spans="1:6">
       <c r="B11" s="5" t="s">
         <v>361</v>
       </c>
@@ -9185,7 +9185,7 @@
       <c r="D11" s="10"/>
       <c r="E11" s="8"/>
     </row>
-    <row r="12" ht="30" spans="2:4">
+    <row r="12" ht="30" spans="1:6">
       <c r="B12" s="5" t="s">
         <v>362</v>
       </c>
@@ -9194,7 +9194,7 @@
       </c>
       <c r="D12" s="10"/>
     </row>
-    <row r="13" ht="38" customHeight="1" spans="2:4">
+    <row r="13" ht="38" customHeight="1" spans="1:6">
       <c r="B13" s="4" t="s">
         <v>363</v>
       </c>
@@ -9205,7 +9205,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="14" ht="30" spans="2:4">
+    <row r="14" ht="30" spans="1:6">
       <c r="B14" s="4" t="s">
         <v>366</v>
       </c>
@@ -9214,7 +9214,7 @@
       </c>
       <c r="D14" s="10"/>
     </row>
-    <row r="15" ht="153" customHeight="1" spans="2:5">
+    <row r="15" ht="153" customHeight="1" spans="1:6">
       <c r="B15" s="4" t="s">
         <v>368</v>
       </c>
@@ -9226,7 +9226,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="16" ht="75" spans="2:4">
+    <row r="16" ht="75" spans="1:6">
       <c r="B16" s="5" t="s">
         <v>269</v>
       </c>
@@ -9237,7 +9237,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="17" ht="30" spans="2:3">
+    <row r="17" ht="30" spans="2:6">
       <c r="B17" s="5" t="s">
         <v>271</v>
       </c>
@@ -9245,7 +9245,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="18" ht="90" spans="2:5">
+    <row r="18" ht="90" spans="2:6">
       <c r="B18" t="s">
         <v>371</v>
       </c>
@@ -9270,7 +9270,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="20" spans="2:4">
+    <row r="20" spans="2:6">
       <c r="B20" s="4" t="s">
         <v>192</v>
       </c>
@@ -9281,7 +9281,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="21" ht="45" customHeight="1" spans="2:4">
+    <row r="21" ht="45" customHeight="1" spans="2:6">
       <c r="B21" s="4" t="s">
         <v>195</v>
       </c>
@@ -9347,7 +9347,7 @@
       <c r="E2" s="3"/>
       <c r="F2" s="20"/>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:6">
       <c r="A3" s="1"/>
       <c r="B3" s="4" t="s">
         <v>14</v>
@@ -9356,7 +9356,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="4" ht="78" spans="1:4">
+    <row r="4" ht="78" spans="1:6">
       <c r="A4" s="1"/>
       <c r="B4" s="5" t="s">
         <v>16</v>
@@ -9380,7 +9380,7 @@
       <c r="E5" s="4"/>
       <c r="F5" s="4"/>
     </row>
-    <row r="6" customFormat="1" ht="30" spans="2:6">
+    <row r="6" customFormat="1" ht="30" spans="1:6">
       <c r="B6" s="17" t="s">
         <v>22</v>
       </c>
@@ -9391,7 +9391,7 @@
       <c r="E6" s="4"/>
       <c r="F6" s="4"/>
     </row>
-    <row r="7" spans="2:6">
+    <row r="7" spans="1:6">
       <c r="B7" t="s">
         <v>55</v>
       </c>
@@ -9402,7 +9402,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="8" ht="105" spans="2:5">
+    <row r="8" ht="105" spans="1:6">
       <c r="B8" s="5" t="s">
         <v>202</v>
       </c>
@@ -9416,7 +9416,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="9" ht="139" customHeight="1" spans="2:5">
+    <row r="9" ht="139" customHeight="1" spans="1:6">
       <c r="B9" s="5" t="s">
         <v>386</v>
       </c>
@@ -9427,7 +9427,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="10" ht="45" spans="2:5">
+    <row r="10" ht="45" spans="1:6">
       <c r="B10" s="5" t="s">
         <v>219</v>
       </c>
@@ -9439,7 +9439,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="11" ht="210" spans="2:5">
+    <row r="11" ht="210" spans="1:6">
       <c r="B11" s="5" t="s">
         <v>214</v>
       </c>
@@ -9448,7 +9448,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="12" ht="210" spans="2:5">
+    <row r="12" ht="210" spans="1:6">
       <c r="B12" s="5" t="s">
         <v>217</v>
       </c>
@@ -9457,7 +9457,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="13" spans="2:5">
+    <row r="13" spans="1:6">
       <c r="B13" s="5" t="s">
         <v>393</v>
       </c>
@@ -9466,7 +9466,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="14" ht="84" customHeight="1" spans="2:5">
+    <row r="14" ht="84" customHeight="1" spans="1:6">
       <c r="B14" s="5" t="s">
         <v>356</v>
       </c>
@@ -9478,7 +9478,7 @@
       </c>
       <c r="E14" s="9"/>
     </row>
-    <row r="15" spans="2:5">
+    <row r="15" spans="1:6">
       <c r="B15" s="5" t="s">
         <v>359</v>
       </c>
@@ -9488,7 +9488,7 @@
       <c r="D15" s="10"/>
       <c r="E15" s="9"/>
     </row>
-    <row r="16" spans="2:5">
+    <row r="16" spans="1:6">
       <c r="B16" s="5" t="s">
         <v>361</v>
       </c>
@@ -9498,7 +9498,7 @@
       <c r="D16" s="10"/>
       <c r="E16" s="9"/>
     </row>
-    <row r="17" ht="30" spans="2:5">
+    <row r="17" ht="30" spans="2:6">
       <c r="B17" s="5" t="s">
         <v>362</v>
       </c>
@@ -9510,7 +9510,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="18" ht="105" spans="2:5">
+    <row r="18" ht="105" spans="2:6">
       <c r="B18" s="4" t="s">
         <v>363</v>
       </c>
@@ -9524,7 +9524,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="19" ht="30" spans="2:3">
+    <row r="19" ht="30" spans="2:6">
       <c r="B19" s="4" t="s">
         <v>366</v>
       </c>
@@ -9532,7 +9532,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="20" ht="30" spans="2:3">
+    <row r="20" ht="30" spans="2:6">
       <c r="B20" s="4" t="s">
         <v>368</v>
       </c>
@@ -9540,7 +9540,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="21" ht="37" customHeight="1" spans="2:5">
+    <row r="21" ht="37" customHeight="1" spans="2:6">
       <c r="B21" s="5" t="s">
         <v>402</v>
       </c>
@@ -9552,7 +9552,7 @@
       </c>
       <c r="E21" s="8"/>
     </row>
-    <row r="22" ht="75" spans="2:5">
+    <row r="22" ht="75" spans="2:6">
       <c r="B22" s="5" t="s">
         <v>405</v>
       </c>
@@ -9564,7 +9564,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="23" ht="45" spans="2:5">
+    <row r="23" ht="45" spans="2:6">
       <c r="B23" s="5" t="s">
         <v>408</v>
       </c>
@@ -9573,7 +9573,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="24" ht="60" spans="2:4">
+    <row r="24" ht="60" spans="2:6">
       <c r="B24" s="5" t="s">
         <v>269</v>
       </c>
@@ -9584,7 +9584,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="25" ht="30" spans="2:3">
+    <row r="25" ht="30" spans="2:6">
       <c r="B25" s="5" t="s">
         <v>271</v>
       </c>
@@ -9592,7 +9592,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="26" ht="45" spans="2:4">
+    <row r="26" ht="45" spans="2:6">
       <c r="B26" s="5" t="s">
         <v>410</v>
       </c>
@@ -9603,7 +9603,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="27" ht="225" spans="2:5">
+    <row r="27" ht="225" spans="2:6">
       <c r="B27" s="5" t="s">
         <v>371</v>
       </c>
@@ -9615,7 +9615,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="28" ht="45" spans="2:4">
+    <row r="28" ht="45" spans="2:6">
       <c r="B28" s="5" t="s">
         <v>414</v>
       </c>
@@ -9638,7 +9638,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="30" spans="2:4">
+    <row r="30" spans="2:6">
       <c r="B30" s="4" t="s">
         <v>192</v>
       </c>
@@ -9649,7 +9649,7 @@
         <v>416</v>
       </c>
     </row>
-    <row r="31" ht="46" customHeight="1" spans="2:4">
+    <row r="31" ht="46" customHeight="1" spans="2:6">
       <c r="B31" s="4" t="s">
         <v>195</v>
       </c>
@@ -9717,7 +9717,7 @@
       <c r="E2" s="3"/>
       <c r="F2" s="3"/>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:6">
       <c r="A3" s="1"/>
       <c r="B3" s="4" t="s">
         <v>14</v>
@@ -9726,7 +9726,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="4" spans="1:4">
+    <row r="4" spans="1:6">
       <c r="A4" s="1"/>
       <c r="B4" s="5" t="s">
         <v>16</v>
@@ -9750,7 +9750,7 @@
       <c r="E5" s="4"/>
       <c r="F5" s="4"/>
     </row>
-    <row r="6" customFormat="1" ht="30" spans="2:6">
+    <row r="6" customFormat="1" ht="30" spans="1:6">
       <c r="B6" s="17" t="s">
         <v>22</v>
       </c>
@@ -9761,7 +9761,7 @@
       <c r="E6" s="4"/>
       <c r="F6" s="4"/>
     </row>
-    <row r="7" spans="2:6">
+    <row r="7" spans="1:6">
       <c r="B7" t="s">
         <v>55</v>
       </c>
@@ -9775,7 +9775,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="8" ht="105" spans="2:5">
+    <row r="8" ht="105" spans="1:6">
       <c r="B8" s="5" t="s">
         <v>202</v>
       </c>
@@ -9789,7 +9789,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="9" ht="409" customHeight="1" spans="2:5">
+    <row r="9" ht="409" customHeight="1" spans="1:6">
       <c r="B9" s="5" t="s">
         <v>386</v>
       </c>
@@ -9800,7 +9800,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="10" ht="165" spans="2:5">
+    <row r="10" ht="165" spans="1:6">
       <c r="B10" s="5" t="s">
         <v>356</v>
       </c>
@@ -9814,7 +9814,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="11" ht="180" spans="2:5">
+    <row r="11" ht="180" spans="1:6">
       <c r="B11" s="5" t="s">
         <v>359</v>
       </c>
@@ -9823,7 +9823,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="12" ht="150" spans="2:5">
+    <row r="12" ht="150" spans="1:6">
       <c r="B12" s="5" t="s">
         <v>361</v>
       </c>
@@ -9832,7 +9832,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="13" ht="75" spans="2:4">
+    <row r="13" ht="75" spans="1:6">
       <c r="B13" s="5" t="s">
         <v>269</v>
       </c>
@@ -9843,7 +9843,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="14" ht="30" spans="2:3">
+    <row r="14" ht="30" spans="1:6">
       <c r="B14" s="5" t="s">
         <v>271</v>
       </c>
@@ -9851,7 +9851,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="15" ht="45" spans="2:4">
+    <row r="15" ht="45" spans="1:6">
       <c r="B15" s="5" t="s">
         <v>410</v>
       </c>
@@ -9862,7 +9862,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="16" ht="225" spans="2:5">
+    <row r="16" ht="225" spans="1:6">
       <c r="B16" s="5" t="s">
         <v>371</v>
       </c>
@@ -9874,7 +9874,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="17" ht="45" spans="2:4">
+    <row r="17" ht="45" spans="2:6">
       <c r="B17" s="5" t="s">
         <v>414</v>
       </c>
@@ -9899,7 +9899,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="19" ht="165" spans="2:5">
+    <row r="19" ht="165" spans="2:6">
       <c r="B19" t="s">
         <v>426</v>
       </c>
@@ -9910,7 +9910,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="20" spans="2:4">
+    <row r="20" spans="2:6">
       <c r="B20" s="4" t="s">
         <v>192</v>
       </c>
@@ -9921,7 +9921,7 @@
         <v>416</v>
       </c>
     </row>
-    <row r="21" ht="46" customHeight="1" spans="2:4">
+    <row r="21" ht="46" customHeight="1" spans="2:6">
       <c r="B21" s="4" t="s">
         <v>195</v>
       </c>

--- a/support/specifications/ccda/CCDA to FHIR Conversion Spec - Epic.xlsx
+++ b/support/specifications/ccda/CCDA to FHIR Conversion Spec - Epic.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12180" tabRatio="709" activeTab="1"/>
+    <workbookView windowWidth="28800" windowHeight="12180" tabRatio="709" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Epic" sheetId="11" r:id="rId1"/>
@@ -1697,7 +1697,7 @@
     <t>maritalStatus -&gt; coding -&gt; system</t>
   </si>
   <si>
-    <t>"http://terminology.hl7.org/CodeSystem/v3-MaritalStatus"</t>
+    <t>If maritalStatus code is "UNK" then "http://terminology.hl7.org/CodeSystem/v3-NullFlavor", otherwise "http://terminology.hl7.org/CodeSystem/v3-MaritalStatus".</t>
   </si>
   <si>
     <t>maritalStatus -&gt; coding -&gt; code</t>
@@ -5533,6 +5533,7 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color rgb="FFC00000"/>
       <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -5546,17 +5547,16 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <i/>
       <sz val="11"/>
-      <color rgb="FFC00000"/>
+      <color rgb="FF00B050"/>
       <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF00B050"/>
       <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -6024,7 +6024,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -6083,9 +6083,6 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -6672,18 +6669,18 @@
   <dimension ref="A1:C7"/>
   <sheetFormatPr defaultColWidth="8.88571428571429" defaultRowHeight="15" outlineLevelRow="6" outlineLevelCol="2"/>
   <cols>
-    <col min="1" max="1" width="8.88571428571429" style="34"/>
+    <col min="1" max="1" width="8.88571428571429" style="33"/>
     <col min="2" max="2" width="35.2190476190476" customWidth="1"/>
     <col min="3" max="3" width="92.6666666666667" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="B1" s="35" t="s">
+      <c r="B1" s="34" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:3">
-      <c r="A3" s="34">
+      <c r="A3" s="33">
         <v>1</v>
       </c>
       <c r="B3" s="5" t="s">
@@ -6694,7 +6691,7 @@
       </c>
     </row>
     <row r="4" spans="1:3">
-      <c r="A4" s="34">
+      <c r="A4" s="33">
         <v>2</v>
       </c>
       <c r="B4" s="10" t="s">
@@ -6705,7 +6702,7 @@
       </c>
     </row>
     <row r="5" spans="1:3">
-      <c r="A5" s="34">
+      <c r="A5" s="33">
         <v>3</v>
       </c>
       <c r="B5" s="16" t="s">
@@ -6716,10 +6713,10 @@
       </c>
     </row>
     <row r="6" spans="1:3">
-      <c r="A6" s="34">
+      <c r="A6" s="33">
         <v>4</v>
       </c>
-      <c r="B6" s="27" t="s">
+      <c r="B6" s="26" t="s">
         <v>3</v>
       </c>
       <c r="C6" t="s">
@@ -6727,10 +6724,10 @@
       </c>
     </row>
     <row r="7" spans="1:3">
-      <c r="A7" s="34">
+      <c r="A7" s="33">
         <v>5</v>
       </c>
-      <c r="B7" s="29" t="s">
+      <c r="B7" s="28" t="s">
         <v>3</v>
       </c>
       <c r="C7" t="s">
@@ -7037,44 +7034,44 @@
       <c r="B4" t="s">
         <v>16</v>
       </c>
-      <c r="C4" s="29" t="s">
+      <c r="C4" s="28" t="s">
         <v>17</v>
       </c>
       <c r="D4" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="5" s="28" customFormat="1" ht="61" customHeight="1" spans="1:6">
-      <c r="A5" s="30"/>
-      <c r="B5" s="30" t="s">
+    <row r="5" s="27" customFormat="1" ht="61" customHeight="1" spans="1:6">
+      <c r="A5" s="29"/>
+      <c r="B5" s="29" t="s">
         <v>19</v>
       </c>
-      <c r="C5" s="30" t="s">
+      <c r="C5" s="29" t="s">
         <v>20</v>
       </c>
-      <c r="D5" s="31" t="s">
+      <c r="D5" s="30" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="6" s="28" customFormat="1" ht="49" customHeight="1" spans="1:6">
-      <c r="A6" s="30"/>
-      <c r="B6" s="30" t="s">
+    <row r="6" s="27" customFormat="1" ht="49" customHeight="1" spans="1:6">
+      <c r="A6" s="29"/>
+      <c r="B6" s="29" t="s">
         <v>22</v>
       </c>
-      <c r="C6" s="30" t="s">
+      <c r="C6" s="29" t="s">
         <v>23</v>
       </c>
-      <c r="D6" s="31"/>
-    </row>
-    <row r="7" s="28" customFormat="1" ht="316" customHeight="1" spans="1:6">
-      <c r="A7" s="30"/>
-      <c r="B7" s="30" t="s">
+      <c r="D6" s="30"/>
+    </row>
+    <row r="7" s="27" customFormat="1" ht="316" customHeight="1" spans="1:6">
+      <c r="A7" s="29"/>
+      <c r="B7" s="29" t="s">
         <v>24</v>
       </c>
-      <c r="C7" s="32" t="s">
+      <c r="C7" s="31" t="s">
         <v>25</v>
       </c>
-      <c r="D7" s="31"/>
+      <c r="D7" s="30"/>
     </row>
     <row r="8" spans="1:6">
       <c r="B8" t="s">
@@ -7137,7 +7134,7 @@
       <c r="C19" t="s">
         <v>40</v>
       </c>
-      <c r="E19" s="20" t="s">
+      <c r="E19" s="6" t="s">
         <v>41</v>
       </c>
     </row>
@@ -7166,7 +7163,7 @@
       <c r="E22" s="9"/>
     </row>
     <row r="23" ht="105" spans="2:7">
-      <c r="B23" s="33" t="s">
+      <c r="B23" s="32" t="s">
         <v>47</v>
       </c>
       <c r="C23" s="11" t="s">
@@ -7207,19 +7204,19 @@
       <c r="A1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="25" t="s">
+      <c r="B1" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="C1" s="25" t="s">
+      <c r="C1" s="24" t="s">
         <v>10</v>
       </c>
-      <c r="D1" s="25" t="s">
+      <c r="D1" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="E1" s="25" t="s">
+      <c r="E1" s="24" t="s">
         <v>49</v>
       </c>
-      <c r="F1" s="25" t="s">
+      <c r="F1" s="24" t="s">
         <v>50</v>
       </c>
     </row>
@@ -7241,7 +7238,7 @@
       <c r="B4" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="C4" s="20" t="s">
+      <c r="C4" s="6" t="s">
         <v>52</v>
       </c>
       <c r="D4" s="4" t="s">
@@ -7451,7 +7448,7 @@
       <c r="D24" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="E24" s="20" t="s">
+      <c r="E24" s="6" t="s">
         <v>103</v>
       </c>
     </row>
@@ -7470,7 +7467,7 @@
       <c r="C26" s="4" t="s">
         <v>107</v>
       </c>
-      <c r="E26" s="24" t="s">
+      <c r="E26" s="23" t="s">
         <v>108</v>
       </c>
     </row>
@@ -7597,7 +7594,7 @@
         <v>80</v>
       </c>
       <c r="D38" s="15"/>
-      <c r="E38" s="36" t="s">
+      <c r="E38" s="35" t="s">
         <v>130</v>
       </c>
     </row>
@@ -7669,7 +7666,7 @@
       <c r="D45" s="11" t="s">
         <v>146</v>
       </c>
-      <c r="E45" s="20" t="s">
+      <c r="E45" s="6" t="s">
         <v>147</v>
       </c>
     </row>
@@ -7677,7 +7674,7 @@
       <c r="B46" s="18" t="s">
         <v>148</v>
       </c>
-      <c r="C46" s="20" t="s">
+      <c r="C46" s="6" t="s">
         <v>149</v>
       </c>
       <c r="D46" s="11" t="s">
@@ -7697,7 +7694,7 @@
       <c r="D47" s="11" t="s">
         <v>154</v>
       </c>
-      <c r="E47" s="26"/>
+      <c r="E47" s="25"/>
     </row>
     <row r="48" customFormat="1" spans="2:6">
       <c r="B48" s="4" t="s">
@@ -7743,7 +7740,7 @@
       <c r="B52" s="11" t="s">
         <v>161</v>
       </c>
-      <c r="C52" s="20" t="s">
+      <c r="C52" s="6" t="s">
         <v>162</v>
       </c>
       <c r="D52" s="11" t="s">
@@ -7823,7 +7820,7 @@
       <c r="D59" s="11" t="s">
         <v>176</v>
       </c>
-      <c r="E59" s="20" t="s">
+      <c r="E59" s="6" t="s">
         <v>177</v>
       </c>
     </row>
@@ -7838,7 +7835,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="61" spans="2:6">
+    <row r="61" ht="45" spans="2:6">
       <c r="B61" s="4" t="s">
         <v>181</v>
       </c>
@@ -8015,7 +8012,7 @@
       <c r="C6" t="s">
         <v>202</v>
       </c>
-      <c r="E6" s="27"/>
+      <c r="E6" s="26"/>
     </row>
     <row r="7" ht="120" spans="1:7">
       <c r="B7" s="5" t="s">
@@ -8254,7 +8251,7 @@
       <c r="B1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C1" s="25" t="s">
+      <c r="C1" s="24" t="s">
         <v>10</v>
       </c>
       <c r="D1" s="2" t="s">
@@ -8291,7 +8288,7 @@
       <c r="B4" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="C4" s="20" t="s">
+      <c r="C4" s="6" t="s">
         <v>248</v>
       </c>
       <c r="D4" t="s">
@@ -8326,7 +8323,7 @@
       <c r="B7" s="5" t="s">
         <v>203</v>
       </c>
-      <c r="C7" s="20" t="s">
+      <c r="C7" s="6" t="s">
         <v>251</v>
       </c>
       <c r="D7" t="s">
@@ -8348,7 +8345,7 @@
       </c>
       <c r="E8" s="10"/>
     </row>
-    <row r="9" ht="30" spans="1:6">
+    <row r="9" spans="1:6">
       <c r="B9" s="5" t="s">
         <v>257</v>
       </c>
@@ -8356,7 +8353,7 @@
         <v>258</v>
       </c>
       <c r="D9" s="11"/>
-      <c r="E9" s="26"/>
+      <c r="E9" s="25"/>
     </row>
     <row r="10" spans="1:6">
       <c r="B10" s="5" t="s">
@@ -8368,11 +8365,11 @@
       <c r="D10" s="11"/>
       <c r="E10" s="10"/>
     </row>
-    <row r="11" ht="30" spans="1:6">
+    <row r="11" spans="1:6">
       <c r="B11" s="5" t="s">
         <v>261</v>
       </c>
-      <c r="C11" s="20" t="s">
+      <c r="C11" s="6" t="s">
         <v>262</v>
       </c>
       <c r="D11" s="13" t="s">
@@ -8484,7 +8481,7 @@
       <c r="C22" s="4" t="s">
         <v>289</v>
       </c>
-      <c r="E22" s="23"/>
+      <c r="E22" s="22"/>
     </row>
     <row r="23" ht="66" customHeight="1" spans="2:5">
       <c r="B23" t="s">
@@ -8643,7 +8640,7 @@
       <c r="B8" t="s">
         <v>306</v>
       </c>
-      <c r="C8" s="20" t="s">
+      <c r="C8" s="6" t="s">
         <v>307</v>
       </c>
       <c r="D8" s="11" t="s">
@@ -8697,7 +8694,7 @@
       <c r="B13" t="s">
         <v>317</v>
       </c>
-      <c r="C13" s="20" t="s">
+      <c r="C13" s="6" t="s">
         <v>318</v>
       </c>
       <c r="D13" s="11" t="s">
@@ -8715,7 +8712,7 @@
         <v>321</v>
       </c>
       <c r="D14" s="11"/>
-      <c r="E14" s="23"/>
+      <c r="E14" s="22"/>
     </row>
     <row r="15" customFormat="1" ht="30" spans="1:6">
       <c r="B15" s="4" t="s">
@@ -8725,7 +8722,7 @@
         <v>323</v>
       </c>
       <c r="D15" s="11"/>
-      <c r="E15" s="23"/>
+      <c r="E15" s="22"/>
     </row>
     <row r="16" customFormat="1" ht="30" spans="1:6">
       <c r="B16" s="4" t="s">
@@ -8750,7 +8747,7 @@
       <c r="B18" s="5" t="s">
         <v>327</v>
       </c>
-      <c r="C18" s="20" t="s">
+      <c r="C18" s="6" t="s">
         <v>328</v>
       </c>
       <c r="D18" s="11" t="s">
@@ -8789,7 +8786,7 @@
       <c r="D21" s="11" t="s">
         <v>336</v>
       </c>
-      <c r="E21" s="20" t="s">
+      <c r="E21" s="6" t="s">
         <v>103</v>
       </c>
       <c r="F21" s="4"/>
@@ -8812,7 +8809,7 @@
         <v>338</v>
       </c>
       <c r="D23" s="11"/>
-      <c r="E23" s="24" t="s">
+      <c r="E23" s="23" t="s">
         <v>339</v>
       </c>
       <c r="F23" s="4"/>
@@ -8967,7 +8964,7 @@
       </c>
     </row>
     <row r="2" ht="45" spans="1:6">
-      <c r="A2" s="22" t="s">
+      <c r="A2" s="21" t="s">
         <v>351</v>
       </c>
     </row>
@@ -9122,7 +9119,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="17" ht="30" spans="2:6">
+    <row r="17" spans="2:6">
       <c r="B17" s="5" t="s">
         <v>272</v>
       </c>
@@ -9230,7 +9227,7 @@
       <c r="C2" s="3"/>
       <c r="D2" s="3"/>
       <c r="E2" s="3"/>
-      <c r="F2" s="21"/>
+      <c r="F2" s="20"/>
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="1"/>
@@ -9246,7 +9243,7 @@
       <c r="B4" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="C4" s="20" t="s">
+      <c r="C4" s="6" t="s">
         <v>385</v>
       </c>
       <c r="D4" s="4" t="s">
@@ -9308,7 +9305,7 @@
       <c r="D9" s="7" t="s">
         <v>391</v>
       </c>
-      <c r="E9" s="20" t="s">
+      <c r="E9" s="6" t="s">
         <v>392</v>
       </c>
     </row>
@@ -9405,7 +9402,7 @@
       <c r="D18" s="11" t="s">
         <v>403</v>
       </c>
-      <c r="E18" s="20" t="s">
+      <c r="E18" s="6" t="s">
         <v>404</v>
       </c>
     </row>
@@ -9496,7 +9493,7 @@
       <c r="D27" t="s">
         <v>377</v>
       </c>
-      <c r="E27" s="20" t="s">
+      <c r="E27" s="6" t="s">
         <v>417</v>
       </c>
     </row>
@@ -9695,7 +9692,7 @@
       <c r="D10" s="11" t="s">
         <v>426</v>
       </c>
-      <c r="E10" s="20" t="s">
+      <c r="E10" s="6" t="s">
         <v>427</v>
       </c>
     </row>
@@ -9728,7 +9725,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="14" ht="30" spans="1:6">
+    <row r="14" spans="1:6">
       <c r="B14" s="5" t="s">
         <v>272</v>
       </c>
@@ -9755,7 +9752,7 @@
       <c r="D16" t="s">
         <v>377</v>
       </c>
-      <c r="E16" s="20" t="s">
+      <c r="E16" s="6" t="s">
         <v>417</v>
       </c>
     </row>

--- a/support/specifications/ccda/CCDA to FHIR Conversion Spec - Epic.xlsx
+++ b/support/specifications/ccda/CCDA to FHIR Conversion Spec - Epic.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12180" tabRatio="709" activeTab="2"/>
+    <workbookView windowWidth="28800" windowHeight="12180" tabRatio="709" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="Epic" sheetId="11" r:id="rId1"/>
@@ -3109,7 +3109,8 @@
     <t>SHA-256 UUID generated using 
 1. Patient-MRN (the value set for 'identifier (MR) -&gt; value' of Patient Resource from Document.recordTarget.patientRole.id.extension)
 2. Value of the header variable 'X-TechBD-CIN'
-3. Content of first occurance of Document.author section</t>
+3. Content of first occurance of Document.author section
+4. Organization Name from ClinicalDocument.component.structuredBody.component.section[code[@code='46240-8']].entry[1].encounter.participant[@typeCode='LOC'].participantRole[@classCode='SDLOC'].playingEntity.name</t>
   </si>
   <si>
     <t>"id" : "8e4752d52cb9f94657401368f1c8e3cdb052624b10166a665e4c80cdabc62b3c",</t>
@@ -5531,6 +5532,14 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF00B050"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFC00000"/>
@@ -5541,15 +5550,6 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF00B050"/>
       <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -5557,6 +5557,7 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -8586,7 +8587,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="4" ht="90" spans="1:6">
+    <row r="4" ht="165" spans="1:6">
       <c r="B4" t="s">
         <v>16</v>
       </c>
